--- a/Financial Analysis/PLTR.xlsx
+++ b/Financial Analysis/PLTR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Desktop\Financial Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A23B7803-E416-489F-B12C-C09C82740B85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74EDD837-9E8A-4307-AF27-2BEC712322C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{F38281D2-A2D5-4B11-829A-E3DB86132867}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{F38281D2-A2D5-4B11-829A-E3DB86132867}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -836,14 +836,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="4">
-        <v>112.86</v>
+        <v>127.59</v>
       </c>
       <c r="E3" s="3">
-        <v>45783</v>
+        <v>45804</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45783</v>
+        <v>45804</v>
       </c>
       <c r="G3" s="3">
         <v>45880</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>265074.28200000001</v>
+        <v>299670.63299999997</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -908,7 +908,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>259844.28200000001</v>
+        <v>294440.63299999997</v>
       </c>
     </row>
   </sheetData>
@@ -6152,7 +6152,7 @@
       </c>
       <c r="AZ31" s="4">
         <f>Main!D3</f>
-        <v>112.86</v>
+        <v>127.59</v>
       </c>
     </row>
     <row r="32" spans="2:166" x14ac:dyDescent="0.3">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="AZ32" s="10">
         <f>AZ30/AZ31-1</f>
-        <v>-0.65985115258855642</v>
+        <v>-0.69912062921188567</v>
       </c>
     </row>
     <row r="33" spans="2:52" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -7863,13 +7863,13 @@
     <row r="57" spans="2:141" x14ac:dyDescent="0.3">
       <c r="AZ57" s="4">
         <f>Main!D3</f>
-        <v>112.86</v>
+        <v>127.59</v>
       </c>
     </row>
     <row r="58" spans="2:141" x14ac:dyDescent="0.3">
       <c r="AZ58" s="10">
         <f>AZ56/AZ57-1</f>
-        <v>-0.61581621136985243</v>
+        <v>-0.66016943032527275</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/PLTR.xlsx
+++ b/Financial Analysis/PLTR.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74EDD837-9E8A-4307-AF27-2BEC712322C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5F75BA6-639A-4EAD-9D2C-9B295DCCB37A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{F38281D2-A2D5-4B11-829A-E3DB86132867}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="92">
   <si>
     <t>PLTR</t>
   </si>
@@ -299,6 +299,9 @@
   </si>
   <si>
     <t>FCF</t>
+  </si>
+  <si>
+    <t>SBC y/y</t>
   </si>
 </sst>
 </file>
@@ -412,15 +415,15 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>60</xdr:row>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
+      <xdr:row>62</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -436,8 +439,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="17571720" y="0"/>
-          <a:ext cx="0" cy="11079480"/>
+          <a:off x="18166080" y="0"/>
+          <a:ext cx="0" cy="11445240"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -470,7 +473,7 @@
     <xdr:to>
       <xdr:col>38</xdr:col>
       <xdr:colOff>15240</xdr:colOff>
-      <xdr:row>60</xdr:row>
+      <xdr:row>62</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -836,17 +839,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="4">
-        <v>127.59</v>
+        <v>182.39</v>
       </c>
       <c r="E3" s="3">
-        <v>45804</v>
+        <v>45920</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45804</v>
+        <v>45920</v>
       </c>
       <c r="G3" s="3">
-        <v>45880</v>
+        <v>45967</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -854,11 +857,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="5">
-        <f>2348.7</f>
-        <v>2348.6999999999998</v>
+        <f>2365.2</f>
+        <v>2365.1999999999998</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -867,7 +870,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>299670.63299999997</v>
+        <v>431388.82799999992</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -879,7 +882,7 @@
         <v>5230</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -890,7 +893,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -908,7 +911,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>294440.63299999997</v>
+        <v>426158.82799999992</v>
       </c>
     </row>
   </sheetData>
@@ -919,7 +922,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2658081B-9184-4400-8759-A5F68341B1D3}">
-  <dimension ref="B2:FJ58"/>
+  <dimension ref="B2:FJ73"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="24.5546875" bestFit="1" customWidth="1"/>
@@ -1151,16 +1154,15 @@
         <v>883.9</v>
       </c>
       <c r="AB3" s="8">
-        <f>X3*1.38</f>
-        <v>935.77799999999991</v>
+        <v>1003.7</v>
       </c>
       <c r="AC3" s="8">
-        <f>Y3*1.35</f>
-        <v>979.42500000000007</v>
+        <f>Y3*1.52</f>
+        <v>1102.76</v>
       </c>
       <c r="AD3" s="8">
-        <f>Z3*1.3</f>
-        <v>1075.75</v>
+        <f>Z3*1.47</f>
+        <v>1216.425</v>
       </c>
       <c r="AF3" s="8">
         <v>595.4</v>
@@ -1190,47 +1192,47 @@
       </c>
       <c r="AM3" s="8">
         <f>SUM(AA3:AD3)</f>
-        <v>3874.8530000000001</v>
+        <v>4206.7849999999999</v>
       </c>
       <c r="AN3" s="8">
         <f>AM3*1.3</f>
-        <v>5037.3089</v>
+        <v>5468.8204999999998</v>
       </c>
       <c r="AO3" s="8">
         <f>AN3*1.27</f>
-        <v>6397.3823030000003</v>
+        <v>6945.4020350000001</v>
       </c>
       <c r="AP3" s="8">
         <f>AO3*1.24</f>
-        <v>7932.75405572</v>
+        <v>8612.2985234000007</v>
       </c>
       <c r="AQ3" s="8">
         <f>AP3*1.18</f>
-        <v>9360.6497857495997</v>
+        <v>10162.512257612001</v>
       </c>
       <c r="AR3" s="8">
         <f>AQ3*1.14</f>
-        <v>10671.140755754543</v>
+        <v>11585.26397367768</v>
       </c>
       <c r="AS3" s="8">
         <f>AR3*1.1</f>
-        <v>11738.254831329998</v>
+        <v>12743.790371045448</v>
       </c>
       <c r="AT3" s="8">
-        <f>AS3*1.08</f>
-        <v>12677.315217836398</v>
+        <f t="shared" ref="AT3:AW3" si="0">AS3*1.1</f>
+        <v>14018.169408149994</v>
       </c>
       <c r="AU3" s="8">
-        <f>AT3*1.06</f>
-        <v>13437.954130906583</v>
+        <f t="shared" si="0"/>
+        <v>15419.986348964994</v>
       </c>
       <c r="AV3" s="8">
-        <f t="shared" ref="AV3" si="0">AU3*1.05</f>
-        <v>14109.851837451912</v>
+        <f t="shared" si="0"/>
+        <v>16961.984983861494</v>
       </c>
       <c r="AW3" s="8">
-        <f>AV3*1.04</f>
-        <v>14674.245910949989</v>
+        <f t="shared" si="0"/>
+        <v>18658.183482247645</v>
       </c>
     </row>
     <row r="4" spans="2:49" x14ac:dyDescent="0.3">
@@ -1315,16 +1317,15 @@
         <v>173</v>
       </c>
       <c r="AB4" s="5">
-        <f t="shared" ref="AB4:AD4" si="1">AB3-AB5</f>
-        <v>187.15559999999994</v>
+        <v>192.9</v>
       </c>
       <c r="AC4" s="5">
-        <f t="shared" si="1"/>
-        <v>195.88499999999999</v>
+        <f t="shared" ref="AC4:AD4" si="1">AC3-AC5</f>
+        <v>220.55199999999991</v>
       </c>
       <c r="AD4" s="5">
         <f t="shared" si="1"/>
-        <v>225.90749999999991</v>
+        <v>255.44924999999989</v>
       </c>
       <c r="AF4" s="5">
         <v>165.4</v>
@@ -1354,47 +1355,47 @@
       </c>
       <c r="AM4" s="5">
         <f>SUM(AA4:AD4)</f>
-        <v>781.94809999999984</v>
+        <v>841.90124999999978</v>
       </c>
       <c r="AN4" s="5">
         <f t="shared" ref="AN4:AR4" si="2">AN3-AN5</f>
-        <v>1007.4617799999996</v>
+        <v>1093.7640999999994</v>
       </c>
       <c r="AO4" s="5">
         <f t="shared" si="2"/>
-        <v>1279.4764605999999</v>
+        <v>1389.0804069999995</v>
       </c>
       <c r="AP4" s="5">
         <f t="shared" si="2"/>
-        <v>1586.5508111439995</v>
+        <v>1722.45970468</v>
       </c>
       <c r="AQ4" s="5">
         <f t="shared" si="2"/>
-        <v>1872.1299571499194</v>
+        <v>2032.5024515223995</v>
       </c>
       <c r="AR4" s="5">
         <f t="shared" si="2"/>
-        <v>2134.2281511509082</v>
+        <v>2317.0527947355349</v>
       </c>
       <c r="AS4" s="5">
         <f t="shared" ref="AS4:AW4" si="3">AS3-AS5</f>
-        <v>2347.6509662659992</v>
+        <v>2548.7580742090886</v>
       </c>
       <c r="AT4" s="5">
         <f t="shared" si="3"/>
-        <v>2535.4630435672789</v>
+        <v>2803.6338816299976</v>
       </c>
       <c r="AU4" s="5">
         <f t="shared" si="3"/>
-        <v>2687.5908261813165</v>
+        <v>3083.9972697929988</v>
       </c>
       <c r="AV4" s="5">
         <f t="shared" si="3"/>
-        <v>2821.9703674903812</v>
+        <v>3392.3969967722987</v>
       </c>
       <c r="AW4" s="5">
         <f t="shared" si="3"/>
-        <v>2934.849182189997</v>
+        <v>3731.6366964495282</v>
       </c>
     </row>
     <row r="5" spans="2:49" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1482,7 +1483,7 @@
         <v>499.79999999999995</v>
       </c>
       <c r="W5" s="8">
-        <f t="shared" ref="W5:AA5" si="11">W3-W4</f>
+        <f t="shared" ref="W5:AB5" si="11">W3-W4</f>
         <v>518</v>
       </c>
       <c r="X5" s="8">
@@ -1502,16 +1503,16 @@
         <v>710.9</v>
       </c>
       <c r="AB5" s="8">
-        <f t="shared" ref="AB5:AC5" si="12">AB3*0.8</f>
-        <v>748.62239999999997</v>
+        <f t="shared" si="11"/>
+        <v>810.80000000000007</v>
       </c>
       <c r="AC5" s="8">
-        <f t="shared" si="12"/>
-        <v>783.54000000000008</v>
+        <f t="shared" ref="AC5" si="12">AC3*0.8</f>
+        <v>882.20800000000008</v>
       </c>
       <c r="AD5" s="8">
         <f>AD3*0.79</f>
-        <v>849.84250000000009</v>
+        <v>960.97575000000006</v>
       </c>
       <c r="AF5" s="8">
         <f>AF3-AF4</f>
@@ -1543,47 +1544,47 @@
       </c>
       <c r="AM5" s="8">
         <f t="shared" si="13"/>
-        <v>3092.9049000000005</v>
+        <v>3364.88375</v>
       </c>
       <c r="AN5" s="8">
         <f>AN3*0.8</f>
-        <v>4029.8471200000004</v>
+        <v>4375.0564000000004</v>
       </c>
       <c r="AO5" s="8">
         <f t="shared" ref="AO5:AW5" si="14">AO3*0.8</f>
-        <v>5117.9058424000004</v>
+        <v>5556.3216280000006</v>
       </c>
       <c r="AP5" s="8">
         <f t="shared" si="14"/>
-        <v>6346.2032445760005</v>
+        <v>6889.8388187200007</v>
       </c>
       <c r="AQ5" s="8">
         <f t="shared" si="14"/>
-        <v>7488.5198285996803</v>
+        <v>8130.0098060896016</v>
       </c>
       <c r="AR5" s="8">
         <f t="shared" si="14"/>
-        <v>8536.9126046036345</v>
+        <v>9268.2111789421451</v>
       </c>
       <c r="AS5" s="8">
         <f t="shared" si="14"/>
-        <v>9390.6038650639985</v>
+        <v>10195.03229683636</v>
       </c>
       <c r="AT5" s="8">
         <f t="shared" si="14"/>
-        <v>10141.852174269119</v>
+        <v>11214.535526519996</v>
       </c>
       <c r="AU5" s="8">
         <f t="shared" si="14"/>
-        <v>10750.363304725266</v>
+        <v>12335.989079171995</v>
       </c>
       <c r="AV5" s="8">
         <f t="shared" si="14"/>
-        <v>11287.88146996153</v>
+        <v>13569.587987089195</v>
       </c>
       <c r="AW5" s="8">
         <f t="shared" si="14"/>
-        <v>11739.396728759992</v>
+        <v>14926.546785798117</v>
       </c>
     </row>
     <row r="6" spans="2:49" x14ac:dyDescent="0.3">
@@ -1668,16 +1669,15 @@
         <v>236.3</v>
       </c>
       <c r="AB6" s="5">
-        <f>AB3*0.26</f>
-        <v>243.30228</v>
+        <v>243.8</v>
       </c>
       <c r="AC6" s="5">
         <f>AC3*0.26</f>
-        <v>254.65050000000002</v>
+        <v>286.7176</v>
       </c>
       <c r="AD6" s="5">
         <f>AD3*0.31</f>
-        <v>333.48250000000002</v>
+        <v>377.09174999999999</v>
       </c>
       <c r="AF6" s="5">
         <v>461.8</v>
@@ -1707,47 +1707,47 @@
       </c>
       <c r="AM6" s="5">
         <f>SUM(AA6:AD6)</f>
-        <v>1067.7352800000001</v>
+        <v>1143.9093500000001</v>
       </c>
       <c r="AN6" s="5">
         <f>AN3*0.25</f>
-        <v>1259.327225</v>
+        <v>1367.205125</v>
       </c>
       <c r="AO6" s="5">
         <f>AO3*0.22</f>
-        <v>1407.42410666</v>
+        <v>1527.9884477000001</v>
       </c>
       <c r="AP6" s="5">
         <f>AP3*0.19</f>
-        <v>1507.2232705868</v>
+        <v>1636.3367194460002</v>
       </c>
       <c r="AQ6" s="5">
         <f>AQ3*0.17</f>
-        <v>1591.3104635774321</v>
+        <v>1727.6270837940403</v>
       </c>
       <c r="AR6" s="5">
         <f>AR3*0.16</f>
-        <v>1707.3825209207268</v>
+        <v>1853.6422357884289</v>
       </c>
       <c r="AS6" s="5">
         <f>AS3*0.15</f>
-        <v>1760.7382246994996</v>
+        <v>1911.5685556568171</v>
       </c>
       <c r="AT6" s="5">
         <f>AT3*0.15</f>
-        <v>1901.5972826754596</v>
+        <v>2102.7254112224991</v>
       </c>
       <c r="AU6" s="5">
         <f t="shared" ref="AU6:AW6" si="15">AU3*0.15</f>
-        <v>2015.6931196359874</v>
+        <v>2312.9979523447491</v>
       </c>
       <c r="AV6" s="5">
         <f t="shared" si="15"/>
-        <v>2116.4777756177868</v>
+        <v>2544.2977475792241</v>
       </c>
       <c r="AW6" s="5">
         <f t="shared" si="15"/>
-        <v>2201.1368866424982</v>
+        <v>2798.7275223371466</v>
       </c>
     </row>
     <row r="7" spans="2:49" x14ac:dyDescent="0.3">
@@ -1832,11 +1832,10 @@
         <v>134.9</v>
       </c>
       <c r="AB7" s="5">
-        <f t="shared" ref="AB7:AC7" si="16">X7*1.25</f>
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AC7" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" ref="AC7" si="16">Y7*1.25</f>
         <v>147</v>
       </c>
       <c r="AD7" s="5">
@@ -1871,47 +1870,47 @@
       </c>
       <c r="AM7" s="5">
         <f>SUM(AA7:AD7)</f>
-        <v>615.125</v>
+        <v>614.125</v>
       </c>
       <c r="AN7" s="5">
         <f>AM7*1.13</f>
-        <v>695.09124999999995</v>
+        <v>693.96124999999995</v>
       </c>
       <c r="AO7" s="5">
         <f>AN7*1.07</f>
-        <v>743.7476375</v>
+        <v>742.53853749999996</v>
       </c>
       <c r="AP7" s="5">
         <f>AO7*1.04</f>
-        <v>773.49754300000006</v>
+        <v>772.24007900000004</v>
       </c>
       <c r="AQ7" s="5">
         <f>AP7*1.03</f>
-        <v>796.70246929000007</v>
+        <v>795.40728137000008</v>
       </c>
       <c r="AR7" s="5">
         <f t="shared" ref="AR7:AR8" si="17">AQ7*1.02</f>
-        <v>812.63651867580006</v>
+        <v>811.3154269974001</v>
       </c>
       <c r="AS7" s="5">
         <f t="shared" ref="AS7:AS8" si="18">AR7*1.02</f>
-        <v>828.88924904931605</v>
+        <v>827.54173553734813</v>
       </c>
       <c r="AT7" s="5">
         <f t="shared" ref="AT7:AT8" si="19">AS7*1.02</f>
-        <v>845.46703403030233</v>
+        <v>844.09257024809506</v>
       </c>
       <c r="AU7" s="5">
         <f t="shared" ref="AU7:AU8" si="20">AT7*1.02</f>
-        <v>862.37637471090841</v>
+        <v>860.97442165305699</v>
       </c>
       <c r="AV7" s="5">
         <f t="shared" ref="AV7:AV8" si="21">AU7*1.02</f>
-        <v>879.62390220512657</v>
+        <v>878.19391008611819</v>
       </c>
       <c r="AW7" s="5">
         <f t="shared" ref="AW7:AW8" si="22">AV7*1.02</f>
-        <v>897.21638024922913</v>
+        <v>895.75778828784053</v>
       </c>
     </row>
     <row r="8" spans="2:49" x14ac:dyDescent="0.3">
@@ -1996,11 +1995,10 @@
         <v>163.6</v>
       </c>
       <c r="AB8" s="5">
-        <f t="shared" ref="AB8:AC8" si="23">X8*1.15</f>
-        <v>159.38999999999999</v>
+        <v>162.6</v>
       </c>
       <c r="AC8" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" ref="AC8" si="23">Y8*1.15</f>
         <v>159.50499999999997</v>
       </c>
       <c r="AD8" s="5">
@@ -2035,47 +2033,47 @@
       </c>
       <c r="AM8" s="5">
         <f>SUM(AA8:AD8)</f>
-        <v>682.80500000000006</v>
+        <v>686.01499999999987</v>
       </c>
       <c r="AN8" s="5">
         <f>AM8*1.09</f>
-        <v>744.25745000000018</v>
+        <v>747.75634999999988</v>
       </c>
       <c r="AO8" s="5">
         <f>AN8*1.05</f>
-        <v>781.47032250000018</v>
+        <v>785.14416749999987</v>
       </c>
       <c r="AP8" s="5">
         <f>AO8*1.04</f>
-        <v>812.72913540000025</v>
+        <v>816.54993419999994</v>
       </c>
       <c r="AQ8" s="5">
         <f>AP8*1.03</f>
-        <v>837.11100946200031</v>
+        <v>841.04643222599998</v>
       </c>
       <c r="AR8" s="5">
         <f t="shared" si="17"/>
-        <v>853.85322965124033</v>
+        <v>857.86736087051997</v>
       </c>
       <c r="AS8" s="5">
         <f t="shared" si="18"/>
-        <v>870.93029424426516</v>
+        <v>875.02470808793043</v>
       </c>
       <c r="AT8" s="5">
         <f t="shared" si="19"/>
-        <v>888.34890012915048</v>
+        <v>892.52520224968907</v>
       </c>
       <c r="AU8" s="5">
         <f t="shared" si="20"/>
-        <v>906.11587813173355</v>
+        <v>910.37570629468291</v>
       </c>
       <c r="AV8" s="5">
         <f t="shared" si="21"/>
-        <v>924.23819569436819</v>
+        <v>928.58322042057659</v>
       </c>
       <c r="AW8" s="5">
         <f t="shared" si="22"/>
-        <v>942.72295960825556</v>
+        <v>947.15488482898809</v>
       </c>
     </row>
     <row r="9" spans="2:49" x14ac:dyDescent="0.3">
@@ -2184,15 +2182,15 @@
       </c>
       <c r="AB9" s="5">
         <f t="shared" si="33"/>
-        <v>538.69227999999998</v>
+        <v>541.4</v>
       </c>
       <c r="AC9" s="5">
         <f t="shared" si="33"/>
-        <v>561.15549999999996</v>
+        <v>593.22259999999994</v>
       </c>
       <c r="AD9" s="5">
         <f t="shared" si="33"/>
-        <v>731.01749999999993</v>
+        <v>774.6267499999999</v>
       </c>
       <c r="AF9" s="5">
         <f>AF6+AF7+AF8</f>
@@ -2224,47 +2222,47 @@
       </c>
       <c r="AM9" s="5">
         <f t="shared" si="34"/>
-        <v>2365.6652800000002</v>
+        <v>2444.0493500000002</v>
       </c>
       <c r="AN9" s="5">
         <f t="shared" si="34"/>
-        <v>2698.675925</v>
+        <v>2808.9227249999994</v>
       </c>
       <c r="AO9" s="5">
         <f t="shared" si="34"/>
-        <v>2932.6420666600002</v>
+        <v>3055.6711526999998</v>
       </c>
       <c r="AP9" s="5">
         <f t="shared" si="34"/>
-        <v>3093.4499489868003</v>
+        <v>3225.1267326460002</v>
       </c>
       <c r="AQ9" s="5">
         <f t="shared" si="34"/>
-        <v>3225.1239423294323</v>
+        <v>3364.0807973900405</v>
       </c>
       <c r="AR9" s="5">
         <f t="shared" si="34"/>
-        <v>3373.8722692477672</v>
+        <v>3522.825023656349</v>
       </c>
       <c r="AS9" s="5">
         <f t="shared" ref="AS9:AW9" si="35">AS6+AS7+AS8</f>
-        <v>3460.5577679930807</v>
+        <v>3614.1349992820956</v>
       </c>
       <c r="AT9" s="5">
         <f t="shared" si="35"/>
-        <v>3635.4132168349124</v>
+        <v>3839.3431837202834</v>
       </c>
       <c r="AU9" s="5">
         <f t="shared" si="35"/>
-        <v>3784.1853724786292</v>
+        <v>4084.3480802924892</v>
       </c>
       <c r="AV9" s="5">
         <f t="shared" si="35"/>
-        <v>3920.3398735172814</v>
+        <v>4351.0748780859185</v>
       </c>
       <c r="AW9" s="5">
         <f t="shared" si="35"/>
-        <v>4041.076226499983</v>
+        <v>4641.6401954539751</v>
       </c>
     </row>
     <row r="10" spans="2:49" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2373,15 +2371,15 @@
       </c>
       <c r="AB10" s="8">
         <f t="shared" si="45"/>
-        <v>209.93011999999999</v>
+        <v>269.40000000000009</v>
       </c>
       <c r="AC10" s="8">
         <f t="shared" si="45"/>
-        <v>222.38450000000012</v>
+        <v>288.98540000000014</v>
       </c>
       <c r="AD10" s="8">
         <f t="shared" si="45"/>
-        <v>118.82500000000016</v>
+        <v>186.34900000000016</v>
       </c>
       <c r="AF10" s="8">
         <f>AF5-AF9</f>
@@ -2413,47 +2411,47 @@
       </c>
       <c r="AM10" s="8">
         <f t="shared" si="46"/>
-        <v>727.23962000000029</v>
+        <v>920.83439999999973</v>
       </c>
       <c r="AN10" s="8">
         <f t="shared" si="46"/>
-        <v>1331.1711950000004</v>
+        <v>1566.1336750000009</v>
       </c>
       <c r="AO10" s="8">
         <f t="shared" si="46"/>
-        <v>2185.2637757400003</v>
+        <v>2500.6504753000008</v>
       </c>
       <c r="AP10" s="8">
         <f t="shared" si="46"/>
-        <v>3252.7532955892002</v>
+        <v>3664.7120860740006</v>
       </c>
       <c r="AQ10" s="8">
         <f t="shared" si="46"/>
-        <v>4263.3958862702475</v>
+        <v>4765.9290086995607</v>
       </c>
       <c r="AR10" s="8">
         <f t="shared" si="46"/>
-        <v>5163.0403353558668</v>
+        <v>5745.3861552857961</v>
       </c>
       <c r="AS10" s="8">
         <f t="shared" ref="AS10:AW10" si="47">AS5-AS9</f>
-        <v>5930.0460970709173</v>
+        <v>6580.8972975542638</v>
       </c>
       <c r="AT10" s="8">
         <f t="shared" si="47"/>
-        <v>6506.4389574342067</v>
+        <v>7375.1923427997126</v>
       </c>
       <c r="AU10" s="8">
         <f t="shared" si="47"/>
-        <v>6966.1779322466373</v>
+        <v>8251.6409988795058</v>
       </c>
       <c r="AV10" s="8">
         <f t="shared" si="47"/>
-        <v>7367.5415964442491</v>
+        <v>9218.5131090032773</v>
       </c>
       <c r="AW10" s="8">
         <f t="shared" si="47"/>
-        <v>7698.3205022600087</v>
+        <v>10284.906590344141</v>
       </c>
     </row>
     <row r="11" spans="2:49" x14ac:dyDescent="0.3">
@@ -2538,11 +2536,10 @@
         <v>-50.4</v>
       </c>
       <c r="AB11" s="5">
-        <f t="shared" ref="AB11:AD11" si="48">X11*1.2</f>
-        <v>-55.92</v>
+        <v>-56.3</v>
       </c>
       <c r="AC11" s="5">
-        <f t="shared" si="48"/>
+        <f t="shared" ref="AC11:AD11" si="48">Y11*1.2</f>
         <v>-62.519999999999996</v>
       </c>
       <c r="AD11" s="5">
@@ -2577,47 +2574,47 @@
       </c>
       <c r="AM11" s="5">
         <f>SUM(AA11:AD11)</f>
-        <v>-234.47999999999996</v>
+        <v>-234.85999999999996</v>
       </c>
       <c r="AN11" s="5">
         <f>AM11*1.15</f>
-        <v>-269.65199999999993</v>
+        <v>-270.08899999999994</v>
       </c>
       <c r="AO11" s="5">
         <f t="shared" ref="AO11:AW11" si="49">AN11*1.15</f>
-        <v>-310.0997999999999</v>
+        <v>-310.60234999999989</v>
       </c>
       <c r="AP11" s="5">
         <f t="shared" si="49"/>
-        <v>-356.61476999999985</v>
+        <v>-357.19270249999983</v>
       </c>
       <c r="AQ11" s="5">
         <f t="shared" si="49"/>
-        <v>-410.10698549999978</v>
+        <v>-410.77160787499975</v>
       </c>
       <c r="AR11" s="5">
         <f t="shared" si="49"/>
-        <v>-471.62303332499971</v>
+        <v>-472.38734905624966</v>
       </c>
       <c r="AS11" s="5">
         <f t="shared" si="49"/>
-        <v>-542.36648832374965</v>
+        <v>-543.24545141468707</v>
       </c>
       <c r="AT11" s="5">
         <f t="shared" si="49"/>
-        <v>-623.72146157231202</v>
+        <v>-624.73226912689006</v>
       </c>
       <c r="AU11" s="5">
         <f t="shared" si="49"/>
-        <v>-717.27968080815879</v>
+        <v>-718.44210949592355</v>
       </c>
       <c r="AV11" s="5">
         <f t="shared" si="49"/>
-        <v>-824.87163292938249</v>
+        <v>-826.20842592031204</v>
       </c>
       <c r="AW11" s="5">
         <f t="shared" si="49"/>
-        <v>-948.60237786878974</v>
+        <v>-950.13968980835875</v>
       </c>
     </row>
     <row r="12" spans="2:49" x14ac:dyDescent="0.3">
@@ -3024,7 +3021,7 @@
         <v>3.2</v>
       </c>
       <c r="AB14" s="5">
-        <v>0</v>
+        <v>-6.6</v>
       </c>
       <c r="AC14" s="5">
         <v>0</v>
@@ -3060,7 +3057,7 @@
       </c>
       <c r="AM14" s="5">
         <f>SUM(AA14:AD14)</f>
-        <v>3.2</v>
+        <v>-3.3999999999999995</v>
       </c>
       <c r="AN14" s="5">
         <v>0</v>
@@ -3199,15 +3196,15 @@
       </c>
       <c r="AB15" s="8">
         <f t="shared" ref="AB15:AD15" si="69">AB10-AB11-AB12-AB13-AB14</f>
-        <v>265.85012</v>
+        <v>332.30000000000013</v>
       </c>
       <c r="AC15" s="8">
         <f t="shared" si="69"/>
-        <v>284.9045000000001</v>
+        <v>351.50540000000012</v>
       </c>
       <c r="AD15" s="8">
         <f t="shared" si="69"/>
-        <v>184.46500000000015</v>
+        <v>251.98900000000015</v>
       </c>
       <c r="AF15" s="8">
         <f>AF10-AF11-AF12-AF13-AF14</f>
@@ -3239,47 +3236,47 @@
       </c>
       <c r="AM15" s="8">
         <f t="shared" si="70"/>
-        <v>958.51962000000026</v>
+        <v>1159.0943999999997</v>
       </c>
       <c r="AN15" s="8">
         <f t="shared" si="70"/>
-        <v>1600.8231950000004</v>
+        <v>1836.2226750000009</v>
       </c>
       <c r="AO15" s="8">
         <f t="shared" si="70"/>
-        <v>2495.3635757400002</v>
+        <v>2811.2528253000009</v>
       </c>
       <c r="AP15" s="8">
         <f t="shared" si="70"/>
-        <v>3609.3680655891999</v>
+        <v>4021.9047885740006</v>
       </c>
       <c r="AQ15" s="8">
         <f t="shared" si="70"/>
-        <v>4673.5028717702471</v>
+        <v>5176.7006165745606</v>
       </c>
       <c r="AR15" s="8">
         <f t="shared" si="70"/>
-        <v>5634.6633686808664</v>
+        <v>6217.7735043420462</v>
       </c>
       <c r="AS15" s="8">
         <f t="shared" ref="AS15:AW15" si="71">AS10-AS11-AS12-AS13-AS14</f>
-        <v>6472.4125853946671</v>
+        <v>7124.1427489689504</v>
       </c>
       <c r="AT15" s="8">
         <f t="shared" si="71"/>
-        <v>7130.1604190065191</v>
+        <v>7999.9246119266027</v>
       </c>
       <c r="AU15" s="8">
         <f t="shared" si="71"/>
-        <v>7683.4576130547957</v>
+        <v>8970.0831083754292</v>
       </c>
       <c r="AV15" s="8">
         <f t="shared" si="71"/>
-        <v>8192.4132293736311</v>
+        <v>10044.721534923588</v>
       </c>
       <c r="AW15" s="8">
         <f t="shared" si="71"/>
-        <v>8646.9228801287991</v>
+        <v>11235.046280152499</v>
       </c>
     </row>
     <row r="16" spans="2:49" x14ac:dyDescent="0.3">
@@ -3364,16 +3361,15 @@
         <v>5.6</v>
       </c>
       <c r="AB16" s="5">
-        <f t="shared" ref="AB16:AD16" si="72">AB15*0.04</f>
-        <v>10.6340048</v>
+        <v>3.6</v>
       </c>
       <c r="AC16" s="5">
-        <f t="shared" si="72"/>
-        <v>11.396180000000005</v>
+        <f t="shared" ref="AC16:AD16" si="72">AC15*0.04</f>
+        <v>14.060216000000006</v>
       </c>
       <c r="AD16" s="5">
         <f t="shared" si="72"/>
-        <v>7.3786000000000058</v>
+        <v>10.079560000000006</v>
       </c>
       <c r="AF16" s="5">
         <v>9.1</v>
@@ -3403,47 +3399,47 @@
       </c>
       <c r="AM16" s="5">
         <f>SUM(AA16:AD16)</f>
-        <v>35.008784800000015</v>
+        <v>33.339776000000015</v>
       </c>
       <c r="AN16" s="5">
         <f t="shared" ref="AN16:AQ16" si="73">AN15*0.1</f>
-        <v>160.08231950000004</v>
+        <v>183.62226750000011</v>
       </c>
       <c r="AO16" s="5">
         <f t="shared" si="73"/>
-        <v>249.53635757400002</v>
+        <v>281.12528253000011</v>
       </c>
       <c r="AP16" s="5">
         <f t="shared" si="73"/>
-        <v>360.93680655892001</v>
+        <v>402.19047885740008</v>
       </c>
       <c r="AQ16" s="5">
         <f t="shared" si="73"/>
-        <v>467.35028717702471</v>
+        <v>517.67006165745613</v>
       </c>
       <c r="AR16" s="5">
         <f>AR15*0.15</f>
-        <v>845.19950530212998</v>
+        <v>932.66602565130688</v>
       </c>
       <c r="AS16" s="5">
         <f t="shared" ref="AS16:AW16" si="74">AS15*0.15</f>
-        <v>970.86188780919997</v>
+        <v>1068.6214123453426</v>
       </c>
       <c r="AT16" s="5">
         <f t="shared" si="74"/>
-        <v>1069.5240628509778</v>
+        <v>1199.9886917889903</v>
       </c>
       <c r="AU16" s="5">
         <f t="shared" si="74"/>
-        <v>1152.5186419582194</v>
+        <v>1345.5124662563144</v>
       </c>
       <c r="AV16" s="5">
         <f t="shared" si="74"/>
-        <v>1228.8619844060447</v>
+        <v>1506.7082302385381</v>
       </c>
       <c r="AW16" s="5">
         <f t="shared" si="74"/>
-        <v>1297.0384320193198</v>
+        <v>1685.2569420228749</v>
       </c>
     </row>
     <row r="17" spans="2:166" x14ac:dyDescent="0.3">
@@ -3482,16 +3478,15 @@
         <v>3.7</v>
       </c>
       <c r="AB17" s="5">
-        <f t="shared" ref="AB17:AD17" si="75">AB15*0.01</f>
-        <v>2.6585011999999999</v>
+        <v>1.8</v>
       </c>
       <c r="AC17" s="5">
-        <f t="shared" si="75"/>
-        <v>2.8490450000000012</v>
+        <f t="shared" ref="AC17:AD17" si="75">AC15*0.01</f>
+        <v>3.5150540000000015</v>
       </c>
       <c r="AD17" s="5">
         <f t="shared" si="75"/>
-        <v>1.8446500000000015</v>
+        <v>2.5198900000000015</v>
       </c>
       <c r="AF17" s="5"/>
       <c r="AG17" s="5"/>
@@ -3505,47 +3500,47 @@
       </c>
       <c r="AM17" s="5">
         <f>SUM(AA17:AD17)</f>
-        <v>11.052196200000003</v>
+        <v>11.534944000000003</v>
       </c>
       <c r="AN17" s="5">
         <f t="shared" ref="AN17:AW17" si="76">AN15*0.02</f>
-        <v>32.016463900000005</v>
+        <v>36.724453500000017</v>
       </c>
       <c r="AO17" s="5">
         <f t="shared" si="76"/>
-        <v>49.907271514800009</v>
+        <v>56.225056506000023</v>
       </c>
       <c r="AP17" s="5">
         <f t="shared" si="76"/>
-        <v>72.187361311784002</v>
+        <v>80.438095771480008</v>
       </c>
       <c r="AQ17" s="5">
         <f t="shared" si="76"/>
-        <v>93.470057435404939</v>
+        <v>103.53401233149121</v>
       </c>
       <c r="AR17" s="5">
         <f t="shared" si="76"/>
-        <v>112.69326737361733</v>
+        <v>124.35547008684092</v>
       </c>
       <c r="AS17" s="5">
         <f t="shared" si="76"/>
-        <v>129.44825170789335</v>
+        <v>142.482854979379</v>
       </c>
       <c r="AT17" s="5">
         <f t="shared" si="76"/>
-        <v>142.60320838013038</v>
+        <v>159.99849223853207</v>
       </c>
       <c r="AU17" s="5">
         <f t="shared" si="76"/>
-        <v>153.66915226109592</v>
+        <v>179.40166216750859</v>
       </c>
       <c r="AV17" s="5">
         <f t="shared" si="76"/>
-        <v>163.84826458747261</v>
+        <v>200.89443069847178</v>
       </c>
       <c r="AW17" s="5">
         <f t="shared" si="76"/>
-        <v>172.93845760257599</v>
+        <v>224.70092560305</v>
       </c>
     </row>
     <row r="18" spans="2:166" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -3654,15 +3649,15 @@
       </c>
       <c r="AB18" s="8">
         <f t="shared" si="86"/>
-        <v>252.557614</v>
+        <v>326.90000000000009</v>
       </c>
       <c r="AC18" s="8">
         <f t="shared" si="86"/>
-        <v>270.65927500000009</v>
+        <v>333.93013000000008</v>
       </c>
       <c r="AD18" s="8">
         <f t="shared" si="86"/>
-        <v>175.24175000000014</v>
+        <v>239.38955000000013</v>
       </c>
       <c r="AF18" s="8">
         <f>AF15-AF16</f>
@@ -3694,515 +3689,515 @@
       </c>
       <c r="AM18" s="8">
         <f t="shared" si="90"/>
-        <v>912.45863900000018</v>
+        <v>1114.2196799999997</v>
       </c>
       <c r="AN18" s="8">
         <f t="shared" si="90"/>
-        <v>1408.7244116000004</v>
+        <v>1615.8759540000008</v>
       </c>
       <c r="AO18" s="8">
         <f t="shared" si="90"/>
-        <v>2195.9199466512005</v>
+        <v>2473.9024862640008</v>
       </c>
       <c r="AP18" s="8">
         <f t="shared" si="90"/>
-        <v>3176.2438977184956</v>
+        <v>3539.2762139451202</v>
       </c>
       <c r="AQ18" s="8">
         <f t="shared" si="90"/>
-        <v>4112.6825271578182</v>
+        <v>4555.4965425856135</v>
       </c>
       <c r="AR18" s="8">
         <f t="shared" si="90"/>
-        <v>4676.7705960051189</v>
+        <v>5160.7520086038985</v>
       </c>
       <c r="AS18" s="8">
         <f t="shared" si="90"/>
-        <v>5372.1024458775737</v>
+        <v>5913.0384816442283</v>
       </c>
       <c r="AT18" s="8">
         <f t="shared" si="90"/>
-        <v>5918.0331477754107</v>
+        <v>6639.9374278990799</v>
       </c>
       <c r="AU18" s="8">
         <f t="shared" si="90"/>
-        <v>6377.2698188354798</v>
+        <v>7445.1689799516071</v>
       </c>
       <c r="AV18" s="8">
         <f t="shared" si="90"/>
-        <v>6799.7029803801133</v>
+        <v>8337.1188739865775</v>
       </c>
       <c r="AW18" s="8">
         <f t="shared" si="90"/>
-        <v>7176.9459905069034</v>
+        <v>9325.0884125265729</v>
       </c>
       <c r="AX18" s="1">
         <f t="shared" ref="AX18:CC18" si="91">AW18*(1+$AZ$25)</f>
-        <v>7105.1765306018342</v>
+        <v>9231.8375284013073</v>
       </c>
       <c r="AY18" s="1">
         <f t="shared" si="91"/>
-        <v>7034.1247652958155</v>
+        <v>9139.519153117295</v>
       </c>
       <c r="AZ18" s="1">
         <f t="shared" si="91"/>
-        <v>6963.7835176428571</v>
+        <v>9048.1239615861214</v>
       </c>
       <c r="BA18" s="1">
         <f t="shared" si="91"/>
-        <v>6894.1456824664283</v>
+        <v>8957.64272197026</v>
       </c>
       <c r="BB18" s="1">
         <f t="shared" si="91"/>
-        <v>6825.2042256417635</v>
+        <v>8868.0662947505571</v>
       </c>
       <c r="BC18" s="1">
         <f t="shared" si="91"/>
-        <v>6756.952183385346</v>
+        <v>8779.3856318030521</v>
       </c>
       <c r="BD18" s="1">
         <f t="shared" si="91"/>
-        <v>6689.3826615514927</v>
+        <v>8691.5917754850216</v>
       </c>
       <c r="BE18" s="1">
         <f t="shared" si="91"/>
-        <v>6622.488834935978</v>
+        <v>8604.6758577301716</v>
       </c>
       <c r="BF18" s="1">
         <f t="shared" si="91"/>
-        <v>6556.2639465866187</v>
+        <v>8518.6290991528695</v>
       </c>
       <c r="BG18" s="1">
         <f t="shared" si="91"/>
-        <v>6490.7013071207521</v>
+        <v>8433.4428081613405</v>
       </c>
       <c r="BH18" s="1">
         <f t="shared" si="91"/>
-        <v>6425.7942940495441</v>
+        <v>8349.1083800797278</v>
       </c>
       <c r="BI18" s="1">
         <f t="shared" si="91"/>
-        <v>6361.5363511090482</v>
+        <v>8265.6172962789296</v>
       </c>
       <c r="BJ18" s="1">
         <f t="shared" si="91"/>
-        <v>6297.9209875979577</v>
+        <v>8182.9611233161404</v>
       </c>
       <c r="BK18" s="1">
         <f t="shared" si="91"/>
-        <v>6234.9417777219778</v>
+        <v>8101.1315120829786</v>
       </c>
       <c r="BL18" s="1">
         <f t="shared" si="91"/>
-        <v>6172.5923599447578</v>
+        <v>8020.1201969621488</v>
       </c>
       <c r="BM18" s="1">
         <f t="shared" si="91"/>
-        <v>6110.8664363453099</v>
+        <v>7939.9189949925276</v>
       </c>
       <c r="BN18" s="1">
         <f t="shared" si="91"/>
-        <v>6049.7577719818564</v>
+        <v>7860.5198050426025</v>
       </c>
       <c r="BO18" s="1">
         <f t="shared" si="91"/>
-        <v>5989.2601942620377</v>
+        <v>7781.9146069921762</v>
       </c>
       <c r="BP18" s="1">
         <f t="shared" si="91"/>
-        <v>5929.3675923194169</v>
+        <v>7704.0954609222545</v>
       </c>
       <c r="BQ18" s="1">
         <f t="shared" si="91"/>
-        <v>5870.0739163962226</v>
+        <v>7627.0545063130321</v>
       </c>
       <c r="BR18" s="1">
         <f t="shared" si="91"/>
-        <v>5811.3731772322599</v>
+        <v>7550.7839612499019</v>
       </c>
       <c r="BS18" s="1">
         <f t="shared" si="91"/>
-        <v>5753.2594454599375</v>
+        <v>7475.2761216374029</v>
       </c>
       <c r="BT18" s="1">
         <f t="shared" si="91"/>
-        <v>5695.7268510053382</v>
+        <v>7400.5233604210289</v>
       </c>
       <c r="BU18" s="1">
         <f t="shared" si="91"/>
-        <v>5638.7695824952843</v>
+        <v>7326.5181268168189</v>
       </c>
       <c r="BV18" s="1">
         <f t="shared" si="91"/>
-        <v>5582.3818866703314</v>
+        <v>7253.252945548651</v>
       </c>
       <c r="BW18" s="1">
         <f t="shared" si="91"/>
-        <v>5526.5580678036276</v>
+        <v>7180.7204160931642</v>
       </c>
       <c r="BX18" s="1">
         <f t="shared" si="91"/>
-        <v>5471.2924871255909</v>
+        <v>7108.9132119322321</v>
       </c>
       <c r="BY18" s="1">
         <f t="shared" si="91"/>
-        <v>5416.5795622543346</v>
+        <v>7037.82407981291</v>
       </c>
       <c r="BZ18" s="1">
         <f t="shared" si="91"/>
-        <v>5362.4137666317911</v>
+        <v>6967.4458390147811</v>
       </c>
       <c r="CA18" s="1">
         <f t="shared" si="91"/>
-        <v>5308.7896289654727</v>
+        <v>6897.7713806246329</v>
       </c>
       <c r="CB18" s="1">
         <f t="shared" si="91"/>
-        <v>5255.7017326758178</v>
+        <v>6828.7936668183866</v>
       </c>
       <c r="CC18" s="1">
         <f t="shared" si="91"/>
-        <v>5203.1447153490599</v>
+        <v>6760.5057301502029</v>
       </c>
       <c r="CD18" s="1">
         <f t="shared" ref="CD18:DI18" si="92">CC18*(1+$AZ$25)</f>
-        <v>5151.1132681955696</v>
+        <v>6692.9006728487011</v>
       </c>
       <c r="CE18" s="1">
         <f t="shared" si="92"/>
-        <v>5099.6021355136136</v>
+        <v>6625.9716661202137</v>
       </c>
       <c r="CF18" s="1">
         <f t="shared" si="92"/>
-        <v>5048.6061141584778</v>
+        <v>6559.7119494590115</v>
       </c>
       <c r="CG18" s="1">
         <f t="shared" si="92"/>
-        <v>4998.1200530168926</v>
+        <v>6494.114829964421</v>
       </c>
       <c r="CH18" s="1">
         <f t="shared" si="92"/>
-        <v>4948.1388524867234</v>
+        <v>6429.1736816647772</v>
       </c>
       <c r="CI18" s="1">
         <f t="shared" si="92"/>
-        <v>4898.6574639618557</v>
+        <v>6364.881944848129</v>
       </c>
       <c r="CJ18" s="1">
         <f t="shared" si="92"/>
-        <v>4849.6708893222367</v>
+        <v>6301.2331253996481</v>
       </c>
       <c r="CK18" s="1">
         <f t="shared" si="92"/>
-        <v>4801.1741804290141</v>
+        <v>6238.2207941456518</v>
       </c>
       <c r="CL18" s="1">
         <f t="shared" si="92"/>
-        <v>4753.162438624724</v>
+        <v>6175.8385862041951</v>
       </c>
       <c r="CM18" s="1">
         <f t="shared" si="92"/>
-        <v>4705.6308142384769</v>
+        <v>6114.0802003421531</v>
       </c>
       <c r="CN18" s="1">
         <f t="shared" si="92"/>
-        <v>4658.5745060960917</v>
+        <v>6052.9393983387317</v>
       </c>
       <c r="CO18" s="1">
         <f t="shared" si="92"/>
-        <v>4611.9887610351307</v>
+        <v>5992.4100043553444</v>
       </c>
       <c r="CP18" s="1">
         <f t="shared" si="92"/>
-        <v>4565.8688734247789</v>
+        <v>5932.4859043117913</v>
       </c>
       <c r="CQ18" s="1">
         <f t="shared" si="92"/>
-        <v>4520.2101846905307</v>
+        <v>5873.1610452686737</v>
       </c>
       <c r="CR18" s="1">
         <f t="shared" si="92"/>
-        <v>4475.0080828436257</v>
+        <v>5814.4294348159865</v>
       </c>
       <c r="CS18" s="1">
         <f t="shared" si="92"/>
-        <v>4430.258002015189</v>
+        <v>5756.2851404678267</v>
       </c>
       <c r="CT18" s="1">
         <f t="shared" si="92"/>
-        <v>4385.9554219950369</v>
+        <v>5698.7222890631483</v>
       </c>
       <c r="CU18" s="1">
         <f t="shared" si="92"/>
-        <v>4342.0958677750868</v>
+        <v>5641.7350661725168</v>
       </c>
       <c r="CV18" s="1">
         <f t="shared" si="92"/>
-        <v>4298.6749090973362</v>
+        <v>5585.3177155107915</v>
       </c>
       <c r="CW18" s="1">
         <f t="shared" si="92"/>
-        <v>4255.6881600063625</v>
+        <v>5529.4645383556835</v>
       </c>
       <c r="CX18" s="1">
         <f t="shared" si="92"/>
-        <v>4213.1312784062984</v>
+        <v>5474.1698929721269</v>
       </c>
       <c r="CY18" s="1">
         <f t="shared" si="92"/>
-        <v>4170.9999656222353</v>
+        <v>5419.4281940424053</v>
       </c>
       <c r="CZ18" s="1">
         <f t="shared" si="92"/>
-        <v>4129.2899659660134</v>
+        <v>5365.2339121019813</v>
       </c>
       <c r="DA18" s="1">
         <f t="shared" si="92"/>
-        <v>4087.9970663063532</v>
+        <v>5311.581572980961</v>
       </c>
       <c r="DB18" s="1">
         <f t="shared" si="92"/>
-        <v>4047.1170956432898</v>
+        <v>5258.4657572511514</v>
       </c>
       <c r="DC18" s="1">
         <f t="shared" si="92"/>
-        <v>4006.6459246868567</v>
+        <v>5205.8810996786397</v>
       </c>
       <c r="DD18" s="1">
         <f t="shared" si="92"/>
-        <v>3966.5794654399879</v>
+        <v>5153.822288681853</v>
       </c>
       <c r="DE18" s="1">
         <f t="shared" si="92"/>
-        <v>3926.9136707855878</v>
+        <v>5102.2840657950346</v>
       </c>
       <c r="DF18" s="1">
         <f t="shared" si="92"/>
-        <v>3887.6445340777318</v>
+        <v>5051.2612251370838</v>
       </c>
       <c r="DG18" s="1">
         <f t="shared" si="92"/>
-        <v>3848.7680887369543</v>
+        <v>5000.7486128857126</v>
       </c>
       <c r="DH18" s="1">
         <f t="shared" si="92"/>
-        <v>3810.2804078495847</v>
+        <v>4950.7411267568559</v>
       </c>
       <c r="DI18" s="1">
         <f t="shared" si="92"/>
-        <v>3772.1776037710888</v>
+        <v>4901.2337154892875</v>
       </c>
       <c r="DJ18" s="1">
         <f t="shared" ref="DJ18:EO18" si="93">DI18*(1+$AZ$25)</f>
-        <v>3734.4558277333781</v>
+        <v>4852.221378334395</v>
       </c>
       <c r="DK18" s="1">
         <f t="shared" si="93"/>
-        <v>3697.1112694560443</v>
+        <v>4803.6991645510507</v>
       </c>
       <c r="DL18" s="1">
         <f t="shared" si="93"/>
-        <v>3660.1401567614839</v>
+        <v>4755.6621729055405</v>
       </c>
       <c r="DM18" s="1">
         <f t="shared" si="93"/>
-        <v>3623.5387551938688</v>
+        <v>4708.1055511764853</v>
       </c>
       <c r="DN18" s="1">
         <f t="shared" si="93"/>
-        <v>3587.30336764193</v>
+        <v>4661.0244956647202</v>
       </c>
       <c r="DO18" s="1">
         <f t="shared" si="93"/>
-        <v>3551.4303339655107</v>
+        <v>4614.4142507080733</v>
       </c>
       <c r="DP18" s="1">
         <f t="shared" si="93"/>
-        <v>3515.9160306258555</v>
+        <v>4568.2701082009926</v>
       </c>
       <c r="DQ18" s="1">
         <f t="shared" si="93"/>
-        <v>3480.7568703195971</v>
+        <v>4522.5874071189828</v>
       </c>
       <c r="DR18" s="1">
         <f t="shared" si="93"/>
-        <v>3445.949301616401</v>
+        <v>4477.3615330477933</v>
       </c>
       <c r="DS18" s="1">
         <f t="shared" si="93"/>
-        <v>3411.4898086002372</v>
+        <v>4432.5879177173156</v>
       </c>
       <c r="DT18" s="1">
         <f t="shared" si="93"/>
-        <v>3377.3749105142347</v>
+        <v>4388.2620385401424</v>
       </c>
       <c r="DU18" s="1">
         <f t="shared" si="93"/>
-        <v>3343.6011614090921</v>
+        <v>4344.379418154741</v>
       </c>
       <c r="DV18" s="1">
         <f t="shared" si="93"/>
-        <v>3310.1651497950011</v>
+        <v>4300.9356239731933</v>
       </c>
       <c r="DW18" s="1">
         <f t="shared" si="93"/>
-        <v>3277.063498297051</v>
+        <v>4257.9262677334609</v>
       </c>
       <c r="DX18" s="1">
         <f t="shared" si="93"/>
-        <v>3244.2928633140805</v>
+        <v>4215.3470050561264</v>
       </c>
       <c r="DY18" s="1">
         <f t="shared" si="93"/>
-        <v>3211.8499346809394</v>
+        <v>4173.1935350055646</v>
       </c>
       <c r="DZ18" s="1">
         <f t="shared" si="93"/>
-        <v>3179.7314353341299</v>
+        <v>4131.4615996555085</v>
       </c>
       <c r="EA18" s="1">
         <f t="shared" si="93"/>
-        <v>3147.9341209807885</v>
+        <v>4090.1469836589536</v>
       </c>
       <c r="EB18" s="1">
         <f t="shared" si="93"/>
-        <v>3116.4547797709806</v>
+        <v>4049.245513822364</v>
       </c>
       <c r="EC18" s="1">
         <f t="shared" si="93"/>
-        <v>3085.2902319732707</v>
+        <v>4008.7530586841403</v>
       </c>
       <c r="ED18" s="1">
         <f t="shared" si="93"/>
-        <v>3054.4373296535377</v>
+        <v>3968.6655280972991</v>
       </c>
       <c r="EE18" s="1">
         <f t="shared" si="93"/>
-        <v>3023.8929563570023</v>
+        <v>3928.9788728163262</v>
       </c>
       <c r="EF18" s="1">
         <f t="shared" si="93"/>
-        <v>2993.6540267934324</v>
+        <v>3889.6890840881629</v>
       </c>
       <c r="EG18" s="1">
         <f t="shared" si="93"/>
-        <v>2963.7174865254979</v>
+        <v>3850.7921932472814</v>
       </c>
       <c r="EH18" s="1">
         <f t="shared" si="93"/>
-        <v>2934.0803116602428</v>
+        <v>3812.2842713148084</v>
       </c>
       <c r="EI18" s="1">
         <f t="shared" si="93"/>
-        <v>2904.7395085436406</v>
+        <v>3774.1614286016602</v>
       </c>
       <c r="EJ18" s="1">
         <f t="shared" si="93"/>
-        <v>2875.6921134582039</v>
+        <v>3736.4198143156436</v>
       </c>
       <c r="EK18" s="1">
         <f t="shared" si="93"/>
-        <v>2846.9351923236218</v>
+        <v>3699.0556161724871</v>
       </c>
       <c r="EL18" s="1">
         <f t="shared" si="93"/>
-        <v>2818.4658404003853</v>
+        <v>3662.0650600107624</v>
       </c>
       <c r="EM18" s="1">
         <f t="shared" si="93"/>
-        <v>2790.2811819963813</v>
+        <v>3625.4444094106548</v>
       </c>
       <c r="EN18" s="1">
         <f t="shared" si="93"/>
-        <v>2762.3783701764173</v>
+        <v>3589.1899653165483</v>
       </c>
       <c r="EO18" s="1">
         <f t="shared" si="93"/>
-        <v>2734.754586474653</v>
+        <v>3553.2980656633827</v>
       </c>
       <c r="EP18" s="1">
         <f t="shared" ref="EP18:FJ18" si="94">EO18*(1+$AZ$25)</f>
-        <v>2707.4070406099063</v>
+        <v>3517.7650850067489</v>
       </c>
       <c r="EQ18" s="1">
         <f t="shared" si="94"/>
-        <v>2680.3329702038072</v>
+        <v>3482.5874341566814</v>
       </c>
       <c r="ER18" s="1">
         <f t="shared" si="94"/>
-        <v>2653.5296405017693</v>
+        <v>3447.7615598151147</v>
       </c>
       <c r="ES18" s="1">
         <f t="shared" si="94"/>
-        <v>2626.9943440967518</v>
+        <v>3413.2839442169634</v>
       </c>
       <c r="ET18" s="1">
         <f t="shared" si="94"/>
-        <v>2600.7244006557844</v>
+        <v>3379.1511047747936</v>
       </c>
       <c r="EU18" s="1">
         <f t="shared" si="94"/>
-        <v>2574.7171566492266</v>
+        <v>3345.3595937270456</v>
       </c>
       <c r="EV18" s="1">
         <f t="shared" si="94"/>
-        <v>2548.9699850827342</v>
+        <v>3311.905997789775</v>
       </c>
       <c r="EW18" s="1">
         <f t="shared" si="94"/>
-        <v>2523.4802852319067</v>
+        <v>3278.7869378118771</v>
       </c>
       <c r="EX18" s="1">
         <f t="shared" si="94"/>
-        <v>2498.2454823795874</v>
+        <v>3245.9990684337581</v>
       </c>
       <c r="EY18" s="1">
         <f t="shared" si="94"/>
-        <v>2473.2630275557917</v>
+        <v>3213.5390777494204</v>
       </c>
       <c r="EZ18" s="1">
         <f t="shared" si="94"/>
-        <v>2448.530397280234</v>
+        <v>3181.4036869719262</v>
       </c>
       <c r="FA18" s="1">
         <f t="shared" si="94"/>
-        <v>2424.0450933074317</v>
+        <v>3149.5896501022071</v>
       </c>
       <c r="FB18" s="1">
         <f t="shared" si="94"/>
-        <v>2399.8046423743572</v>
+        <v>3118.0937536011852</v>
       </c>
       <c r="FC18" s="1">
         <f t="shared" si="94"/>
-        <v>2375.8065959506134</v>
+        <v>3086.9128160651735</v>
       </c>
       <c r="FD18" s="1">
         <f t="shared" si="94"/>
-        <v>2352.0485299911074</v>
+        <v>3056.0436879045219</v>
       </c>
       <c r="FE18" s="1">
         <f t="shared" si="94"/>
-        <v>2328.5280446911966</v>
+        <v>3025.4832510254769</v>
       </c>
       <c r="FF18" s="1">
         <f t="shared" si="94"/>
-        <v>2305.2427642442844</v>
+        <v>2995.2284185152221</v>
       </c>
       <c r="FG18" s="1">
         <f t="shared" si="94"/>
-        <v>2282.1903366018414</v>
+        <v>2965.2761343300699</v>
       </c>
       <c r="FH18" s="1">
         <f t="shared" si="94"/>
-        <v>2259.368433235823</v>
+        <v>2935.623372986769</v>
       </c>
       <c r="FI18" s="1">
         <f t="shared" si="94"/>
-        <v>2236.7747489034646</v>
+        <v>2906.2671392569014</v>
       </c>
       <c r="FJ18" s="1">
         <f t="shared" si="94"/>
-        <v>2214.4070014144299</v>
+        <v>2877.2044678643324</v>
       </c>
     </row>
     <row r="19" spans="2:166" x14ac:dyDescent="0.3">
@@ -4289,16 +4284,16 @@
         <v>2348.6999999999998</v>
       </c>
       <c r="AB19" s="5">
-        <f>2348.7</f>
-        <v>2348.6999999999998</v>
+        <f>2365.2</f>
+        <v>2365.1999999999998</v>
       </c>
       <c r="AC19" s="5">
-        <f>2348.7</f>
-        <v>2348.6999999999998</v>
+        <f>2365.2</f>
+        <v>2365.1999999999998</v>
       </c>
       <c r="AD19" s="5">
-        <f>2348.7</f>
-        <v>2348.6999999999998</v>
+        <f>2365.2</f>
+        <v>2365.1999999999998</v>
       </c>
       <c r="AF19" s="5">
         <v>1742</v>
@@ -4323,48 +4318,48 @@
         <v>2345.4</v>
       </c>
       <c r="AM19" s="5">
-        <f t="shared" ref="AM19:AW19" si="96">2348.7</f>
-        <v>2348.6999999999998</v>
+        <f t="shared" ref="AM19:AW19" si="96">2365.2</f>
+        <v>2365.1999999999998</v>
       </c>
       <c r="AN19" s="5">
         <f t="shared" si="96"/>
-        <v>2348.6999999999998</v>
+        <v>2365.1999999999998</v>
       </c>
       <c r="AO19" s="5">
         <f t="shared" si="96"/>
-        <v>2348.6999999999998</v>
+        <v>2365.1999999999998</v>
       </c>
       <c r="AP19" s="5">
         <f t="shared" si="96"/>
-        <v>2348.6999999999998</v>
+        <v>2365.1999999999998</v>
       </c>
       <c r="AQ19" s="5">
         <f t="shared" si="96"/>
-        <v>2348.6999999999998</v>
+        <v>2365.1999999999998</v>
       </c>
       <c r="AR19" s="5">
         <f t="shared" si="96"/>
-        <v>2348.6999999999998</v>
+        <v>2365.1999999999998</v>
       </c>
       <c r="AS19" s="5">
         <f t="shared" si="96"/>
-        <v>2348.6999999999998</v>
+        <v>2365.1999999999998</v>
       </c>
       <c r="AT19" s="5">
         <f t="shared" si="96"/>
-        <v>2348.6999999999998</v>
+        <v>2365.1999999999998</v>
       </c>
       <c r="AU19" s="5">
         <f t="shared" si="96"/>
-        <v>2348.6999999999998</v>
+        <v>2365.1999999999998</v>
       </c>
       <c r="AV19" s="5">
         <f t="shared" si="96"/>
-        <v>2348.6999999999998</v>
+        <v>2365.1999999999998</v>
       </c>
       <c r="AW19" s="5">
         <f t="shared" si="96"/>
-        <v>2348.6999999999998</v>
+        <v>2365.1999999999998</v>
       </c>
     </row>
     <row r="20" spans="2:166" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -4473,15 +4468,15 @@
       </c>
       <c r="AB20" s="7">
         <f t="shared" si="107"/>
-        <v>0.1075308102354494</v>
+        <v>0.13821241332656864</v>
       </c>
       <c r="AC20" s="7">
         <f t="shared" si="107"/>
-        <v>0.11523790820453873</v>
+        <v>0.14118473279215293</v>
       </c>
       <c r="AD20" s="7">
         <f t="shared" si="107"/>
-        <v>7.4612232298718509E-2</v>
+        <v>0.10121323778116022</v>
       </c>
       <c r="AF20" s="7">
         <f>AF18/AF19</f>
@@ -4513,47 +4508,47 @@
       </c>
       <c r="AM20" s="7">
         <f t="shared" ref="AM20" si="112">AM18/AM19</f>
-        <v>0.38849518414442041</v>
+        <v>0.47108899036022317</v>
       </c>
       <c r="AN20" s="7">
         <f t="shared" ref="AN20" si="113">AN18/AN19</f>
-        <v>0.5997889945927537</v>
+        <v>0.68318787163876238</v>
       </c>
       <c r="AO20" s="7">
         <f t="shared" ref="AO20" si="114">AO18/AO19</f>
-        <v>0.93495122691327148</v>
+        <v>1.04595910970066</v>
       </c>
       <c r="AP20" s="7">
         <f t="shared" ref="AP20" si="115">AP18/AP19</f>
-        <v>1.3523412516364355</v>
+        <v>1.4963961668971422</v>
       </c>
       <c r="AQ20" s="7">
         <f t="shared" ref="AQ20" si="116">AQ18/AQ19</f>
-        <v>1.7510463350610204</v>
+        <v>1.9260513033086479</v>
       </c>
       <c r="AR20" s="7">
         <f t="shared" ref="AR20:AS20" si="117">AR18/AR19</f>
-        <v>1.9912166713522883</v>
+        <v>2.1819516356349986</v>
       </c>
       <c r="AS20" s="7">
         <f t="shared" si="117"/>
-        <v>2.2872663370705388</v>
+        <v>2.5000162699324493</v>
       </c>
       <c r="AT20" s="7">
         <f t="shared" ref="AT20:AW20" si="118">AT18/AT19</f>
-        <v>2.5197058576128968</v>
+        <v>2.8073471283185696</v>
       </c>
       <c r="AU20" s="7">
         <f t="shared" si="118"/>
-        <v>2.7152338820775239</v>
+        <v>3.1477967951765633</v>
       </c>
       <c r="AV20" s="7">
         <f t="shared" si="118"/>
-        <v>2.8950921702985113</v>
+        <v>3.5249107365070937</v>
       </c>
       <c r="AW20" s="7">
         <f t="shared" si="118"/>
-        <v>3.0557099631740554</v>
+        <v>3.9426215172190826</v>
       </c>
     </row>
     <row r="21" spans="2:166" x14ac:dyDescent="0.3">
@@ -4651,15 +4646,15 @@
       </c>
       <c r="AB22" s="9">
         <f t="shared" ref="AB22" si="137">AB3/X3-1</f>
-        <v>0.37999999999999989</v>
+        <v>0.48016516737944248</v>
       </c>
       <c r="AC22" s="9">
         <f t="shared" ref="AC22" si="138">AC3/Y3-1</f>
-        <v>0.35000000000000009</v>
+        <v>0.52</v>
       </c>
       <c r="AD22" s="9">
         <f t="shared" ref="AD22" si="139">AD3/Z3-1</f>
-        <v>0.30000000000000004</v>
+        <v>0.47</v>
       </c>
       <c r="AG22" s="9">
         <f>AG3/AF3-1</f>
@@ -4687,7 +4682,7 @@
       </c>
       <c r="AM22" s="9">
         <f t="shared" si="140"/>
-        <v>0.35229043065540577</v>
+        <v>0.46813184895651561</v>
       </c>
       <c r="AN22" s="9">
         <f t="shared" si="140"/>
@@ -4715,19 +4710,19 @@
       </c>
       <c r="AT22" s="9">
         <f t="shared" ref="AT22" si="142">AT3/AS3-1</f>
-        <v>8.0000000000000071E-2</v>
+        <v>0.10000000000000009</v>
       </c>
       <c r="AU22" s="9">
         <f t="shared" ref="AU22" si="143">AU3/AT3-1</f>
-        <v>6.0000000000000053E-2</v>
+        <v>0.10000000000000009</v>
       </c>
       <c r="AV22" s="9">
         <f t="shared" ref="AV22" si="144">AV3/AU3-1</f>
-        <v>5.0000000000000044E-2</v>
+        <v>0.10000000000000009</v>
       </c>
       <c r="AW22" s="9">
         <f t="shared" ref="AW22" si="145">AW3/AV3-1</f>
-        <v>4.0000000000000036E-2</v>
+        <v>0.10000000000000009</v>
       </c>
     </row>
     <row r="23" spans="2:166" x14ac:dyDescent="0.3">
@@ -4832,7 +4827,7 @@
       </c>
       <c r="AB23" s="9">
         <f t="shared" si="149"/>
-        <v>0.8</v>
+        <v>0.80781109893394443</v>
       </c>
       <c r="AC23" s="9">
         <f t="shared" si="149"/>
@@ -4872,7 +4867,7 @@
       </c>
       <c r="AM23" s="9">
         <f t="shared" si="151"/>
-        <v>0.79819928652777294</v>
+        <v>0.79987062566781997</v>
       </c>
       <c r="AN23" s="9">
         <f t="shared" si="151"/>
@@ -5017,15 +5012,15 @@
       </c>
       <c r="AB24" s="9">
         <f t="shared" si="157"/>
-        <v>0.22433752449833189</v>
+        <v>0.26840689449038563</v>
       </c>
       <c r="AC24" s="9">
         <f t="shared" si="157"/>
-        <v>0.22705618092248012</v>
+        <v>0.26205647647720276</v>
       </c>
       <c r="AD24" s="9">
         <f t="shared" si="157"/>
-        <v>0.11045782012549399</v>
+        <v>0.15319399058717156</v>
       </c>
       <c r="AF24" s="9">
         <f t="shared" ref="AF24:AR24" si="158">AF10/AF3</f>
@@ -5057,47 +5052,47 @@
       </c>
       <c r="AM24" s="9">
         <f t="shared" si="158"/>
-        <v>0.18768186044735125</v>
+        <v>0.21889266981792505</v>
       </c>
       <c r="AN24" s="9">
         <f t="shared" si="158"/>
-        <v>0.26426237132291019</v>
+        <v>0.28637503735951858</v>
       </c>
       <c r="AO24" s="9">
         <f t="shared" si="158"/>
-        <v>0.34158717929288651</v>
+        <v>0.36004402087862736</v>
       </c>
       <c r="AP24" s="9">
         <f t="shared" si="158"/>
-        <v>0.41004086005209839</v>
+        <v>0.42552079170465512</v>
       </c>
       <c r="AQ24" s="9">
         <f t="shared" si="158"/>
-        <v>0.45545939479123831</v>
+        <v>0.46897153852185997</v>
       </c>
       <c r="AR24" s="9">
         <f t="shared" si="158"/>
-        <v>0.48383209007637112</v>
+        <v>0.49592190288798005</v>
       </c>
       <c r="AS24" s="9">
         <f t="shared" ref="AS24:AW24" si="159">AS10/AS3</f>
-        <v>0.50518975625263507</v>
+        <v>0.51640030995067243</v>
       </c>
       <c r="AT24" s="9">
         <f t="shared" si="159"/>
-        <v>0.51323476979415539</v>
+        <v>0.52611665104516891</v>
       </c>
       <c r="AU24" s="9">
         <f t="shared" si="159"/>
-        <v>0.5183957218773948</v>
+        <v>0.53512634915097479</v>
       </c>
       <c r="AV24" s="9">
         <f t="shared" si="159"/>
-        <v>0.52215584410946925</v>
+        <v>0.54348079648544945</v>
       </c>
       <c r="AW24" s="9">
         <f t="shared" si="159"/>
-        <v>0.5246143855689025</v>
+        <v>0.55122764765014398</v>
       </c>
     </row>
     <row r="25" spans="2:166" x14ac:dyDescent="0.3">
@@ -5202,7 +5197,7 @@
       </c>
       <c r="AB25" s="9">
         <f t="shared" si="164"/>
-        <v>0.26</v>
+        <v>0.24290126531832221</v>
       </c>
       <c r="AC25" s="9">
         <f t="shared" si="164"/>
@@ -5242,7 +5237,7 @@
       </c>
       <c r="AM25" s="9">
         <f t="shared" si="166"/>
-        <v>0.27555504170093681</v>
+        <v>0.27192008861874334</v>
       </c>
       <c r="AN25" s="9">
         <f t="shared" si="166"/>
@@ -5384,7 +5379,7 @@
       </c>
       <c r="AB26" s="9">
         <f t="shared" ref="AB26:AB27" si="171">AB7/X7-1</f>
-        <v>0.25</v>
+        <v>0.24080882352941169</v>
       </c>
       <c r="AC26" s="9">
         <f t="shared" ref="AC26:AC27" si="172">AC7/Y7-1</f>
@@ -5421,7 +5416,7 @@
       </c>
       <c r="AM26" s="9">
         <f t="shared" si="174"/>
-        <v>0.21111439259696807</v>
+        <v>0.20914550108289043</v>
       </c>
       <c r="AN26" s="9">
         <f t="shared" si="174"/>
@@ -5467,7 +5462,7 @@
         <v>38</v>
       </c>
       <c r="AZ26" s="9">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="27" spans="2:166" x14ac:dyDescent="0.3">
@@ -5563,7 +5558,7 @@
       </c>
       <c r="AB27" s="9">
         <f t="shared" si="171"/>
-        <v>0.14999999999999991</v>
+        <v>0.17316017316017307</v>
       </c>
       <c r="AC27" s="9">
         <f t="shared" si="172"/>
@@ -5600,7 +5595,7 @@
       </c>
       <c r="AM27" s="9">
         <f t="shared" si="177"/>
-        <v>0.1506656555443211</v>
+        <v>0.15607516009437128</v>
       </c>
       <c r="AN27" s="9">
         <f t="shared" si="177"/>
@@ -5647,7 +5642,7 @@
       </c>
       <c r="AZ27" s="5">
         <f>NPV(AZ26,AM18:FJ18)</f>
-        <v>84934.711500715945</v>
+        <v>128931.12409030413</v>
       </c>
     </row>
     <row r="28" spans="2:166" x14ac:dyDescent="0.3">
@@ -5752,7 +5747,7 @@
       </c>
       <c r="AB28" s="9">
         <f t="shared" si="181"/>
-        <v>0.04</v>
+        <v>1.08335841107433E-2</v>
       </c>
       <c r="AC28" s="9">
         <f t="shared" si="181"/>
@@ -5792,7 +5787,7 @@
       </c>
       <c r="AM28" s="9">
         <f t="shared" si="183"/>
-        <v>3.6523806158500968E-2</v>
+        <v>2.8763641684404671E-2</v>
       </c>
       <c r="AN28" s="9">
         <f t="shared" si="183"/>
@@ -5808,7 +5803,7 @@
       </c>
       <c r="AQ28" s="9">
         <f t="shared" si="183"/>
-        <v>0.1</v>
+        <v>0.10000000000000002</v>
       </c>
       <c r="AR28" s="9">
         <f t="shared" si="183"/>
@@ -5881,7 +5876,7 @@
       </c>
       <c r="AB29" s="9">
         <f t="shared" si="185"/>
-        <v>0.01</v>
+        <v>5.4167920553716501E-3</v>
       </c>
       <c r="AC29" s="9">
         <f t="shared" si="185"/>
@@ -5903,11 +5898,11 @@
       </c>
       <c r="AM29" s="9">
         <f t="shared" si="186"/>
-        <v>1.1530485103685201E-2</v>
+        <v>9.9516864200189445E-3</v>
       </c>
       <c r="AN29" s="9">
         <f t="shared" si="186"/>
-        <v>1.9999999999999997E-2</v>
+        <v>0.02</v>
       </c>
       <c r="AO29" s="9">
         <f t="shared" si="186"/>
@@ -5950,7 +5945,7 @@
       </c>
       <c r="AZ29" s="5">
         <f>AZ27+AZ28</f>
-        <v>90164.711500715945</v>
+        <v>134161.12409030413</v>
       </c>
     </row>
     <row r="30" spans="2:166" x14ac:dyDescent="0.3">
@@ -6056,15 +6051,15 @@
       </c>
       <c r="AB30" s="9">
         <f t="shared" si="190"/>
-        <v>0.26989052317964307</v>
+        <v>0.32569492876357486</v>
       </c>
       <c r="AC30" s="9">
         <f t="shared" si="190"/>
-        <v>0.27634507491640509</v>
+        <v>0.30281305995864927</v>
       </c>
       <c r="AD30" s="9">
         <f t="shared" si="190"/>
-        <v>0.16290192888682328</v>
+        <v>0.19679762418562602</v>
       </c>
       <c r="AF30" s="9">
         <f t="shared" ref="AF30:AS30" si="191">AF18/AF3</f>
@@ -6096,54 +6091,54 @@
       </c>
       <c r="AM30" s="9">
         <f t="shared" si="191"/>
-        <v>0.23548213028984588</v>
+        <v>0.26486252090373047</v>
       </c>
       <c r="AN30" s="9">
         <f t="shared" si="191"/>
-        <v>0.27965813484259433</v>
+        <v>0.2954706511212063</v>
       </c>
       <c r="AO30" s="9">
         <f t="shared" si="191"/>
-        <v>0.34325288729758135</v>
+        <v>0.35619284150827429</v>
       </c>
       <c r="AP30" s="9">
         <f t="shared" si="191"/>
-        <v>0.40039611406182823</v>
+        <v>0.41095605363989046</v>
       </c>
       <c r="AQ30" s="9">
         <f t="shared" si="191"/>
-        <v>0.43935865792339063</v>
+        <v>0.44826480176429023</v>
       </c>
       <c r="AR30" s="9">
         <f t="shared" si="191"/>
-        <v>0.43826341560372667</v>
+        <v>0.44545830119446517</v>
       </c>
       <c r="AS30" s="9">
         <f t="shared" si="191"/>
-        <v>0.45765767765913207</v>
+        <v>0.46399370277456525</v>
       </c>
       <c r="AT30" s="9">
         <f t="shared" ref="AT30:AW30" si="192">AT18/AT3</f>
-        <v>0.46682069871142834</v>
+        <v>0.47366651340642957</v>
       </c>
       <c r="AU30" s="9">
         <f t="shared" si="192"/>
-        <v>0.4745714828842954</v>
+        <v>0.48282591251783663</v>
       </c>
       <c r="AV30" s="9">
         <f t="shared" si="192"/>
-        <v>0.48191172088225603</v>
+        <v>0.49151787847465622</v>
       </c>
       <c r="AW30" s="9">
         <f t="shared" si="192"/>
-        <v>0.48908448407229116</v>
+        <v>0.49978543845915879</v>
       </c>
       <c r="AY30" t="s">
         <v>42</v>
       </c>
       <c r="AZ30" s="4">
         <f>AZ29/AR19</f>
-        <v>38.389198918855513</v>
+        <v>56.722951162820962</v>
       </c>
     </row>
     <row r="31" spans="2:166" x14ac:dyDescent="0.3">
@@ -6152,7 +6147,7 @@
       </c>
       <c r="AZ31" s="4">
         <f>Main!D3</f>
-        <v>127.59</v>
+        <v>182.39</v>
       </c>
     </row>
     <row r="32" spans="2:166" x14ac:dyDescent="0.3">
@@ -6161,7 +6156,7 @@
       </c>
       <c r="AZ32" s="10">
         <f>AZ30/AZ31-1</f>
-        <v>-0.69912062921188567</v>
+        <v>-0.68900185776182377</v>
       </c>
     </row>
     <row r="33" spans="2:52" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -6169,8 +6164,12 @@
         <v>73</v>
       </c>
       <c r="W33" s="8">
-        <f t="shared" ref="W33" si="193">W18</f>
+        <f t="shared" ref="W33:X33" si="193">W18</f>
         <v>106.00000000000001</v>
+      </c>
+      <c r="X33" s="8">
+        <f t="shared" si="193"/>
+        <v>135.49999999999997</v>
       </c>
       <c r="AA33" s="8">
         <f t="shared" ref="AA33:AD33" si="194">AA18</f>
@@ -6178,15 +6177,15 @@
       </c>
       <c r="AB33" s="8">
         <f t="shared" si="194"/>
-        <v>252.557614</v>
+        <v>326.90000000000009</v>
       </c>
       <c r="AC33" s="8">
         <f t="shared" si="194"/>
-        <v>270.65927500000009</v>
+        <v>333.93013000000008</v>
       </c>
       <c r="AD33" s="8">
         <f t="shared" si="194"/>
-        <v>175.24175000000014</v>
+        <v>239.38955000000013</v>
       </c>
       <c r="AJ33" s="8">
         <f t="shared" ref="AJ33:AK33" si="195">AJ18</f>
@@ -6202,47 +6201,47 @@
       </c>
       <c r="AM33" s="8">
         <f t="shared" ref="AM33:AW33" si="196">AM18</f>
-        <v>912.45863900000018</v>
+        <v>1114.2196799999997</v>
       </c>
       <c r="AN33" s="8">
         <f t="shared" si="196"/>
-        <v>1408.7244116000004</v>
+        <v>1615.8759540000008</v>
       </c>
       <c r="AO33" s="8">
         <f t="shared" si="196"/>
-        <v>2195.9199466512005</v>
+        <v>2473.9024862640008</v>
       </c>
       <c r="AP33" s="8">
         <f t="shared" si="196"/>
-        <v>3176.2438977184956</v>
+        <v>3539.2762139451202</v>
       </c>
       <c r="AQ33" s="8">
         <f t="shared" si="196"/>
-        <v>4112.6825271578182</v>
+        <v>4555.4965425856135</v>
       </c>
       <c r="AR33" s="8">
         <f t="shared" si="196"/>
-        <v>4676.7705960051189</v>
+        <v>5160.7520086038985</v>
       </c>
       <c r="AS33" s="8">
         <f t="shared" si="196"/>
-        <v>5372.1024458775737</v>
+        <v>5913.0384816442283</v>
       </c>
       <c r="AT33" s="8">
         <f t="shared" si="196"/>
-        <v>5918.0331477754107</v>
+        <v>6639.9374278990799</v>
       </c>
       <c r="AU33" s="8">
         <f t="shared" si="196"/>
-        <v>6377.2698188354798</v>
+        <v>7445.1689799516071</v>
       </c>
       <c r="AV33" s="8">
         <f t="shared" si="196"/>
-        <v>6799.7029803801133</v>
+        <v>8337.1188739865775</v>
       </c>
       <c r="AW33" s="8">
         <f t="shared" si="196"/>
-        <v>7176.9459905069034</v>
+        <v>9325.0884125265729</v>
       </c>
       <c r="AY33" t="s">
         <v>45</v>
@@ -6258,20 +6257,24 @@
       <c r="W34" s="5">
         <v>8.4</v>
       </c>
+      <c r="X34" s="5">
+        <f t="shared" ref="X34:X48" si="197">X56-W34</f>
+        <v>8.1</v>
+      </c>
       <c r="AA34" s="5">
         <v>6.6</v>
       </c>
       <c r="AB34" s="5">
-        <f>AA34*1.05</f>
+        <f t="shared" ref="AB34:AB48" si="198">AB56-AA34</f>
+        <v>6.6</v>
+      </c>
+      <c r="AC34" s="5">
+        <f t="shared" ref="AC34:AD34" si="199">AB34*1.05</f>
         <v>6.93</v>
       </c>
-      <c r="AC34" s="5">
-        <f t="shared" ref="AC34:AD34" si="197">AB34*1.05</f>
+      <c r="AD34" s="5">
+        <f t="shared" si="199"/>
         <v>7.2765000000000004</v>
-      </c>
-      <c r="AD34" s="5">
-        <f t="shared" si="197"/>
-        <v>7.6403250000000007</v>
       </c>
       <c r="AJ34" s="5">
         <v>22.5</v>
@@ -6284,47 +6287,47 @@
       </c>
       <c r="AM34" s="5">
         <f>SUM(AA34:AD34)</f>
-        <v>28.446825</v>
+        <v>27.406500000000001</v>
       </c>
       <c r="AN34" s="5">
-        <f t="shared" ref="AN34:AW34" si="198">AM34*1.05</f>
-        <v>29.869166250000003</v>
+        <f t="shared" ref="AN34:AW34" si="200">AM34*1.05</f>
+        <v>28.776825000000002</v>
       </c>
       <c r="AO34" s="5">
-        <f t="shared" si="198"/>
-        <v>31.362624562500006</v>
+        <f t="shared" si="200"/>
+        <v>30.215666250000005</v>
       </c>
       <c r="AP34" s="5">
-        <f t="shared" si="198"/>
-        <v>32.930755790625007</v>
+        <f t="shared" si="200"/>
+        <v>31.726449562500008</v>
       </c>
       <c r="AQ34" s="5">
-        <f t="shared" si="198"/>
-        <v>34.577293580156258</v>
+        <f t="shared" si="200"/>
+        <v>33.312772040625006</v>
       </c>
       <c r="AR34" s="5">
-        <f t="shared" si="198"/>
-        <v>36.306158259164071</v>
+        <f t="shared" si="200"/>
+        <v>34.978410642656257</v>
       </c>
       <c r="AS34" s="5">
-        <f t="shared" si="198"/>
-        <v>38.121466172122275</v>
+        <f t="shared" si="200"/>
+        <v>36.727331174789072</v>
       </c>
       <c r="AT34" s="5">
-        <f t="shared" si="198"/>
-        <v>40.027539480728393</v>
+        <f t="shared" si="200"/>
+        <v>38.563697733528528</v>
       </c>
       <c r="AU34" s="5">
-        <f t="shared" si="198"/>
-        <v>42.028916454764811</v>
+        <f t="shared" si="200"/>
+        <v>40.491882620204954</v>
       </c>
       <c r="AV34" s="5">
-        <f t="shared" si="198"/>
-        <v>44.130362277503053</v>
+        <f t="shared" si="200"/>
+        <v>42.516476751215201</v>
       </c>
       <c r="AW34" s="5">
-        <f t="shared" si="198"/>
-        <v>46.336880391378209</v>
+        <f t="shared" si="200"/>
+        <v>44.64230058877596</v>
       </c>
     </row>
     <row r="35" spans="2:52" x14ac:dyDescent="0.3">
@@ -6334,20 +6337,24 @@
       <c r="W35" s="5">
         <v>125.7</v>
       </c>
+      <c r="X35" s="5">
+        <f t="shared" si="197"/>
+        <v>141.69999999999999</v>
+      </c>
       <c r="AA35" s="5">
         <v>155.30000000000001</v>
       </c>
       <c r="AB35" s="5">
-        <f>AA35*1.1</f>
-        <v>170.83</v>
+        <f t="shared" si="198"/>
+        <v>160</v>
       </c>
       <c r="AC35" s="5">
-        <f t="shared" ref="AC35:AD35" si="199">AB35*1.1</f>
-        <v>187.91300000000004</v>
+        <f t="shared" ref="AC35:AD35" si="201">AB35*1.1</f>
+        <v>176</v>
       </c>
       <c r="AD35" s="5">
-        <f t="shared" si="199"/>
-        <v>206.70430000000005</v>
+        <f t="shared" si="201"/>
+        <v>193.60000000000002</v>
       </c>
       <c r="AJ35" s="5">
         <v>564.79999999999995</v>
@@ -6359,48 +6366,48 @@
         <v>691.6</v>
       </c>
       <c r="AM35" s="5">
-        <f t="shared" ref="AM35:AM50" si="200">SUM(AA35:AD35)</f>
-        <v>720.7473</v>
+        <f t="shared" ref="AM35:AM50" si="202">SUM(AA35:AD35)</f>
+        <v>684.90000000000009</v>
       </c>
       <c r="AN35" s="5">
         <f>AM35*1.07</f>
-        <v>771.199611</v>
+        <v>732.84300000000019</v>
       </c>
       <c r="AO35" s="5">
         <f>AN35*1.05</f>
-        <v>809.7595915500001</v>
+        <v>769.4851500000002</v>
       </c>
       <c r="AP35" s="5">
         <f>AO35*1.03</f>
-        <v>834.05237929650013</v>
+        <v>792.56970450000028</v>
       </c>
       <c r="AQ35" s="5">
         <f>AP35*1.02</f>
-        <v>850.73342688243019</v>
+        <v>808.42109859000027</v>
       </c>
       <c r="AR35" s="5">
-        <f t="shared" ref="AR35:AW35" si="201">AQ35*1.02</f>
-        <v>867.74809542007881</v>
+        <f t="shared" ref="AR35:AW35" si="203">AQ35*1.02</f>
+        <v>824.58952056180033</v>
       </c>
       <c r="AS35" s="5">
-        <f t="shared" si="201"/>
-        <v>885.10305732848042</v>
+        <f t="shared" si="203"/>
+        <v>841.08131097303635</v>
       </c>
       <c r="AT35" s="5">
-        <f t="shared" si="201"/>
-        <v>902.80511847504999</v>
+        <f t="shared" si="203"/>
+        <v>857.90293719249712</v>
       </c>
       <c r="AU35" s="5">
-        <f t="shared" si="201"/>
-        <v>920.86122084455099</v>
+        <f t="shared" si="203"/>
+        <v>875.06099593634713</v>
       </c>
       <c r="AV35" s="5">
-        <f t="shared" si="201"/>
-        <v>939.27844526144202</v>
+        <f t="shared" si="203"/>
+        <v>892.5622158550741</v>
       </c>
       <c r="AW35" s="5">
-        <f t="shared" si="201"/>
-        <v>958.06401416667086</v>
+        <f t="shared" si="203"/>
+        <v>910.41346017217563</v>
       </c>
     </row>
     <row r="36" spans="2:52" x14ac:dyDescent="0.3">
@@ -6410,10 +6417,15 @@
       <c r="W36" s="5">
         <v>0</v>
       </c>
+      <c r="X36" s="5">
+        <f t="shared" si="197"/>
+        <v>0</v>
+      </c>
       <c r="AA36" s="5">
         <v>0</v>
       </c>
       <c r="AB36" s="5">
+        <f t="shared" si="198"/>
         <v>0</v>
       </c>
       <c r="AC36" s="5">
@@ -6432,47 +6444,47 @@
         <v>41.2</v>
       </c>
       <c r="AM36" s="5">
-        <f t="shared" si="200"/>
+        <f t="shared" si="202"/>
         <v>0</v>
       </c>
       <c r="AN36" s="5">
-        <f t="shared" ref="AN36:AW36" si="202">AM36*1.05</f>
+        <f t="shared" ref="AN36:AW36" si="204">AM36*1.05</f>
         <v>0</v>
       </c>
       <c r="AO36" s="5">
-        <f t="shared" si="202"/>
+        <f t="shared" si="204"/>
         <v>0</v>
       </c>
       <c r="AP36" s="5">
-        <f t="shared" si="202"/>
+        <f t="shared" si="204"/>
         <v>0</v>
       </c>
       <c r="AQ36" s="5">
-        <f t="shared" si="202"/>
+        <f t="shared" si="204"/>
         <v>0</v>
       </c>
       <c r="AR36" s="5">
-        <f t="shared" si="202"/>
+        <f t="shared" si="204"/>
         <v>0</v>
       </c>
       <c r="AS36" s="5">
-        <f t="shared" si="202"/>
+        <f t="shared" si="204"/>
         <v>0</v>
       </c>
       <c r="AT36" s="5">
-        <f t="shared" si="202"/>
+        <f t="shared" si="204"/>
         <v>0</v>
       </c>
       <c r="AU36" s="5">
-        <f t="shared" si="202"/>
+        <f t="shared" si="204"/>
         <v>0</v>
       </c>
       <c r="AV36" s="5">
-        <f t="shared" si="202"/>
+        <f t="shared" si="204"/>
         <v>0</v>
       </c>
       <c r="AW36" s="5">
-        <f t="shared" si="202"/>
+        <f t="shared" si="204"/>
         <v>0</v>
       </c>
     </row>
@@ -6483,11 +6495,16 @@
       <c r="W37" s="5">
         <v>12.4</v>
       </c>
+      <c r="X37" s="5">
+        <f t="shared" si="197"/>
+        <v>7.6</v>
+      </c>
       <c r="AA37" s="5">
         <v>10.7</v>
       </c>
       <c r="AB37" s="5">
-        <v>11</v>
+        <f t="shared" si="198"/>
+        <v>-11.2</v>
       </c>
       <c r="AC37" s="5">
         <v>11</v>
@@ -6505,8 +6522,8 @@
         <v>19.3</v>
       </c>
       <c r="AM37" s="5">
-        <f t="shared" si="200"/>
-        <v>43.7</v>
+        <f t="shared" si="202"/>
+        <v>21.5</v>
       </c>
       <c r="AN37" s="5">
         <v>0</v>
@@ -6546,20 +6563,24 @@
       <c r="W38" s="5">
         <v>-11.9</v>
       </c>
+      <c r="X38" s="5">
+        <f t="shared" si="197"/>
+        <v>-14.6</v>
+      </c>
       <c r="AA38" s="5">
         <v>-15.5</v>
       </c>
       <c r="AB38" s="5">
-        <f>AA38*1.03</f>
-        <v>-15.965</v>
+        <f t="shared" si="198"/>
+        <v>-8.8999999999999986</v>
       </c>
       <c r="AC38" s="5">
-        <f t="shared" ref="AC38:AD38" si="203">AB38*1.03</f>
-        <v>-16.443950000000001</v>
+        <f t="shared" ref="AC38:AD38" si="205">AB38*1.03</f>
+        <v>-9.166999999999998</v>
       </c>
       <c r="AD38" s="5">
-        <f t="shared" si="203"/>
-        <v>-16.937268500000002</v>
+        <f t="shared" si="205"/>
+        <v>-9.442009999999998</v>
       </c>
       <c r="AJ38" s="5">
         <v>-15.5</v>
@@ -6571,48 +6592,48 @@
         <v>-52.5</v>
       </c>
       <c r="AM38" s="5">
-        <f t="shared" si="200"/>
-        <v>-64.846218500000006</v>
+        <f t="shared" si="202"/>
+        <v>-43.009009999999989</v>
       </c>
       <c r="AN38" s="5">
-        <f t="shared" ref="AN38:AW38" si="204">AM38*1.05</f>
-        <v>-68.088529425000004</v>
+        <f t="shared" ref="AN38:AW38" si="206">AM38*1.05</f>
+        <v>-45.159460499999987</v>
       </c>
       <c r="AO38" s="5">
-        <f t="shared" si="204"/>
-        <v>-71.49295589625001</v>
+        <f t="shared" si="206"/>
+        <v>-47.417433524999986</v>
       </c>
       <c r="AP38" s="5">
-        <f t="shared" si="204"/>
-        <v>-75.067603691062516</v>
+        <f t="shared" si="206"/>
+        <v>-49.78830520124999</v>
       </c>
       <c r="AQ38" s="5">
-        <f t="shared" si="204"/>
-        <v>-78.820983875615639</v>
+        <f t="shared" si="206"/>
+        <v>-52.277720461312491</v>
       </c>
       <c r="AR38" s="5">
-        <f t="shared" si="204"/>
-        <v>-82.762033069396423</v>
+        <f t="shared" si="206"/>
+        <v>-54.891606484378116</v>
       </c>
       <c r="AS38" s="5">
-        <f t="shared" si="204"/>
-        <v>-86.900134722866255</v>
+        <f t="shared" si="206"/>
+        <v>-57.636186808597024</v>
       </c>
       <c r="AT38" s="5">
-        <f t="shared" si="204"/>
-        <v>-91.245141459009574</v>
+        <f t="shared" si="206"/>
+        <v>-60.517996149026878</v>
       </c>
       <c r="AU38" s="5">
-        <f t="shared" si="204"/>
-        <v>-95.807398531960061</v>
+        <f t="shared" si="206"/>
+        <v>-63.543895956478224</v>
       </c>
       <c r="AV38" s="5">
-        <f t="shared" si="204"/>
-        <v>-100.59776845855806</v>
+        <f t="shared" si="206"/>
+        <v>-66.721090754302139</v>
       </c>
       <c r="AW38" s="5">
-        <f t="shared" si="204"/>
-        <v>-105.62765688148598</v>
+        <f t="shared" si="206"/>
+        <v>-70.057145292017253</v>
       </c>
     </row>
     <row r="39" spans="2:52" x14ac:dyDescent="0.3">
@@ -6622,11 +6643,16 @@
       <c r="W39" s="5">
         <v>5.6</v>
       </c>
+      <c r="X39" s="5">
+        <f t="shared" si="197"/>
+        <v>5.8000000000000007</v>
+      </c>
       <c r="AA39" s="5">
         <v>3.5</v>
       </c>
       <c r="AB39" s="5">
-        <v>0</v>
+        <f t="shared" si="198"/>
+        <v>23</v>
       </c>
       <c r="AC39" s="5">
         <v>0</v>
@@ -6644,8 +6670,8 @@
         <v>24.8</v>
       </c>
       <c r="AM39" s="5">
-        <f t="shared" si="200"/>
-        <v>3.5</v>
+        <f t="shared" si="202"/>
+        <v>26.5</v>
       </c>
       <c r="AN39" s="5">
         <v>0</v>
@@ -6685,11 +6711,16 @@
       <c r="W40" s="5">
         <v>-121.9</v>
       </c>
+      <c r="X40" s="5">
+        <f t="shared" si="197"/>
+        <v>-176.4</v>
+      </c>
       <c r="AA40" s="5">
         <v>-135</v>
       </c>
       <c r="AB40" s="5">
-        <v>0</v>
+        <f t="shared" si="198"/>
+        <v>-28.5</v>
       </c>
       <c r="AC40" s="5">
         <v>0</v>
@@ -6707,8 +6738,8 @@
         <v>-211.2</v>
       </c>
       <c r="AM40" s="5">
-        <f t="shared" si="200"/>
-        <v>-135</v>
+        <f t="shared" si="202"/>
+        <v>-163.5</v>
       </c>
       <c r="AN40" s="5">
         <v>0</v>
@@ -6746,8 +6777,13 @@
         <v>81</v>
       </c>
       <c r="W41" s="5"/>
+      <c r="X41" s="5">
+        <f t="shared" si="197"/>
+        <v>0</v>
+      </c>
       <c r="AA41" s="5"/>
       <c r="AB41" s="5">
+        <f t="shared" si="198"/>
         <v>0</v>
       </c>
       <c r="AC41" s="5">
@@ -6766,7 +6802,7 @@
         <v>7.2</v>
       </c>
       <c r="AM41" s="5">
-        <f t="shared" si="200"/>
+        <f t="shared" si="202"/>
         <v>0</v>
       </c>
       <c r="AN41" s="5">
@@ -6807,11 +6843,16 @@
       <c r="W42" s="5">
         <v>22.9</v>
       </c>
+      <c r="X42" s="5">
+        <f t="shared" si="197"/>
+        <v>-20.099999999999998</v>
+      </c>
       <c r="AA42" s="5">
         <v>40.700000000000003</v>
       </c>
       <c r="AB42" s="5">
-        <v>0</v>
+        <f t="shared" si="198"/>
+        <v>-48</v>
       </c>
       <c r="AC42" s="5">
         <v>0</v>
@@ -6829,8 +6870,8 @@
         <v>4.7</v>
       </c>
       <c r="AM42" s="5">
-        <f t="shared" si="200"/>
-        <v>40.700000000000003</v>
+        <f t="shared" si="202"/>
+        <v>-7.2999999999999972</v>
       </c>
       <c r="AN42" s="5">
         <v>0</v>
@@ -6870,11 +6911,16 @@
       <c r="W43" s="5">
         <v>4.7</v>
       </c>
+      <c r="X43" s="5">
+        <f t="shared" si="197"/>
+        <v>18.100000000000001</v>
+      </c>
       <c r="AA43" s="5">
         <v>22.4</v>
       </c>
       <c r="AB43" s="5">
-        <v>0</v>
+        <f t="shared" si="198"/>
+        <v>25.800000000000004</v>
       </c>
       <c r="AC43" s="5">
         <v>0</v>
@@ -6892,8 +6938,8 @@
         <v>-18.8</v>
       </c>
       <c r="AM43" s="5">
-        <f t="shared" si="200"/>
-        <v>22.4</v>
+        <f t="shared" si="202"/>
+        <v>48.2</v>
       </c>
       <c r="AN43" s="5">
         <v>0</v>
@@ -6931,8 +6977,13 @@
         <v>84</v>
       </c>
       <c r="W44" s="5"/>
+      <c r="X44" s="5">
+        <f t="shared" si="197"/>
+        <v>0</v>
+      </c>
       <c r="AA44" s="5"/>
       <c r="AB44" s="5">
+        <f t="shared" si="198"/>
         <v>0</v>
       </c>
       <c r="AC44" s="5">
@@ -6951,7 +7002,7 @@
         <v>115.6</v>
       </c>
       <c r="AM44" s="5">
-        <f t="shared" si="200"/>
+        <f t="shared" si="202"/>
         <v>0</v>
       </c>
       <c r="AN44" s="5">
@@ -6992,11 +7043,16 @@
       <c r="W45" s="5">
         <v>-6.8</v>
       </c>
+      <c r="X45" s="5">
+        <f t="shared" si="197"/>
+        <v>40.099999999999994</v>
+      </c>
       <c r="AA45" s="5">
         <v>18.8</v>
       </c>
       <c r="AB45" s="5">
-        <v>0</v>
+        <f t="shared" si="198"/>
+        <v>101.9</v>
       </c>
       <c r="AC45" s="5">
         <v>0</v>
@@ -7014,8 +7070,8 @@
         <v>22.4</v>
       </c>
       <c r="AM45" s="5">
-        <f t="shared" si="200"/>
-        <v>18.8</v>
+        <f t="shared" si="202"/>
+        <v>120.7</v>
       </c>
       <c r="AN45" s="5">
         <v>0</v>
@@ -7053,8 +7109,13 @@
         <v>86</v>
       </c>
       <c r="W46" s="5"/>
+      <c r="X46" s="5">
+        <f t="shared" si="197"/>
+        <v>0</v>
+      </c>
       <c r="AA46" s="5"/>
       <c r="AB46" s="5">
+        <f t="shared" si="198"/>
         <v>0</v>
       </c>
       <c r="AC46" s="5">
@@ -7073,7 +7134,7 @@
         <v>54.4</v>
       </c>
       <c r="AM46" s="5">
-        <f t="shared" si="200"/>
+        <f t="shared" si="202"/>
         <v>0</v>
       </c>
       <c r="AN46" s="5">
@@ -7112,8 +7173,13 @@
         <v>76</v>
       </c>
       <c r="W47" s="5"/>
+      <c r="X47" s="5">
+        <f t="shared" si="197"/>
+        <v>0</v>
+      </c>
       <c r="AA47" s="5"/>
       <c r="AB47" s="5">
+        <f t="shared" si="198"/>
         <v>0</v>
       </c>
       <c r="AC47" s="5">
@@ -7132,7 +7198,7 @@
         <v>-49</v>
       </c>
       <c r="AM47" s="5">
-        <f t="shared" si="200"/>
+        <f t="shared" si="202"/>
         <v>0</v>
       </c>
       <c r="AN47" s="5">
@@ -7173,11 +7239,16 @@
       <c r="W48" s="5">
         <v>-15.5</v>
       </c>
+      <c r="X48" s="5">
+        <f t="shared" si="197"/>
+        <v>-1.8000000000000007</v>
+      </c>
       <c r="AA48" s="5">
         <v>-13.2</v>
       </c>
       <c r="AB48" s="5">
-        <v>0</v>
+        <f t="shared" si="198"/>
+        <v>-11.7</v>
       </c>
       <c r="AC48" s="5">
         <v>0</v>
@@ -7195,8 +7266,8 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="AM48" s="5">
-        <f t="shared" si="200"/>
-        <v>-13.2</v>
+        <f t="shared" si="202"/>
+        <v>-24.9</v>
       </c>
       <c r="AN48" s="5">
         <v>0</v>
@@ -7237,21 +7308,25 @@
         <f>W33+SUM(W34:W48)</f>
         <v>129.6</v>
       </c>
+      <c r="X49" s="8">
+        <f>X33+SUM(X34:X48)</f>
+        <v>143.99999999999997</v>
+      </c>
       <c r="AA49" s="8">
         <f>AA33+SUM(AA34:AA48)</f>
         <v>308.29999999999995</v>
       </c>
       <c r="AB49" s="8">
         <f>AB33+SUM(AB34:AB48)</f>
-        <v>425.35261400000002</v>
+        <v>535.90000000000009</v>
       </c>
       <c r="AC49" s="8">
-        <f t="shared" ref="AC49:AD49" si="205">AC33+SUM(AC34:AC48)</f>
-        <v>460.40482500000013</v>
+        <f t="shared" ref="AC49:AD49" si="207">AC33+SUM(AC34:AC48)</f>
+        <v>518.69313000000011</v>
       </c>
       <c r="AD49" s="8">
-        <f t="shared" si="205"/>
-        <v>383.64910650000019</v>
+        <f t="shared" si="207"/>
+        <v>441.82404000000014</v>
       </c>
       <c r="AJ49" s="8">
         <f>AJ33+SUM(AJ34:AJ48)</f>
@@ -7266,48 +7341,48 @@
         <v>1150.0000000000002</v>
       </c>
       <c r="AM49" s="8">
-        <f t="shared" ref="AM49:AW49" si="206">AM33+SUM(AM34:AM48)</f>
-        <v>1577.7065455000002</v>
+        <f t="shared" ref="AM49:AW49" si="208">AM33+SUM(AM34:AM48)</f>
+        <v>1804.7171699999999</v>
       </c>
       <c r="AN49" s="8">
-        <f t="shared" si="206"/>
-        <v>2141.7046594250005</v>
+        <f t="shared" si="208"/>
+        <v>2332.3363185000007</v>
       </c>
       <c r="AO49" s="8">
-        <f t="shared" si="206"/>
-        <v>2965.5492068674507</v>
+        <f t="shared" si="208"/>
+        <v>3226.1858689890009</v>
       </c>
       <c r="AP49" s="8">
-        <f t="shared" si="206"/>
-        <v>3968.1594291145584</v>
+        <f t="shared" si="208"/>
+        <v>4313.7840628063705</v>
       </c>
       <c r="AQ49" s="8">
-        <f t="shared" si="206"/>
-        <v>4919.1722637447892</v>
+        <f t="shared" si="208"/>
+        <v>5344.9526927549259</v>
       </c>
       <c r="AR49" s="8">
-        <f t="shared" si="206"/>
-        <v>5498.0628166149654</v>
+        <f t="shared" si="208"/>
+        <v>5965.4283333239773</v>
       </c>
       <c r="AS49" s="8">
-        <f t="shared" si="206"/>
-        <v>6208.4268346553099</v>
+        <f t="shared" si="208"/>
+        <v>6733.210936983457</v>
       </c>
       <c r="AT49" s="8">
-        <f t="shared" si="206"/>
-        <v>6769.6206642721791</v>
+        <f t="shared" si="208"/>
+        <v>7475.8860666760784</v>
       </c>
       <c r="AU49" s="8">
-        <f t="shared" si="206"/>
-        <v>7244.3525576028351</v>
+        <f t="shared" si="208"/>
+        <v>8297.177962551681</v>
       </c>
       <c r="AV49" s="8">
-        <f t="shared" si="206"/>
-        <v>7682.5140194605001</v>
+        <f t="shared" si="208"/>
+        <v>9205.4764758385645</v>
       </c>
       <c r="AW49" s="8">
-        <f t="shared" si="206"/>
-        <v>8075.7192281834668</v>
+        <f t="shared" si="208"/>
+        <v>10210.087027995507</v>
       </c>
     </row>
     <row r="50" spans="2:141" x14ac:dyDescent="0.3">
@@ -7317,20 +7392,24 @@
       <c r="W50" s="5">
         <v>2.7</v>
       </c>
+      <c r="X50" s="5">
+        <f>X72-W50</f>
+        <v>2.8</v>
+      </c>
       <c r="AA50" s="5">
         <v>6.2</v>
       </c>
       <c r="AB50" s="5">
-        <f>AA50*1.05</f>
-        <v>6.5100000000000007</v>
+        <f>AB72-AA50</f>
+        <v>7.6000000000000005</v>
       </c>
       <c r="AC50" s="5">
-        <f t="shared" ref="AC50:AD50" si="207">AB50*1.05</f>
-        <v>6.8355000000000006</v>
+        <f>AB50*1.15</f>
+        <v>8.74</v>
       </c>
       <c r="AD50" s="5">
-        <f t="shared" si="207"/>
-        <v>7.1772750000000007</v>
+        <f>AC50*1.15</f>
+        <v>10.051</v>
       </c>
       <c r="AJ50" s="5">
         <v>40</v>
@@ -7343,48 +7422,48 @@
         <v>12.6</v>
       </c>
       <c r="AM50" s="5">
-        <f t="shared" si="200"/>
-        <v>26.722775000000002</v>
+        <f t="shared" si="202"/>
+        <v>32.591000000000001</v>
       </c>
       <c r="AN50" s="5">
         <f>AM50*1.15</f>
-        <v>30.731191249999998</v>
+        <v>37.479649999999999</v>
       </c>
       <c r="AO50" s="5">
-        <f t="shared" ref="AO50:AW50" si="208">AN50*1.15</f>
-        <v>35.340869937499996</v>
+        <f t="shared" ref="AO50:AW50" si="209">AN50*1.15</f>
+        <v>43.101597499999997</v>
       </c>
       <c r="AP50" s="5">
-        <f t="shared" si="208"/>
-        <v>40.642000428124994</v>
+        <f t="shared" si="209"/>
+        <v>49.566837124999992</v>
       </c>
       <c r="AQ50" s="5">
-        <f t="shared" si="208"/>
-        <v>46.73830049234374</v>
+        <f t="shared" si="209"/>
+        <v>57.001862693749985</v>
       </c>
       <c r="AR50" s="5">
-        <f t="shared" si="208"/>
-        <v>53.749045566195299</v>
+        <f t="shared" si="209"/>
+        <v>65.552142097812478</v>
       </c>
       <c r="AS50" s="5">
-        <f t="shared" si="208"/>
-        <v>61.811402401124589</v>
+        <f t="shared" si="209"/>
+        <v>75.384963412484339</v>
       </c>
       <c r="AT50" s="5">
-        <f t="shared" si="208"/>
-        <v>71.083112761293265</v>
+        <f t="shared" si="209"/>
+        <v>86.692707924356981</v>
       </c>
       <c r="AU50" s="5">
-        <f t="shared" si="208"/>
-        <v>81.745579675487249</v>
+        <f t="shared" si="209"/>
+        <v>99.696614113010526</v>
       </c>
       <c r="AV50" s="5">
-        <f t="shared" si="208"/>
-        <v>94.007416626810326</v>
+        <f t="shared" si="209"/>
+        <v>114.6511062299621</v>
       </c>
       <c r="AW50" s="5">
-        <f t="shared" si="208"/>
-        <v>108.10852912083186</v>
+        <f t="shared" si="209"/>
+        <v>131.84877216445639</v>
       </c>
     </row>
     <row r="51" spans="2:141" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -7395,21 +7474,25 @@
         <f>W49-W50</f>
         <v>126.89999999999999</v>
       </c>
+      <c r="X51" s="8">
+        <f>X49-X50</f>
+        <v>141.19999999999996</v>
+      </c>
       <c r="AA51" s="8">
         <f>AA49-AA50</f>
         <v>302.09999999999997</v>
       </c>
       <c r="AB51" s="8">
         <f>AB49-AB50</f>
-        <v>418.84261400000003</v>
+        <v>528.30000000000007</v>
       </c>
       <c r="AC51" s="8">
-        <f t="shared" ref="AC51:AD51" si="209">AC49-AC50</f>
-        <v>453.56932500000011</v>
+        <f t="shared" ref="AC51:AD51" si="210">AC49-AC50</f>
+        <v>509.9531300000001</v>
       </c>
       <c r="AD51" s="8">
-        <f t="shared" si="209"/>
-        <v>376.47183150000018</v>
+        <f t="shared" si="210"/>
+        <v>431.77304000000015</v>
       </c>
       <c r="AJ51" s="8">
         <f>AJ49-AJ50</f>
@@ -7424,453 +7507,640 @@
         <v>1137.4000000000003</v>
       </c>
       <c r="AM51" s="8">
-        <f t="shared" ref="AM51:AW51" si="210">AM49-AM50</f>
-        <v>1550.9837705000002</v>
+        <f t="shared" ref="AM51:AW51" si="211">AM49-AM50</f>
+        <v>1772.12617</v>
       </c>
       <c r="AN51" s="8">
-        <f t="shared" si="210"/>
-        <v>2110.9734681750006</v>
+        <f t="shared" si="211"/>
+        <v>2294.8566685000005</v>
       </c>
       <c r="AO51" s="8">
-        <f t="shared" si="210"/>
-        <v>2930.2083369299507</v>
+        <f t="shared" si="211"/>
+        <v>3183.0842714890009</v>
       </c>
       <c r="AP51" s="8">
-        <f t="shared" si="210"/>
-        <v>3927.5174286864335</v>
+        <f t="shared" si="211"/>
+        <v>4264.2172256813701</v>
       </c>
       <c r="AQ51" s="8">
-        <f t="shared" si="210"/>
-        <v>4872.4339632524452</v>
+        <f t="shared" si="211"/>
+        <v>5287.950830061176</v>
       </c>
       <c r="AR51" s="8">
-        <f t="shared" si="210"/>
-        <v>5444.3137710487699</v>
+        <f t="shared" si="211"/>
+        <v>5899.8761912261652</v>
       </c>
       <c r="AS51" s="8">
-        <f t="shared" si="210"/>
-        <v>6146.6154322541852</v>
+        <f t="shared" si="211"/>
+        <v>6657.8259735709726</v>
       </c>
       <c r="AT51" s="8">
-        <f t="shared" si="210"/>
-        <v>6698.5375515108854</v>
+        <f t="shared" si="211"/>
+        <v>7389.1933587517215</v>
       </c>
       <c r="AU51" s="8">
-        <f t="shared" si="210"/>
-        <v>7162.6069779273475</v>
+        <f t="shared" si="211"/>
+        <v>8197.4813484386705</v>
       </c>
       <c r="AV51" s="8">
-        <f t="shared" si="210"/>
-        <v>7588.5066028336896</v>
+        <f t="shared" si="211"/>
+        <v>9090.8253696086031</v>
       </c>
       <c r="AW51" s="8">
-        <f t="shared" si="210"/>
-        <v>7967.6106990626349</v>
+        <f t="shared" si="211"/>
+        <v>10078.238255831051</v>
       </c>
       <c r="AX51" s="1">
         <f>AW51*(1+$AZ$25)</f>
-        <v>7887.9345920720089</v>
+        <v>9977.4558732727401</v>
       </c>
       <c r="AY51" s="1">
-        <f t="shared" ref="AY51:DJ51" si="211">AX51*(1+$AZ$25)</f>
-        <v>7809.0552461512889</v>
+        <f t="shared" ref="AY51:DJ51" si="212">AX51*(1+$AZ$25)</f>
+        <v>9877.681314540012</v>
       </c>
       <c r="AZ51" s="1">
-        <f t="shared" si="211"/>
-        <v>7730.9646936897761</v>
+        <f t="shared" si="212"/>
+        <v>9778.9045013946125</v>
       </c>
       <c r="BA51" s="1">
-        <f t="shared" si="211"/>
-        <v>7653.6550467528787</v>
+        <f t="shared" si="212"/>
+        <v>9681.1154563806667</v>
       </c>
       <c r="BB51" s="1">
-        <f t="shared" si="211"/>
-        <v>7577.1184962853495</v>
+        <f t="shared" si="212"/>
+        <v>9584.3043018168592</v>
       </c>
       <c r="BC51" s="1">
-        <f t="shared" si="211"/>
-        <v>7501.3473113224964</v>
+        <f t="shared" si="212"/>
+        <v>9488.4612587986903</v>
       </c>
       <c r="BD51" s="1">
-        <f t="shared" si="211"/>
-        <v>7426.3338382092716</v>
+        <f t="shared" si="212"/>
+        <v>9393.576646210704</v>
       </c>
       <c r="BE51" s="1">
-        <f t="shared" si="211"/>
-        <v>7352.0704998271785</v>
+        <f t="shared" si="212"/>
+        <v>9299.6408797485965</v>
       </c>
       <c r="BF51" s="1">
-        <f t="shared" si="211"/>
-        <v>7278.5497948289067</v>
+        <f t="shared" si="212"/>
+        <v>9206.6444709511106</v>
       </c>
       <c r="BG51" s="1">
-        <f t="shared" si="211"/>
-        <v>7205.7642968806176</v>
+        <f t="shared" si="212"/>
+        <v>9114.5780262415992</v>
       </c>
       <c r="BH51" s="1">
-        <f t="shared" si="211"/>
-        <v>7133.7066539118114</v>
+        <f t="shared" si="212"/>
+        <v>9023.4322459791838</v>
       </c>
       <c r="BI51" s="1">
-        <f t="shared" si="211"/>
-        <v>7062.3695873726929</v>
+        <f t="shared" si="212"/>
+        <v>8933.1979235193921</v>
       </c>
       <c r="BJ51" s="1">
-        <f t="shared" si="211"/>
-        <v>6991.7458914989656</v>
+        <f t="shared" si="212"/>
+        <v>8843.8659442841981</v>
       </c>
       <c r="BK51" s="1">
-        <f t="shared" si="211"/>
-        <v>6921.8284325839759</v>
+        <f t="shared" si="212"/>
+        <v>8755.4272848413566</v>
       </c>
       <c r="BL51" s="1">
-        <f t="shared" si="211"/>
-        <v>6852.6101482581362</v>
+        <f t="shared" si="212"/>
+        <v>8667.8730119929423</v>
       </c>
       <c r="BM51" s="1">
-        <f t="shared" si="211"/>
-        <v>6784.0840467755552</v>
+        <f t="shared" si="212"/>
+        <v>8581.1942818730131</v>
       </c>
       <c r="BN51" s="1">
-        <f t="shared" si="211"/>
-        <v>6716.2432063077995</v>
+        <f t="shared" si="212"/>
+        <v>8495.3823390542821</v>
       </c>
       <c r="BO51" s="1">
-        <f t="shared" si="211"/>
-        <v>6649.0807742447214</v>
+        <f t="shared" si="212"/>
+        <v>8410.4285156637397</v>
       </c>
       <c r="BP51" s="1">
-        <f t="shared" si="211"/>
-        <v>6582.5899665022744</v>
+        <f t="shared" si="212"/>
+        <v>8326.3242305071017</v>
       </c>
       <c r="BQ51" s="1">
-        <f t="shared" si="211"/>
-        <v>6516.7640668372514</v>
+        <f t="shared" si="212"/>
+        <v>8243.0609882020308</v>
       </c>
       <c r="BR51" s="1">
-        <f t="shared" si="211"/>
-        <v>6451.5964261688787</v>
+        <f t="shared" si="212"/>
+        <v>8160.6303783200101</v>
       </c>
       <c r="BS51" s="1">
-        <f t="shared" si="211"/>
-        <v>6387.0804619071896</v>
+        <f t="shared" si="212"/>
+        <v>8079.0240745368101</v>
       </c>
       <c r="BT51" s="1">
-        <f t="shared" si="211"/>
-        <v>6323.2096572881173</v>
+        <f t="shared" si="212"/>
+        <v>7998.2338337914416</v>
       </c>
       <c r="BU51" s="1">
-        <f t="shared" si="211"/>
-        <v>6259.977560715236</v>
+        <f t="shared" si="212"/>
+        <v>7918.2514954535272</v>
       </c>
       <c r="BV51" s="1">
-        <f t="shared" si="211"/>
-        <v>6197.377785108084</v>
+        <f t="shared" si="212"/>
+        <v>7839.0689804989916</v>
       </c>
       <c r="BW51" s="1">
-        <f t="shared" si="211"/>
-        <v>6135.4040072570033</v>
+        <f t="shared" si="212"/>
+        <v>7760.6782906940016</v>
       </c>
       <c r="BX51" s="1">
-        <f t="shared" si="211"/>
-        <v>6074.0499671844336</v>
+        <f t="shared" si="212"/>
+        <v>7683.0715077870618</v>
       </c>
       <c r="BY51" s="1">
-        <f t="shared" si="211"/>
-        <v>6013.3094675125894</v>
+        <f t="shared" si="212"/>
+        <v>7606.2407927091908</v>
       </c>
       <c r="BZ51" s="1">
-        <f t="shared" si="211"/>
-        <v>5953.1763728374635</v>
+        <f t="shared" si="212"/>
+        <v>7530.1783847820989</v>
       </c>
       <c r="CA51" s="1">
-        <f t="shared" si="211"/>
-        <v>5893.6446091090893</v>
+        <f t="shared" si="212"/>
+        <v>7454.876600934278</v>
       </c>
       <c r="CB51" s="1">
-        <f t="shared" si="211"/>
-        <v>5834.7081630179982</v>
+        <f t="shared" si="212"/>
+        <v>7380.3278349249349</v>
       </c>
       <c r="CC51" s="1">
-        <f t="shared" si="211"/>
-        <v>5776.3610813878186</v>
+        <f t="shared" si="212"/>
+        <v>7306.5245565756859</v>
       </c>
       <c r="CD51" s="1">
-        <f t="shared" si="211"/>
-        <v>5718.59747057394</v>
+        <f t="shared" si="212"/>
+        <v>7233.4593110099286</v>
       </c>
       <c r="CE51" s="1">
-        <f t="shared" si="211"/>
-        <v>5661.4114958682003</v>
+        <f t="shared" si="212"/>
+        <v>7161.1247178998292</v>
       </c>
       <c r="CF51" s="1">
-        <f t="shared" si="211"/>
-        <v>5604.7973809095183</v>
+        <f t="shared" si="212"/>
+        <v>7089.5134707208308</v>
       </c>
       <c r="CG51" s="1">
-        <f t="shared" si="211"/>
-        <v>5548.749407100423</v>
+        <f t="shared" si="212"/>
+        <v>7018.6183360136229</v>
       </c>
       <c r="CH51" s="1">
-        <f t="shared" si="211"/>
-        <v>5493.2619130294188</v>
+        <f t="shared" si="212"/>
+        <v>6948.4321526534868</v>
       </c>
       <c r="CI51" s="1">
-        <f t="shared" si="211"/>
-        <v>5438.3292938991244</v>
+        <f t="shared" si="212"/>
+        <v>6878.9478311269522</v>
       </c>
       <c r="CJ51" s="1">
-        <f t="shared" si="211"/>
-        <v>5383.9460009601335</v>
+        <f t="shared" si="212"/>
+        <v>6810.1583528156825</v>
       </c>
       <c r="CK51" s="1">
-        <f t="shared" si="211"/>
-        <v>5330.1065409505318</v>
+        <f t="shared" si="212"/>
+        <v>6742.0567692875256</v>
       </c>
       <c r="CL51" s="1">
-        <f t="shared" si="211"/>
-        <v>5276.8054755410267</v>
+        <f t="shared" si="212"/>
+        <v>6674.6362015946506</v>
       </c>
       <c r="CM51" s="1">
-        <f t="shared" si="211"/>
-        <v>5224.0374207856166</v>
+        <f t="shared" si="212"/>
+        <v>6607.8898395787037</v>
       </c>
       <c r="CN51" s="1">
-        <f t="shared" si="211"/>
-        <v>5171.7970465777607</v>
+        <f t="shared" si="212"/>
+        <v>6541.8109411829164</v>
       </c>
       <c r="CO51" s="1">
-        <f t="shared" si="211"/>
-        <v>5120.0790761119833</v>
+        <f t="shared" si="212"/>
+        <v>6476.392831771087</v>
       </c>
       <c r="CP51" s="1">
-        <f t="shared" si="211"/>
-        <v>5068.8782853508637</v>
+        <f t="shared" si="212"/>
+        <v>6411.6289034533756</v>
       </c>
       <c r="CQ51" s="1">
-        <f t="shared" si="211"/>
-        <v>5018.1895024973546</v>
+        <f t="shared" si="212"/>
+        <v>6347.5126144188416</v>
       </c>
       <c r="CR51" s="1">
-        <f t="shared" si="211"/>
-        <v>4968.0076074723811</v>
+        <f t="shared" si="212"/>
+        <v>6284.0374882746528</v>
       </c>
       <c r="CS51" s="1">
-        <f t="shared" si="211"/>
-        <v>4918.3275313976574</v>
+        <f t="shared" si="212"/>
+        <v>6221.197113391906</v>
       </c>
       <c r="CT51" s="1">
-        <f t="shared" si="211"/>
-        <v>4869.1442560836804</v>
+        <f t="shared" si="212"/>
+        <v>6158.9851422579868</v>
       </c>
       <c r="CU51" s="1">
-        <f t="shared" si="211"/>
-        <v>4820.4528135228438</v>
+        <f t="shared" si="212"/>
+        <v>6097.3952908354067</v>
       </c>
       <c r="CV51" s="1">
-        <f t="shared" si="211"/>
-        <v>4772.2482853876154</v>
+        <f t="shared" si="212"/>
+        <v>6036.4213379270523</v>
       </c>
       <c r="CW51" s="1">
-        <f t="shared" si="211"/>
-        <v>4724.5258025337389</v>
+        <f t="shared" si="212"/>
+        <v>5976.0571245477813</v>
       </c>
       <c r="CX51" s="1">
-        <f t="shared" si="211"/>
-        <v>4677.2805445084014</v>
+        <f t="shared" si="212"/>
+        <v>5916.2965533023034</v>
       </c>
       <c r="CY51" s="1">
-        <f t="shared" si="211"/>
-        <v>4630.5077390633169</v>
+        <f t="shared" si="212"/>
+        <v>5857.13358776928</v>
       </c>
       <c r="CZ51" s="1">
-        <f t="shared" si="211"/>
-        <v>4584.2026616726835</v>
+        <f t="shared" si="212"/>
+        <v>5798.562251891587</v>
       </c>
       <c r="DA51" s="1">
-        <f t="shared" si="211"/>
-        <v>4538.3606350559567</v>
+        <f t="shared" si="212"/>
+        <v>5740.5766293726711</v>
       </c>
       <c r="DB51" s="1">
-        <f t="shared" si="211"/>
-        <v>4492.9770287053971</v>
+        <f t="shared" si="212"/>
+        <v>5683.1708630789444</v>
       </c>
       <c r="DC51" s="1">
-        <f t="shared" si="211"/>
-        <v>4448.0472584183426</v>
+        <f t="shared" si="212"/>
+        <v>5626.3391544481547</v>
       </c>
       <c r="DD51" s="1">
-        <f t="shared" si="211"/>
-        <v>4403.5667858341594</v>
+        <f t="shared" si="212"/>
+        <v>5570.0757629036734</v>
       </c>
       <c r="DE51" s="1">
-        <f t="shared" si="211"/>
-        <v>4359.5311179758182</v>
+        <f t="shared" si="212"/>
+        <v>5514.3750052746364</v>
       </c>
       <c r="DF51" s="1">
-        <f t="shared" si="211"/>
-        <v>4315.9358067960602</v>
+        <f t="shared" si="212"/>
+        <v>5459.23125522189</v>
       </c>
       <c r="DG51" s="1">
-        <f t="shared" si="211"/>
-        <v>4272.7764487280992</v>
+        <f t="shared" si="212"/>
+        <v>5404.6389426696715</v>
       </c>
       <c r="DH51" s="1">
-        <f t="shared" si="211"/>
-        <v>4230.0486842408181</v>
+        <f t="shared" si="212"/>
+        <v>5350.5925532429746</v>
       </c>
       <c r="DI51" s="1">
-        <f t="shared" si="211"/>
-        <v>4187.7481973984095</v>
+        <f t="shared" si="212"/>
+        <v>5297.0866277105451</v>
       </c>
       <c r="DJ51" s="1">
-        <f t="shared" si="211"/>
-        <v>4145.8707154244257</v>
+        <f t="shared" si="212"/>
+        <v>5244.1157614334397</v>
       </c>
       <c r="DK51" s="1">
-        <f t="shared" ref="DK51:EK51" si="212">DJ51*(1+$AZ$25)</f>
-        <v>4104.4120082701811</v>
+        <f t="shared" ref="DK51:EK51" si="213">DJ51*(1+$AZ$25)</f>
+        <v>5191.674603819105</v>
       </c>
       <c r="DL51" s="1">
-        <f t="shared" si="212"/>
-        <v>4063.3678881874794</v>
+        <f t="shared" si="213"/>
+        <v>5139.7578577809136</v>
       </c>
       <c r="DM51" s="1">
-        <f t="shared" si="212"/>
-        <v>4022.7342093056045</v>
+        <f t="shared" si="213"/>
+        <v>5088.3602792031043</v>
       </c>
       <c r="DN51" s="1">
-        <f t="shared" si="212"/>
-        <v>3982.5068672125485</v>
+        <f t="shared" si="213"/>
+        <v>5037.4766764110727</v>
       </c>
       <c r="DO51" s="1">
-        <f t="shared" si="212"/>
-        <v>3942.6817985404232</v>
+        <f t="shared" si="213"/>
+        <v>4987.1019096469618</v>
       </c>
       <c r="DP51" s="1">
-        <f t="shared" si="212"/>
-        <v>3903.2549805550188</v>
+        <f t="shared" si="213"/>
+        <v>4937.2308905504924</v>
       </c>
       <c r="DQ51" s="1">
-        <f t="shared" si="212"/>
-        <v>3864.2224307494685</v>
+        <f t="shared" si="213"/>
+        <v>4887.8585816449877</v>
       </c>
       <c r="DR51" s="1">
-        <f t="shared" si="212"/>
-        <v>3825.5802064419736</v>
+        <f t="shared" si="213"/>
+        <v>4838.9799958285375</v>
       </c>
       <c r="DS51" s="1">
-        <f t="shared" si="212"/>
-        <v>3787.3244043775539</v>
+        <f t="shared" si="213"/>
+        <v>4790.5901958702525</v>
       </c>
       <c r="DT51" s="1">
-        <f t="shared" si="212"/>
-        <v>3749.4511603337783</v>
+        <f t="shared" si="213"/>
+        <v>4742.6842939115495</v>
       </c>
       <c r="DU51" s="1">
-        <f t="shared" si="212"/>
-        <v>3711.9566487304405</v>
+        <f t="shared" si="213"/>
+        <v>4695.2574509724336</v>
       </c>
       <c r="DV51" s="1">
-        <f t="shared" si="212"/>
-        <v>3674.8370822431361</v>
+        <f t="shared" si="213"/>
+        <v>4648.3048764627092</v>
       </c>
       <c r="DW51" s="1">
-        <f t="shared" si="212"/>
-        <v>3638.0887114207048</v>
+        <f t="shared" si="213"/>
+        <v>4601.8218276980824</v>
       </c>
       <c r="DX51" s="1">
-        <f t="shared" si="212"/>
-        <v>3601.707824306498</v>
+        <f t="shared" si="213"/>
+        <v>4555.8036094211011</v>
       </c>
       <c r="DY51" s="1">
-        <f t="shared" si="212"/>
-        <v>3565.6907460634329</v>
+        <f t="shared" si="213"/>
+        <v>4510.2455733268898</v>
       </c>
       <c r="DZ51" s="1">
-        <f t="shared" si="212"/>
-        <v>3530.0338386027984</v>
+        <f t="shared" si="213"/>
+        <v>4465.1431175936204</v>
       </c>
       <c r="EA51" s="1">
-        <f t="shared" si="212"/>
-        <v>3494.7335002167702</v>
+        <f t="shared" si="213"/>
+        <v>4420.4916864176839</v>
       </c>
       <c r="EB51" s="1">
-        <f t="shared" si="212"/>
-        <v>3459.7861652146025</v>
+        <f t="shared" si="213"/>
+        <v>4376.2867695535069</v>
       </c>
       <c r="EC51" s="1">
-        <f t="shared" si="212"/>
-        <v>3425.1883035624564</v>
+        <f t="shared" si="213"/>
+        <v>4332.5239018579714</v>
       </c>
       <c r="ED51" s="1">
-        <f t="shared" si="212"/>
-        <v>3390.9364205268316</v>
+        <f t="shared" si="213"/>
+        <v>4289.1986628393915</v>
       </c>
       <c r="EE51" s="1">
-        <f t="shared" si="212"/>
-        <v>3357.0270563215631</v>
+        <f t="shared" si="213"/>
+        <v>4246.3066762109975</v>
       </c>
       <c r="EF51" s="1">
-        <f t="shared" si="212"/>
-        <v>3323.4567857583475</v>
+        <f t="shared" si="213"/>
+        <v>4203.843609448887</v>
       </c>
       <c r="EG51" s="1">
-        <f t="shared" si="212"/>
-        <v>3290.222217900764</v>
+        <f t="shared" si="213"/>
+        <v>4161.805173354398</v>
       </c>
       <c r="EH51" s="1">
-        <f t="shared" si="212"/>
-        <v>3257.3199957217562</v>
+        <f t="shared" si="213"/>
+        <v>4120.1871216208538</v>
       </c>
       <c r="EI51" s="1">
-        <f t="shared" si="212"/>
-        <v>3224.7467957645385</v>
+        <f t="shared" si="213"/>
+        <v>4078.9852504046453</v>
       </c>
       <c r="EJ51" s="1">
-        <f t="shared" si="212"/>
-        <v>3192.4993278068932</v>
+        <f t="shared" si="213"/>
+        <v>4038.1953979005989</v>
       </c>
       <c r="EK51" s="1">
-        <f t="shared" si="212"/>
-        <v>3160.5743345288242</v>
+        <f t="shared" si="213"/>
+        <v>3997.8134439215928</v>
       </c>
     </row>
     <row r="53" spans="2:141" x14ac:dyDescent="0.3">
-      <c r="AZ53" s="5">
-        <f>NPV(AZ26,AM51:EK51)</f>
-        <v>96607.241927176132</v>
-      </c>
-    </row>
-    <row r="54" spans="2:141" x14ac:dyDescent="0.3">
-      <c r="AZ54" s="5">
-        <f>Main!D8</f>
-        <v>5230</v>
+      <c r="B53" t="s">
+        <v>91</v>
+      </c>
+      <c r="AA53" s="9">
+        <f>AA35/W35-1</f>
+        <v>0.2354813046937152</v>
+      </c>
+      <c r="AB53" s="9">
+        <f>AB35/X35-1</f>
+        <v>0.1291460832745237</v>
       </c>
     </row>
     <row r="55" spans="2:141" x14ac:dyDescent="0.3">
       <c r="AZ55" s="5">
-        <f>AZ53+AZ54</f>
-        <v>101837.24192717613</v>
+        <f>NPV(AZ26,AM51:EK51)</f>
+        <v>141857.03607088616</v>
       </c>
     </row>
     <row r="56" spans="2:141" x14ac:dyDescent="0.3">
-      <c r="AZ56" s="4">
-        <f>AZ55/AW19</f>
-        <v>43.358982384798459</v>
+      <c r="B56" t="s">
+        <v>74</v>
+      </c>
+      <c r="W56" s="5"/>
+      <c r="X56" s="5">
+        <v>16.5</v>
+      </c>
+      <c r="AB56" s="5">
+        <v>13.2</v>
+      </c>
+      <c r="AZ56" s="5">
+        <f>Main!D8</f>
+        <v>5230</v>
       </c>
     </row>
     <row r="57" spans="2:141" x14ac:dyDescent="0.3">
-      <c r="AZ57" s="4">
-        <f>Main!D3</f>
-        <v>127.59</v>
+      <c r="B57" t="s">
+        <v>75</v>
+      </c>
+      <c r="W57" s="5"/>
+      <c r="X57" s="5">
+        <v>267.39999999999998</v>
+      </c>
+      <c r="AB57" s="5">
+        <v>315.3</v>
+      </c>
+      <c r="AZ57" s="5">
+        <f>AZ55+AZ56</f>
+        <v>147087.03607088616</v>
       </c>
     </row>
     <row r="58" spans="2:141" x14ac:dyDescent="0.3">
-      <c r="AZ58" s="10">
-        <f>AZ56/AZ57-1</f>
-        <v>-0.66016943032527275</v>
-      </c>
+      <c r="B58" t="s">
+        <v>76</v>
+      </c>
+      <c r="W58" s="5"/>
+      <c r="X58" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="5">
+        <v>0</v>
+      </c>
+      <c r="AZ58" s="4">
+        <f>AZ57/AW19</f>
+        <v>62.187990897550385</v>
+      </c>
+    </row>
+    <row r="59" spans="2:141" x14ac:dyDescent="0.3">
+      <c r="B59" t="s">
+        <v>77</v>
+      </c>
+      <c r="W59" s="5"/>
+      <c r="X59" s="5">
+        <v>20</v>
+      </c>
+      <c r="AB59" s="5">
+        <v>-0.5</v>
+      </c>
+      <c r="AZ59" s="4">
+        <f>Main!D3</f>
+        <v>182.39</v>
+      </c>
+    </row>
+    <row r="60" spans="2:141" x14ac:dyDescent="0.3">
+      <c r="B60" t="s">
+        <v>78</v>
+      </c>
+      <c r="W60" s="5"/>
+      <c r="X60" s="5">
+        <v>-26.5</v>
+      </c>
+      <c r="AB60" s="5">
+        <v>-24.4</v>
+      </c>
+      <c r="AZ60" s="10">
+        <f>AZ58/AZ59-1</f>
+        <v>-0.65903837437606017</v>
+      </c>
+    </row>
+    <row r="61" spans="2:141" x14ac:dyDescent="0.3">
+      <c r="B61" t="s">
+        <v>79</v>
+      </c>
+      <c r="W61" s="5"/>
+      <c r="X61" s="5">
+        <v>11.4</v>
+      </c>
+      <c r="AB61" s="5">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="62" spans="2:141" x14ac:dyDescent="0.3">
+      <c r="B62" t="s">
+        <v>80</v>
+      </c>
+      <c r="W62" s="5"/>
+      <c r="X62" s="5">
+        <v>-298.3</v>
+      </c>
+      <c r="AB62" s="5">
+        <v>-163.5</v>
+      </c>
+    </row>
+    <row r="63" spans="2:141" x14ac:dyDescent="0.3">
+      <c r="B63" t="s">
+        <v>81</v>
+      </c>
+      <c r="W63" s="5"/>
+      <c r="X63" s="5"/>
+      <c r="AB63" s="5"/>
+    </row>
+    <row r="64" spans="2:141" x14ac:dyDescent="0.3">
+      <c r="B64" t="s">
+        <v>82</v>
+      </c>
+      <c r="W64" s="5"/>
+      <c r="X64" s="5">
+        <v>2.8</v>
+      </c>
+      <c r="AB64" s="5">
+        <v>-7.3</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B65" t="s">
+        <v>83</v>
+      </c>
+      <c r="W65" s="5"/>
+      <c r="X65" s="5">
+        <v>22.8</v>
+      </c>
+      <c r="AB65" s="5">
+        <v>48.2</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B66" t="s">
+        <v>84</v>
+      </c>
+      <c r="W66" s="5"/>
+      <c r="X66" s="5"/>
+      <c r="AB66" s="5"/>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B67" t="s">
+        <v>85</v>
+      </c>
+      <c r="W67" s="5"/>
+      <c r="X67" s="5">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="AB67" s="5">
+        <v>120.7</v>
+      </c>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B68" t="s">
+        <v>86</v>
+      </c>
+      <c r="W68" s="5"/>
+      <c r="X68" s="5"/>
+      <c r="AB68" s="5"/>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B69" t="s">
+        <v>76</v>
+      </c>
+      <c r="W69" s="5"/>
+      <c r="X69" s="5"/>
+      <c r="AB69" s="5"/>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B70" t="s">
+        <v>87</v>
+      </c>
+      <c r="W70" s="5"/>
+      <c r="X70" s="5">
+        <v>-17.3</v>
+      </c>
+      <c r="AB70" s="5">
+        <v>-24.9</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="W71" s="8"/>
+      <c r="X71" s="8"/>
+      <c r="AB71" s="5"/>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B72" t="s">
+        <v>89</v>
+      </c>
+      <c r="W72" s="5"/>
+      <c r="X72" s="5">
+        <v>5.5</v>
+      </c>
+      <c r="AB72" s="5">
+        <v>13.8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="W73" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/Financial Analysis/PLTR.xlsx
+++ b/Financial Analysis/PLTR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5F75BA6-639A-4EAD-9D2C-9B295DCCB37A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9320AA0-3BA0-4ED5-8BF6-9FB9A4179135}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{F38281D2-A2D5-4B11-829A-E3DB86132867}"/>
   </bookViews>
@@ -415,13 +415,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>28</xdr:col>
+      <xdr:col>29</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>28</xdr:col>
+      <xdr:col>29</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
       <xdr:row>62</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
@@ -439,7 +439,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="18166080" y="0"/>
+          <a:off x="18775680" y="0"/>
           <a:ext cx="0" cy="11445240"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -839,17 +839,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="4">
-        <v>182.39</v>
+        <v>192.48</v>
       </c>
       <c r="E3" s="3">
-        <v>45920</v>
+        <v>45965</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45920</v>
+        <v>45965</v>
       </c>
       <c r="G3" s="3">
-        <v>45967</v>
+        <v>45692</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -857,11 +857,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="5">
-        <f>2365.2</f>
-        <v>2365.1999999999998</v>
+        <f>2377.2</f>
+        <v>2377.1999999999998</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -870,7 +870,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>431388.82799999992</v>
+        <v>457563.45599999995</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -878,11 +878,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="5">
-        <f>2098.5+3131.5</f>
-        <v>5230</v>
+        <f>1616+4821.9</f>
+        <v>6437.9</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -902,7 +902,7 @@
       </c>
       <c r="D8" s="5">
         <f>D6-D7</f>
-        <v>5230</v>
+        <v>6437.9</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -911,7 +911,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>426158.82799999992</v>
+        <v>451125.55599999992</v>
       </c>
     </row>
   </sheetData>
@@ -1157,12 +1157,10 @@
         <v>1003.7</v>
       </c>
       <c r="AC3" s="8">
-        <f>Y3*1.52</f>
-        <v>1102.76</v>
+        <v>1181.0999999999999</v>
       </c>
       <c r="AD3" s="8">
-        <f>Z3*1.47</f>
-        <v>1216.425</v>
+        <v>1329</v>
       </c>
       <c r="AF3" s="8">
         <v>595.4</v>
@@ -1192,47 +1190,47 @@
       </c>
       <c r="AM3" s="8">
         <f>SUM(AA3:AD3)</f>
-        <v>4206.7849999999999</v>
+        <v>4397.7</v>
       </c>
       <c r="AN3" s="8">
-        <f>AM3*1.3</f>
-        <v>5468.8204999999998</v>
+        <f>AM3*1.45</f>
+        <v>6376.665</v>
       </c>
       <c r="AO3" s="8">
-        <f>AN3*1.27</f>
-        <v>6945.4020350000001</v>
+        <f>AN3*1.35</f>
+        <v>8608.4977500000005</v>
       </c>
       <c r="AP3" s="8">
-        <f>AO3*1.24</f>
-        <v>8612.2985234000007</v>
+        <f>AO3*1.3</f>
+        <v>11191.047075</v>
       </c>
       <c r="AQ3" s="8">
-        <f>AP3*1.18</f>
-        <v>10162.512257612001</v>
+        <f>AP3*1.25</f>
+        <v>13988.808843750001</v>
       </c>
       <c r="AR3" s="8">
-        <f>AQ3*1.14</f>
-        <v>11585.26397367768</v>
+        <f>AQ3*1.2</f>
+        <v>16786.5706125</v>
       </c>
       <c r="AS3" s="8">
-        <f>AR3*1.1</f>
-        <v>12743.790371045448</v>
+        <f>AR3*1.15</f>
+        <v>19304.556204375</v>
       </c>
       <c r="AT3" s="8">
         <f t="shared" ref="AT3:AW3" si="0">AS3*1.1</f>
-        <v>14018.169408149994</v>
+        <v>21235.0118248125</v>
       </c>
       <c r="AU3" s="8">
         <f t="shared" si="0"/>
-        <v>15419.986348964994</v>
+        <v>23358.513007293754</v>
       </c>
       <c r="AV3" s="8">
         <f t="shared" si="0"/>
-        <v>16961.984983861494</v>
+        <v>25694.36430802313</v>
       </c>
       <c r="AW3" s="8">
         <f t="shared" si="0"/>
-        <v>18658.183482247645</v>
+        <v>28263.800738825445</v>
       </c>
     </row>
     <row r="4" spans="2:49" x14ac:dyDescent="0.3">
@@ -1320,12 +1318,11 @@
         <v>192.9</v>
       </c>
       <c r="AC4" s="5">
-        <f t="shared" ref="AC4:AD4" si="1">AC3-AC5</f>
-        <v>220.55199999999991</v>
+        <v>207.3</v>
       </c>
       <c r="AD4" s="5">
-        <f t="shared" si="1"/>
-        <v>255.44924999999989</v>
+        <f t="shared" ref="AC4:AD4" si="1">AD3-AD5</f>
+        <v>279.08999999999992</v>
       </c>
       <c r="AF4" s="5">
         <v>165.4</v>
@@ -1355,47 +1352,47 @@
       </c>
       <c r="AM4" s="5">
         <f>SUM(AA4:AD4)</f>
-        <v>841.90124999999978</v>
+        <v>852.29</v>
       </c>
       <c r="AN4" s="5">
         <f t="shared" ref="AN4:AR4" si="2">AN3-AN5</f>
-        <v>1093.7640999999994</v>
+        <v>1211.5663500000001</v>
       </c>
       <c r="AO4" s="5">
         <f t="shared" si="2"/>
-        <v>1389.0804069999995</v>
+        <v>1635.6145724999997</v>
       </c>
       <c r="AP4" s="5">
         <f t="shared" si="2"/>
-        <v>1722.45970468</v>
+        <v>2126.2989442500002</v>
       </c>
       <c r="AQ4" s="5">
         <f t="shared" si="2"/>
-        <v>2032.5024515223995</v>
+        <v>2657.8736803124993</v>
       </c>
       <c r="AR4" s="5">
         <f t="shared" si="2"/>
-        <v>2317.0527947355349</v>
+        <v>3189.4484163749985</v>
       </c>
       <c r="AS4" s="5">
         <f t="shared" ref="AS4:AW4" si="3">AS3-AS5</f>
-        <v>2548.7580742090886</v>
+        <v>3667.8656788312492</v>
       </c>
       <c r="AT4" s="5">
         <f t="shared" si="3"/>
-        <v>2803.6338816299976</v>
+        <v>4034.6522467143732</v>
       </c>
       <c r="AU4" s="5">
         <f t="shared" si="3"/>
-        <v>3083.9972697929988</v>
+        <v>4438.1174713858127</v>
       </c>
       <c r="AV4" s="5">
         <f t="shared" si="3"/>
-        <v>3392.3969967722987</v>
+        <v>4881.9292185243939</v>
       </c>
       <c r="AW4" s="5">
         <f t="shared" si="3"/>
-        <v>3731.6366964495282</v>
+        <v>5370.1221403768322</v>
       </c>
     </row>
     <row r="5" spans="2:49" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1483,7 +1480,7 @@
         <v>499.79999999999995</v>
       </c>
       <c r="W5" s="8">
-        <f t="shared" ref="W5:AB5" si="11">W3-W4</f>
+        <f t="shared" ref="W5:AC5" si="11">W3-W4</f>
         <v>518</v>
       </c>
       <c r="X5" s="8">
@@ -1507,12 +1504,12 @@
         <v>810.80000000000007</v>
       </c>
       <c r="AC5" s="8">
-        <f t="shared" ref="AC5" si="12">AC3*0.8</f>
-        <v>882.20800000000008</v>
+        <f t="shared" si="11"/>
+        <v>973.8</v>
       </c>
       <c r="AD5" s="8">
         <f>AD3*0.79</f>
-        <v>960.97575000000006</v>
+        <v>1049.9100000000001</v>
       </c>
       <c r="AF5" s="8">
         <f>AF3-AF4</f>
@@ -1531,60 +1528,60 @@
         <v>1202.4000000000001</v>
       </c>
       <c r="AJ5" s="8">
-        <f t="shared" ref="AJ5:AM5" si="13">AJ3-AJ4</f>
+        <f t="shared" ref="AJ5:AM5" si="12">AJ3-AJ4</f>
         <v>1497.4</v>
       </c>
       <c r="AK5" s="8">
+        <f t="shared" si="12"/>
+        <v>1794.1</v>
+      </c>
+      <c r="AL5" s="8">
+        <f t="shared" si="12"/>
+        <v>2299.4</v>
+      </c>
+      <c r="AM5" s="8">
+        <f t="shared" si="12"/>
+        <v>3545.41</v>
+      </c>
+      <c r="AN5" s="8">
+        <f>AN3*0.81</f>
+        <v>5165.0986499999999</v>
+      </c>
+      <c r="AO5" s="8">
+        <f t="shared" ref="AO5:AW5" si="13">AO3*0.81</f>
+        <v>6972.8831775000008</v>
+      </c>
+      <c r="AP5" s="8">
         <f t="shared" si="13"/>
-        <v>1794.1</v>
-      </c>
-      <c r="AL5" s="8">
+        <v>9064.7481307500002</v>
+      </c>
+      <c r="AQ5" s="8">
         <f t="shared" si="13"/>
-        <v>2299.4</v>
-      </c>
-      <c r="AM5" s="8">
+        <v>11330.935163437502</v>
+      </c>
+      <c r="AR5" s="8">
         <f t="shared" si="13"/>
-        <v>3364.88375</v>
-      </c>
-      <c r="AN5" s="8">
-        <f>AN3*0.8</f>
-        <v>4375.0564000000004</v>
-      </c>
-      <c r="AO5" s="8">
-        <f t="shared" ref="AO5:AW5" si="14">AO3*0.8</f>
-        <v>5556.3216280000006</v>
-      </c>
-      <c r="AP5" s="8">
-        <f t="shared" si="14"/>
-        <v>6889.8388187200007</v>
-      </c>
-      <c r="AQ5" s="8">
-        <f t="shared" si="14"/>
-        <v>8130.0098060896016</v>
-      </c>
-      <c r="AR5" s="8">
-        <f t="shared" si="14"/>
-        <v>9268.2111789421451</v>
+        <v>13597.122196125001</v>
       </c>
       <c r="AS5" s="8">
-        <f t="shared" si="14"/>
-        <v>10195.03229683636</v>
+        <f t="shared" si="13"/>
+        <v>15636.69052554375</v>
       </c>
       <c r="AT5" s="8">
-        <f t="shared" si="14"/>
-        <v>11214.535526519996</v>
+        <f t="shared" si="13"/>
+        <v>17200.359578098127</v>
       </c>
       <c r="AU5" s="8">
-        <f t="shared" si="14"/>
-        <v>12335.989079171995</v>
+        <f t="shared" si="13"/>
+        <v>18920.395535907941</v>
       </c>
       <c r="AV5" s="8">
-        <f t="shared" si="14"/>
-        <v>13569.587987089195</v>
+        <f t="shared" si="13"/>
+        <v>20812.435089498736</v>
       </c>
       <c r="AW5" s="8">
-        <f t="shared" si="14"/>
-        <v>14926.546785798117</v>
+        <f t="shared" si="13"/>
+        <v>22893.678598448612</v>
       </c>
     </row>
     <row r="6" spans="2:49" x14ac:dyDescent="0.3">
@@ -1672,12 +1669,11 @@
         <v>243.8</v>
       </c>
       <c r="AC6" s="5">
-        <f>AC3*0.26</f>
-        <v>286.7176</v>
+        <v>274.60000000000002</v>
       </c>
       <c r="AD6" s="5">
-        <f>AD3*0.31</f>
-        <v>377.09174999999999</v>
+        <f>AD3*0.29</f>
+        <v>385.40999999999997</v>
       </c>
       <c r="AF6" s="5">
         <v>461.8</v>
@@ -1707,47 +1703,47 @@
       </c>
       <c r="AM6" s="5">
         <f>SUM(AA6:AD6)</f>
-        <v>1143.9093500000001</v>
+        <v>1140.1100000000001</v>
       </c>
       <c r="AN6" s="5">
-        <f>AN3*0.25</f>
-        <v>1367.205125</v>
+        <f>AN3*0.23</f>
+        <v>1466.6329500000002</v>
       </c>
       <c r="AO6" s="5">
-        <f>AO3*0.22</f>
-        <v>1527.9884477000001</v>
+        <f>AO3*0.21</f>
+        <v>1807.7845275</v>
       </c>
       <c r="AP6" s="5">
-        <f>AP3*0.19</f>
-        <v>1636.3367194460002</v>
+        <f>AP3*0.18</f>
+        <v>2014.3884734999999</v>
       </c>
       <c r="AQ6" s="5">
-        <f>AQ3*0.17</f>
-        <v>1727.6270837940403</v>
+        <f>AQ3*0.16</f>
+        <v>2238.2094150000003</v>
       </c>
       <c r="AR6" s="5">
-        <f>AR3*0.16</f>
-        <v>1853.6422357884289</v>
+        <f>AR3*0.14</f>
+        <v>2350.1198857500003</v>
       </c>
       <c r="AS6" s="5">
-        <f>AS3*0.15</f>
-        <v>1911.5685556568171</v>
+        <f>AS3*0.13</f>
+        <v>2509.5923065687502</v>
       </c>
       <c r="AT6" s="5">
-        <f>AT3*0.15</f>
-        <v>2102.7254112224991</v>
+        <f>AT3*0.12</f>
+        <v>2548.2014189775</v>
       </c>
       <c r="AU6" s="5">
-        <f t="shared" ref="AU6:AW6" si="15">AU3*0.15</f>
-        <v>2312.9979523447491</v>
+        <f>AU3*0.12</f>
+        <v>2803.0215608752505</v>
       </c>
       <c r="AV6" s="5">
-        <f t="shared" si="15"/>
-        <v>2544.2977475792241</v>
+        <f t="shared" ref="AV6:AW6" si="14">AV3*0.12</f>
+        <v>3083.3237169627755</v>
       </c>
       <c r="AW6" s="5">
-        <f t="shared" si="15"/>
-        <v>2798.7275223371466</v>
+        <f t="shared" si="14"/>
+        <v>3391.6560886590532</v>
       </c>
     </row>
     <row r="7" spans="2:49" x14ac:dyDescent="0.3">
@@ -1835,12 +1831,11 @@
         <v>135</v>
       </c>
       <c r="AC7" s="5">
-        <f t="shared" ref="AC7" si="16">Y7*1.25</f>
-        <v>147</v>
+        <v>144.19999999999999</v>
       </c>
       <c r="AD7" s="5">
-        <f>Z7*1.15</f>
-        <v>197.22499999999999</v>
+        <f>Z7*1.17</f>
+        <v>200.655</v>
       </c>
       <c r="AF7" s="5">
         <v>285.5</v>
@@ -1870,47 +1865,47 @@
       </c>
       <c r="AM7" s="5">
         <f>SUM(AA7:AD7)</f>
-        <v>614.125</v>
+        <v>614.755</v>
       </c>
       <c r="AN7" s="5">
-        <f>AM7*1.13</f>
-        <v>693.96124999999995</v>
+        <f>AM7*1.14</f>
+        <v>700.82069999999999</v>
       </c>
       <c r="AO7" s="5">
         <f>AN7*1.07</f>
-        <v>742.53853749999996</v>
+        <v>749.87814900000001</v>
       </c>
       <c r="AP7" s="5">
         <f>AO7*1.04</f>
-        <v>772.24007900000004</v>
+        <v>779.87327496</v>
       </c>
       <c r="AQ7" s="5">
         <f>AP7*1.03</f>
-        <v>795.40728137000008</v>
+        <v>803.26947320880004</v>
       </c>
       <c r="AR7" s="5">
-        <f t="shared" ref="AR7:AR8" si="17">AQ7*1.02</f>
-        <v>811.3154269974001</v>
+        <f t="shared" ref="AR7:AW7" si="15">AQ7*1.03</f>
+        <v>827.36755740506408</v>
       </c>
       <c r="AS7" s="5">
-        <f t="shared" ref="AS7:AS8" si="18">AR7*1.02</f>
-        <v>827.54173553734813</v>
+        <f t="shared" si="15"/>
+        <v>852.18858412721602</v>
       </c>
       <c r="AT7" s="5">
-        <f t="shared" ref="AT7:AT8" si="19">AS7*1.02</f>
-        <v>844.09257024809506</v>
+        <f t="shared" si="15"/>
+        <v>877.75424165103254</v>
       </c>
       <c r="AU7" s="5">
-        <f t="shared" ref="AU7:AU8" si="20">AT7*1.02</f>
-        <v>860.97442165305699</v>
+        <f t="shared" si="15"/>
+        <v>904.08686890056356</v>
       </c>
       <c r="AV7" s="5">
-        <f t="shared" ref="AV7:AV8" si="21">AU7*1.02</f>
-        <v>878.19391008611819</v>
+        <f t="shared" si="15"/>
+        <v>931.20947496758049</v>
       </c>
       <c r="AW7" s="5">
-        <f t="shared" ref="AW7:AW8" si="22">AV7*1.02</f>
-        <v>895.75778828784053</v>
+        <f t="shared" si="15"/>
+        <v>959.14575921660798</v>
       </c>
     </row>
     <row r="8" spans="2:49" x14ac:dyDescent="0.3">
@@ -1998,12 +1993,11 @@
         <v>162.6</v>
       </c>
       <c r="AC8" s="5">
-        <f t="shared" ref="AC8" si="23">Y8*1.15</f>
-        <v>159.50499999999997</v>
+        <v>161.69999999999999</v>
       </c>
       <c r="AD8" s="5">
-        <f>Z8*1.1</f>
-        <v>200.31</v>
+        <f>Z8*1.12</f>
+        <v>203.95200000000003</v>
       </c>
       <c r="AF8" s="5">
         <v>306.2</v>
@@ -2033,47 +2027,47 @@
       </c>
       <c r="AM8" s="5">
         <f>SUM(AA8:AD8)</f>
-        <v>686.01499999999987</v>
+        <v>691.85199999999998</v>
       </c>
       <c r="AN8" s="5">
         <f>AM8*1.09</f>
-        <v>747.75634999999988</v>
+        <v>754.11868000000004</v>
       </c>
       <c r="AO8" s="5">
         <f>AN8*1.05</f>
-        <v>785.14416749999987</v>
+        <v>791.82461400000011</v>
       </c>
       <c r="AP8" s="5">
         <f>AO8*1.04</f>
-        <v>816.54993419999994</v>
+        <v>823.49759856000014</v>
       </c>
       <c r="AQ8" s="5">
         <f>AP8*1.03</f>
-        <v>841.04643222599998</v>
+        <v>848.20252651680016</v>
       </c>
       <c r="AR8" s="5">
-        <f t="shared" si="17"/>
-        <v>857.86736087051997</v>
+        <f t="shared" ref="AR7:AR8" si="16">AQ8*1.02</f>
+        <v>865.16657704713623</v>
       </c>
       <c r="AS8" s="5">
-        <f t="shared" si="18"/>
-        <v>875.02470808793043</v>
+        <f t="shared" ref="AS7:AS8" si="17">AR8*1.02</f>
+        <v>882.46990858807897</v>
       </c>
       <c r="AT8" s="5">
-        <f t="shared" si="19"/>
-        <v>892.52520224968907</v>
+        <f t="shared" ref="AT7:AT8" si="18">AS8*1.02</f>
+        <v>900.11930675984058</v>
       </c>
       <c r="AU8" s="5">
-        <f t="shared" si="20"/>
-        <v>910.37570629468291</v>
+        <f t="shared" ref="AU7:AU8" si="19">AT8*1.02</f>
+        <v>918.12169289503743</v>
       </c>
       <c r="AV8" s="5">
-        <f t="shared" si="21"/>
-        <v>928.58322042057659</v>
+        <f t="shared" ref="AV7:AV8" si="20">AU8*1.02</f>
+        <v>936.48412675293821</v>
       </c>
       <c r="AW8" s="5">
-        <f t="shared" si="22"/>
-        <v>947.15488482898809</v>
+        <f t="shared" ref="AW7:AW8" si="21">AV8*1.02</f>
+        <v>955.21380928799704</v>
       </c>
     </row>
     <row r="9" spans="2:49" x14ac:dyDescent="0.3">
@@ -2097,7 +2091,7 @@
         <v>300.89999999999998</v>
       </c>
       <c r="G9" s="5">
-        <f t="shared" ref="G9" si="24">G6+G7+G8</f>
+        <f t="shared" ref="G9" si="22">G6+G7+G8</f>
         <v>235.3</v>
       </c>
       <c r="H9" s="12">
@@ -2113,84 +2107,84 @@
         <v>408.1</v>
       </c>
       <c r="K9" s="5">
-        <f t="shared" ref="K9:M9" si="25">K6+K7+K8</f>
+        <f t="shared" ref="K9:M9" si="23">K6+K7+K8</f>
         <v>381.2</v>
       </c>
       <c r="L9" s="5">
+        <f t="shared" si="23"/>
+        <v>430.9</v>
+      </c>
+      <c r="M9" s="5">
+        <f t="shared" si="23"/>
+        <v>397.2</v>
+      </c>
+      <c r="N9" s="5">
+        <f t="shared" ref="N9:O9" si="24">N6+N7+N8</f>
+        <v>404.3</v>
+      </c>
+      <c r="O9" s="5">
+        <f t="shared" si="24"/>
+        <v>391.4</v>
+      </c>
+      <c r="P9" s="5">
+        <f t="shared" ref="P9:Q9" si="25">P6+P7+P8</f>
+        <v>412.6</v>
+      </c>
+      <c r="Q9" s="5">
         <f t="shared" si="25"/>
-        <v>430.9</v>
-      </c>
-      <c r="M9" s="5">
-        <f t="shared" si="25"/>
-        <v>397.2</v>
-      </c>
-      <c r="N9" s="5">
-        <f t="shared" ref="N9:O9" si="26">N6+N7+N8</f>
-        <v>404.3</v>
-      </c>
-      <c r="O9" s="5">
-        <f t="shared" si="26"/>
-        <v>391.4</v>
-      </c>
-      <c r="P9" s="5">
-        <f t="shared" ref="P9:Q9" si="27">P6+P7+P8</f>
-        <v>412.6</v>
-      </c>
-      <c r="Q9" s="5">
-        <f t="shared" si="27"/>
         <v>432.5</v>
       </c>
       <c r="R9" s="5">
-        <f t="shared" ref="R9" si="28">R6+R7+R8</f>
+        <f t="shared" ref="R9" si="26">R6+R7+R8</f>
         <v>422.1</v>
       </c>
       <c r="S9" s="5">
-        <f t="shared" ref="S9" si="29">S6+S7+S8</f>
+        <f t="shared" ref="S9" si="27">S6+S7+S8</f>
         <v>413.4</v>
       </c>
       <c r="T9" s="5">
-        <f t="shared" ref="T9:U9" si="30">T6+T7+T8</f>
+        <f t="shared" ref="T9:U9" si="28">T6+T7+T8</f>
         <v>416.29999999999995</v>
       </c>
       <c r="U9" s="5">
+        <f t="shared" si="28"/>
+        <v>410.3</v>
+      </c>
+      <c r="V9" s="5">
+        <f t="shared" ref="V9" si="29">V6+V7+V8</f>
+        <v>434</v>
+      </c>
+      <c r="W9" s="5">
+        <f t="shared" ref="W9:X9" si="30">W6+W7+W8</f>
+        <v>437.2</v>
+      </c>
+      <c r="X9" s="5">
         <f t="shared" si="30"/>
-        <v>410.3</v>
-      </c>
-      <c r="V9" s="5">
-        <f t="shared" ref="V9" si="31">V6+V7+V8</f>
-        <v>434</v>
-      </c>
-      <c r="W9" s="5">
-        <f t="shared" ref="W9:X9" si="32">W6+W7+W8</f>
-        <v>437.2</v>
-      </c>
-      <c r="X9" s="5">
-        <f t="shared" si="32"/>
         <v>444.20000000000005</v>
       </c>
       <c r="Y9" s="5">
-        <f t="shared" ref="Y9:AD9" si="33">Y6+Y7+Y8</f>
+        <f t="shared" ref="Y9:AD9" si="31">Y6+Y7+Y8</f>
         <v>465.8</v>
       </c>
       <c r="Z9" s="5">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>641.9</v>
       </c>
       <c r="AA9" s="5">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>534.80000000000007</v>
       </c>
       <c r="AB9" s="5">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>541.4</v>
       </c>
       <c r="AC9" s="5">
-        <f t="shared" si="33"/>
-        <v>593.22259999999994</v>
+        <f t="shared" si="31"/>
+        <v>580.5</v>
       </c>
       <c r="AD9" s="5">
-        <f t="shared" si="33"/>
-        <v>774.6267499999999</v>
+        <f t="shared" si="31"/>
+        <v>790.01699999999994</v>
       </c>
       <c r="AF9" s="5">
         <f>AF6+AF7+AF8</f>
@@ -2205,64 +2199,64 @@
         <v>1913.8</v>
       </c>
       <c r="AI9" s="5">
-        <f t="shared" ref="AI9:AR9" si="34">AI6+AI7+AI8</f>
+        <f t="shared" ref="AI9:AR9" si="32">AI6+AI7+AI8</f>
         <v>1613.6</v>
       </c>
       <c r="AJ9" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>1658.6</v>
       </c>
       <c r="AK9" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>1673.9999999999998</v>
       </c>
       <c r="AL9" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>1989.1</v>
       </c>
       <c r="AM9" s="5">
-        <f t="shared" si="34"/>
-        <v>2444.0493500000002</v>
+        <f t="shared" si="32"/>
+        <v>2446.7170000000001</v>
       </c>
       <c r="AN9" s="5">
-        <f t="shared" si="34"/>
-        <v>2808.9227249999994</v>
+        <f t="shared" si="32"/>
+        <v>2921.5723300000004</v>
       </c>
       <c r="AO9" s="5">
-        <f t="shared" si="34"/>
-        <v>3055.6711526999998</v>
+        <f t="shared" si="32"/>
+        <v>3349.4872905000002</v>
       </c>
       <c r="AP9" s="5">
-        <f t="shared" si="34"/>
-        <v>3225.1267326460002</v>
+        <f t="shared" si="32"/>
+        <v>3617.75934702</v>
       </c>
       <c r="AQ9" s="5">
-        <f t="shared" si="34"/>
-        <v>3364.0807973900405</v>
+        <f t="shared" si="32"/>
+        <v>3889.6814147256009</v>
       </c>
       <c r="AR9" s="5">
-        <f t="shared" si="34"/>
-        <v>3522.825023656349</v>
+        <f t="shared" si="32"/>
+        <v>4042.6540202022006</v>
       </c>
       <c r="AS9" s="5">
-        <f t="shared" ref="AS9:AW9" si="35">AS6+AS7+AS8</f>
-        <v>3614.1349992820956</v>
+        <f t="shared" ref="AS9:AW9" si="33">AS6+AS7+AS8</f>
+        <v>4244.2507992840456</v>
       </c>
       <c r="AT9" s="5">
-        <f t="shared" si="35"/>
-        <v>3839.3431837202834</v>
+        <f t="shared" si="33"/>
+        <v>4326.0749673883729</v>
       </c>
       <c r="AU9" s="5">
-        <f t="shared" si="35"/>
-        <v>4084.3480802924892</v>
+        <f t="shared" si="33"/>
+        <v>4625.2301226708514</v>
       </c>
       <c r="AV9" s="5">
-        <f t="shared" si="35"/>
-        <v>4351.0748780859185</v>
+        <f t="shared" si="33"/>
+        <v>4951.0173186832944</v>
       </c>
       <c r="AW9" s="5">
-        <f t="shared" si="35"/>
-        <v>4641.6401954539751</v>
+        <f t="shared" si="33"/>
+        <v>5306.015657163658</v>
       </c>
     </row>
     <row r="10" spans="2:49" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2286,7 +2280,7 @@
         <v>-147.39999999999998</v>
       </c>
       <c r="G10" s="8">
-        <f t="shared" ref="G10" si="36">G5-G9</f>
+        <f t="shared" ref="G10" si="34">G5-G9</f>
         <v>-70.300000000000011</v>
       </c>
       <c r="H10" s="11">
@@ -2302,84 +2296,84 @@
         <v>-156.5</v>
       </c>
       <c r="K10" s="8">
-        <f t="shared" ref="K10:M10" si="37">K5-K9</f>
+        <f t="shared" ref="K10:M10" si="35">K5-K9</f>
         <v>-114.09999999999997</v>
       </c>
       <c r="L10" s="8">
+        <f t="shared" si="35"/>
+        <v>-146.19999999999993</v>
+      </c>
+      <c r="M10" s="8">
+        <f t="shared" si="35"/>
+        <v>-91.899999999999977</v>
+      </c>
+      <c r="N10" s="8">
+        <f t="shared" ref="N10:O10" si="36">N5-N9</f>
+        <v>-59.000000000000057</v>
+      </c>
+      <c r="O10" s="8">
+        <f t="shared" si="36"/>
+        <v>-39.399999999999977</v>
+      </c>
+      <c r="P10" s="8">
+        <f t="shared" ref="P10:Q10" si="37">P5-P9</f>
+        <v>-41.800000000000011</v>
+      </c>
+      <c r="Q10" s="8">
         <f t="shared" si="37"/>
-        <v>-146.19999999999993</v>
-      </c>
-      <c r="M10" s="8">
-        <f t="shared" si="37"/>
-        <v>-91.899999999999977</v>
-      </c>
-      <c r="N10" s="8">
-        <f t="shared" ref="N10:O10" si="38">N5-N9</f>
-        <v>-59.000000000000057</v>
-      </c>
-      <c r="O10" s="8">
-        <f t="shared" si="38"/>
-        <v>-39.399999999999977</v>
-      </c>
-      <c r="P10" s="8">
-        <f t="shared" ref="P10:Q10" si="39">P5-P9</f>
-        <v>-41.800000000000011</v>
-      </c>
-      <c r="Q10" s="8">
-        <f t="shared" si="39"/>
         <v>-62.200000000000045</v>
       </c>
       <c r="R10" s="8">
-        <f t="shared" ref="R10" si="40">R5-R9</f>
+        <f t="shared" ref="R10" si="38">R5-R9</f>
         <v>-17.800000000000011</v>
       </c>
       <c r="S10" s="8">
-        <f t="shared" ref="S10" si="41">S5-S9</f>
+        <f t="shared" ref="S10" si="39">S5-S9</f>
         <v>4.2000000000000455</v>
       </c>
       <c r="T10" s="8">
-        <f t="shared" ref="T10:U10" si="42">T5-T9</f>
+        <f t="shared" ref="T10:U10" si="40">T5-T9</f>
         <v>10.100000000000023</v>
       </c>
       <c r="U10" s="8">
+        <f t="shared" si="40"/>
+        <v>40.000000000000057</v>
+      </c>
+      <c r="V10" s="8">
+        <f t="shared" ref="V10" si="41">V5-V9</f>
+        <v>65.799999999999955</v>
+      </c>
+      <c r="W10" s="8">
+        <f t="shared" ref="W10:X10" si="42">W5-W9</f>
+        <v>80.800000000000011</v>
+      </c>
+      <c r="X10" s="8">
         <f t="shared" si="42"/>
-        <v>40.000000000000057</v>
-      </c>
-      <c r="V10" s="8">
-        <f t="shared" ref="V10" si="43">V5-V9</f>
-        <v>65.799999999999955</v>
-      </c>
-      <c r="W10" s="8">
-        <f t="shared" ref="W10:X10" si="44">W5-W9</f>
-        <v>80.800000000000011</v>
-      </c>
-      <c r="X10" s="8">
-        <f t="shared" si="44"/>
         <v>105.29999999999995</v>
       </c>
       <c r="Y10" s="8">
-        <f t="shared" ref="Y10:AD10" si="45">Y5-Y9</f>
+        <f t="shared" ref="Y10:AD10" si="43">Y5-Y9</f>
         <v>113.09999999999997</v>
       </c>
       <c r="Z10" s="8">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v>11.100000000000023</v>
       </c>
       <c r="AA10" s="8">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v>176.09999999999991</v>
       </c>
       <c r="AB10" s="8">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v>269.40000000000009</v>
       </c>
       <c r="AC10" s="8">
-        <f t="shared" si="45"/>
-        <v>288.98540000000014</v>
+        <f t="shared" si="43"/>
+        <v>393.29999999999995</v>
       </c>
       <c r="AD10" s="8">
-        <f t="shared" si="45"/>
-        <v>186.34900000000016</v>
+        <f t="shared" si="43"/>
+        <v>259.89300000000014</v>
       </c>
       <c r="AF10" s="8">
         <f>AF5-AF9</f>
@@ -2394,64 +2388,64 @@
         <v>-1173.6000000000001</v>
       </c>
       <c r="AI10" s="8">
-        <f t="shared" ref="AI10:AR10" si="46">AI5-AI9</f>
+        <f t="shared" ref="AI10:AR10" si="44">AI5-AI9</f>
         <v>-411.19999999999982</v>
       </c>
       <c r="AJ10" s="8">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>-161.19999999999982</v>
       </c>
       <c r="AK10" s="8">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>120.10000000000014</v>
       </c>
       <c r="AL10" s="8">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>310.30000000000018</v>
       </c>
       <c r="AM10" s="8">
-        <f t="shared" si="46"/>
-        <v>920.83439999999973</v>
+        <f t="shared" si="44"/>
+        <v>1098.6929999999998</v>
       </c>
       <c r="AN10" s="8">
-        <f t="shared" si="46"/>
-        <v>1566.1336750000009</v>
+        <f t="shared" si="44"/>
+        <v>2243.5263199999995</v>
       </c>
       <c r="AO10" s="8">
-        <f t="shared" si="46"/>
-        <v>2500.6504753000008</v>
+        <f t="shared" si="44"/>
+        <v>3623.3958870000006</v>
       </c>
       <c r="AP10" s="8">
-        <f t="shared" si="46"/>
-        <v>3664.7120860740006</v>
+        <f t="shared" si="44"/>
+        <v>5446.9887837300003</v>
       </c>
       <c r="AQ10" s="8">
-        <f t="shared" si="46"/>
-        <v>4765.9290086995607</v>
+        <f t="shared" si="44"/>
+        <v>7441.2537487119007</v>
       </c>
       <c r="AR10" s="8">
-        <f t="shared" si="46"/>
-        <v>5745.3861552857961</v>
+        <f t="shared" si="44"/>
+        <v>9554.4681759228006</v>
       </c>
       <c r="AS10" s="8">
-        <f t="shared" ref="AS10:AW10" si="47">AS5-AS9</f>
-        <v>6580.8972975542638</v>
+        <f t="shared" ref="AS10:AW10" si="45">AS5-AS9</f>
+        <v>11392.439726259705</v>
       </c>
       <c r="AT10" s="8">
-        <f t="shared" si="47"/>
-        <v>7375.1923427997126</v>
+        <f t="shared" si="45"/>
+        <v>12874.284610709754</v>
       </c>
       <c r="AU10" s="8">
-        <f t="shared" si="47"/>
-        <v>8251.6409988795058</v>
+        <f t="shared" si="45"/>
+        <v>14295.16541323709</v>
       </c>
       <c r="AV10" s="8">
-        <f t="shared" si="47"/>
-        <v>9218.5131090032773</v>
+        <f t="shared" si="45"/>
+        <v>15861.417770815442</v>
       </c>
       <c r="AW10" s="8">
-        <f t="shared" si="47"/>
-        <v>10284.906590344141</v>
+        <f t="shared" si="45"/>
+        <v>17587.662941284954</v>
       </c>
     </row>
     <row r="11" spans="2:49" x14ac:dyDescent="0.3">
@@ -2539,11 +2533,10 @@
         <v>-56.3</v>
       </c>
       <c r="AC11" s="5">
-        <f t="shared" ref="AC11:AD11" si="48">Y11*1.2</f>
-        <v>-62.519999999999996</v>
+        <v>-59.8</v>
       </c>
       <c r="AD11" s="5">
-        <f t="shared" si="48"/>
+        <f t="shared" ref="AC11:AD11" si="46">Z11*1.2</f>
         <v>-65.64</v>
       </c>
       <c r="AF11" s="5">
@@ -2574,47 +2567,47 @@
       </c>
       <c r="AM11" s="5">
         <f>SUM(AA11:AD11)</f>
-        <v>-234.85999999999996</v>
+        <v>-232.14</v>
       </c>
       <c r="AN11" s="5">
         <f>AM11*1.15</f>
-        <v>-270.08899999999994</v>
+        <v>-266.96099999999996</v>
       </c>
       <c r="AO11" s="5">
-        <f t="shared" ref="AO11:AW11" si="49">AN11*1.15</f>
-        <v>-310.60234999999989</v>
+        <f t="shared" ref="AO11:AW11" si="47">AN11*1.15</f>
+        <v>-307.0051499999999</v>
       </c>
       <c r="AP11" s="5">
-        <f t="shared" si="49"/>
-        <v>-357.19270249999983</v>
+        <f t="shared" si="47"/>
+        <v>-353.05592249999984</v>
       </c>
       <c r="AQ11" s="5">
-        <f t="shared" si="49"/>
-        <v>-410.77160787499975</v>
+        <f t="shared" si="47"/>
+        <v>-406.01431087499981</v>
       </c>
       <c r="AR11" s="5">
-        <f t="shared" si="49"/>
-        <v>-472.38734905624966</v>
+        <f t="shared" si="47"/>
+        <v>-466.91645750624974</v>
       </c>
       <c r="AS11" s="5">
-        <f t="shared" si="49"/>
-        <v>-543.24545141468707</v>
+        <f t="shared" si="47"/>
+        <v>-536.95392613218712</v>
       </c>
       <c r="AT11" s="5">
-        <f t="shared" si="49"/>
-        <v>-624.73226912689006</v>
+        <f t="shared" si="47"/>
+        <v>-617.49701505201517</v>
       </c>
       <c r="AU11" s="5">
-        <f t="shared" si="49"/>
-        <v>-718.44210949592355</v>
+        <f t="shared" si="47"/>
+        <v>-710.12156730981735</v>
       </c>
       <c r="AV11" s="5">
-        <f t="shared" si="49"/>
-        <v>-826.20842592031204</v>
+        <f t="shared" si="47"/>
+        <v>-816.63980240628985</v>
       </c>
       <c r="AW11" s="5">
-        <f t="shared" si="49"/>
-        <v>-950.13968980835875</v>
+        <f t="shared" si="47"/>
+        <v>-939.13577276723322</v>
       </c>
     </row>
     <row r="12" spans="2:49" x14ac:dyDescent="0.3">
@@ -2738,43 +2731,43 @@
         <v>0</v>
       </c>
       <c r="AN12" s="5">
-        <f t="shared" ref="AN12:AS12" si="50">AM12*0.9</f>
+        <f t="shared" ref="AN12:AS12" si="48">AM12*0.9</f>
         <v>0</v>
       </c>
       <c r="AO12" s="5">
-        <f t="shared" si="50"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="AP12" s="5">
-        <f t="shared" si="50"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="AQ12" s="5">
-        <f t="shared" si="50"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="AR12" s="5">
-        <f t="shared" si="50"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="AS12" s="5">
-        <f t="shared" si="50"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="AT12" s="5">
-        <f t="shared" ref="AT12" si="51">AS12*0.9</f>
+        <f t="shared" ref="AT12" si="49">AS12*0.9</f>
         <v>0</v>
       </c>
       <c r="AU12" s="5">
-        <f t="shared" ref="AU12" si="52">AT12*0.9</f>
+        <f t="shared" ref="AU12" si="50">AT12*0.9</f>
         <v>0</v>
       </c>
       <c r="AV12" s="5">
-        <f t="shared" ref="AV12" si="53">AU12*0.9</f>
+        <f t="shared" ref="AV12" si="51">AU12*0.9</f>
         <v>0</v>
       </c>
       <c r="AW12" s="5">
-        <f t="shared" ref="AW12" si="54">AV12*0.9</f>
+        <f t="shared" ref="AW12" si="52">AV12*0.9</f>
         <v>0</v>
       </c>
     </row>
@@ -2899,43 +2892,43 @@
         <v>0</v>
       </c>
       <c r="AN13" s="5">
-        <f t="shared" ref="AN13:AS13" si="55">AM13*1.5</f>
+        <f t="shared" ref="AN13:AS13" si="53">AM13*1.5</f>
         <v>0</v>
       </c>
       <c r="AO13" s="5">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="AP13" s="5">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="AQ13" s="5">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="AR13" s="5">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="AS13" s="5">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="AT13" s="5">
-        <f t="shared" ref="AT13" si="56">AS13*1.5</f>
+        <f t="shared" ref="AT13" si="54">AS13*1.5</f>
         <v>0</v>
       </c>
       <c r="AU13" s="5">
-        <f t="shared" ref="AU13" si="57">AT13*1.5</f>
+        <f t="shared" ref="AU13" si="55">AT13*1.5</f>
         <v>0</v>
       </c>
       <c r="AV13" s="5">
-        <f t="shared" ref="AV13" si="58">AU13*1.5</f>
+        <f t="shared" ref="AV13" si="56">AU13*1.5</f>
         <v>0</v>
       </c>
       <c r="AW13" s="5">
-        <f t="shared" ref="AW13" si="59">AV13*1.5</f>
+        <f t="shared" ref="AW13" si="57">AV13*1.5</f>
         <v>0</v>
       </c>
     </row>
@@ -3024,10 +3017,10 @@
         <v>-6.6</v>
       </c>
       <c r="AC14" s="5">
-        <v>0</v>
+        <v>-27.5</v>
       </c>
       <c r="AD14" s="5">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="AF14" s="5">
         <v>2.6</v>
@@ -3057,7 +3050,7 @@
       </c>
       <c r="AM14" s="5">
         <f>SUM(AA14:AD14)</f>
-        <v>-3.3999999999999995</v>
+        <v>-40.9</v>
       </c>
       <c r="AN14" s="5">
         <v>0</v>
@@ -3111,7 +3104,7 @@
         <v>-155.39999999999995</v>
       </c>
       <c r="G15" s="8">
-        <f t="shared" ref="G15" si="60">G10-G11-G12-G13-G14</f>
+        <f t="shared" ref="G15" si="58">G10-G11-G12-G13-G14</f>
         <v>-51.800000000000004</v>
       </c>
       <c r="H15" s="11">
@@ -3127,84 +3120,84 @@
         <v>-155.80000000000001</v>
       </c>
       <c r="K15" s="8">
-        <f t="shared" ref="K15:M15" si="61">K10-K11-K12-K13-K14</f>
+        <f t="shared" ref="K15:M15" si="59">K10-K11-K12-K13-K14</f>
         <v>-120.39999999999996</v>
       </c>
       <c r="L15" s="8">
+        <f t="shared" si="59"/>
+        <v>-148.49999999999991</v>
+      </c>
+      <c r="M15" s="8">
+        <f t="shared" si="59"/>
+        <v>-100.59999999999997</v>
+      </c>
+      <c r="N15" s="8">
+        <f t="shared" ref="N15:O15" si="60">N10-N11-N12-N13-N14</f>
+        <v>-123.20000000000005</v>
+      </c>
+      <c r="O15" s="8">
+        <f t="shared" si="60"/>
+        <v>-99.399999999999977</v>
+      </c>
+      <c r="P15" s="8">
+        <f t="shared" ref="P15:Q15" si="61">P10-P11-P12-P13-P14</f>
+        <v>-176.8</v>
+      </c>
+      <c r="Q15" s="8">
         <f t="shared" si="61"/>
-        <v>-148.49999999999991</v>
-      </c>
-      <c r="M15" s="8">
-        <f t="shared" si="61"/>
-        <v>-100.59999999999997</v>
-      </c>
-      <c r="N15" s="8">
-        <f t="shared" ref="N15:O15" si="62">N10-N11-N12-N13-N14</f>
-        <v>-123.20000000000005</v>
-      </c>
-      <c r="O15" s="8">
-        <f t="shared" si="62"/>
-        <v>-99.399999999999977</v>
-      </c>
-      <c r="P15" s="8">
-        <f t="shared" ref="P15:Q15" si="63">P10-P11-P12-P13-P14</f>
-        <v>-176.8</v>
-      </c>
-      <c r="Q15" s="8">
-        <f t="shared" si="63"/>
         <v>-122.80000000000004</v>
       </c>
       <c r="R15" s="8">
-        <f t="shared" ref="R15" si="64">R10-R11-R12-R13-R14</f>
+        <f t="shared" ref="R15" si="62">R10-R11-R12-R13-R14</f>
         <v>37.899999999999991</v>
       </c>
       <c r="S15" s="8">
-        <f t="shared" ref="S15" si="65">S10-S11-S12-S13-S14</f>
+        <f t="shared" ref="S15" si="63">S10-S11-S12-S13-S14</f>
         <v>21.000000000000043</v>
       </c>
       <c r="T15" s="8">
-        <f t="shared" ref="T15:U15" si="66">T10-T11-T12-T13-T14</f>
+        <f t="shared" ref="T15:U15" si="64">T10-T11-T12-T13-T14</f>
         <v>30.100000000000019</v>
       </c>
       <c r="U15" s="8">
+        <f t="shared" si="64"/>
+        <v>80.100000000000065</v>
+      </c>
+      <c r="V15" s="8">
+        <f t="shared" ref="V15" si="65">V10-V11-V12-V13-V14</f>
+        <v>106.19999999999996</v>
+      </c>
+      <c r="W15" s="8">
+        <f t="shared" ref="W15:AA15" si="66">W10-W11-W12-W13-W14</f>
+        <v>110.70000000000002</v>
+      </c>
+      <c r="X15" s="8">
         <f t="shared" si="66"/>
-        <v>80.100000000000065</v>
-      </c>
-      <c r="V15" s="8">
-        <f t="shared" ref="V15" si="67">V10-V11-V12-V13-V14</f>
-        <v>106.19999999999996</v>
-      </c>
-      <c r="W15" s="8">
-        <f t="shared" ref="W15:AA15" si="68">W10-W11-W12-W13-W14</f>
-        <v>110.70000000000002</v>
-      </c>
-      <c r="X15" s="8">
-        <f t="shared" si="68"/>
         <v>140.69999999999996</v>
       </c>
       <c r="Y15" s="8">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>157.09999999999997</v>
       </c>
       <c r="Z15" s="8">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>80.600000000000023</v>
       </c>
       <c r="AA15" s="8">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>223.29999999999993</v>
       </c>
       <c r="AB15" s="8">
-        <f t="shared" ref="AB15:AD15" si="69">AB10-AB11-AB12-AB13-AB14</f>
+        <f t="shared" ref="AB15:AD15" si="67">AB10-AB11-AB12-AB13-AB14</f>
         <v>332.30000000000013</v>
       </c>
       <c r="AC15" s="8">
-        <f t="shared" si="69"/>
-        <v>351.50540000000012</v>
+        <f t="shared" si="67"/>
+        <v>480.59999999999997</v>
       </c>
       <c r="AD15" s="8">
-        <f t="shared" si="69"/>
-        <v>251.98900000000015</v>
+        <f t="shared" si="67"/>
+        <v>335.53300000000013</v>
       </c>
       <c r="AF15" s="8">
         <f>AF10-AF11-AF12-AF13-AF14</f>
@@ -3223,60 +3216,60 @@
         <v>-492.69999999999982</v>
       </c>
       <c r="AJ15" s="8">
-        <f t="shared" ref="AJ15:AR15" si="70">AJ10-AJ11-AJ12-AJ13-AJ14</f>
+        <f t="shared" ref="AJ15:AR15" si="68">AJ10-AJ11-AJ12-AJ13-AJ14</f>
         <v>-361.09999999999985</v>
       </c>
       <c r="AK15" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="68"/>
         <v>237.40000000000012</v>
       </c>
       <c r="AL15" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="68"/>
         <v>489.10000000000019</v>
       </c>
       <c r="AM15" s="8">
-        <f t="shared" si="70"/>
-        <v>1159.0943999999997</v>
+        <f t="shared" si="68"/>
+        <v>1371.7329999999997</v>
       </c>
       <c r="AN15" s="8">
-        <f t="shared" si="70"/>
-        <v>1836.2226750000009</v>
+        <f t="shared" si="68"/>
+        <v>2510.4873199999993</v>
       </c>
       <c r="AO15" s="8">
-        <f t="shared" si="70"/>
-        <v>2811.2528253000009</v>
+        <f t="shared" si="68"/>
+        <v>3930.4010370000005</v>
       </c>
       <c r="AP15" s="8">
-        <f t="shared" si="70"/>
-        <v>4021.9047885740006</v>
+        <f t="shared" si="68"/>
+        <v>5800.04470623</v>
       </c>
       <c r="AQ15" s="8">
-        <f t="shared" si="70"/>
-        <v>5176.7006165745606</v>
+        <f t="shared" si="68"/>
+        <v>7847.2680595869006</v>
       </c>
       <c r="AR15" s="8">
-        <f t="shared" si="70"/>
-        <v>6217.7735043420462</v>
+        <f t="shared" si="68"/>
+        <v>10021.38463342905</v>
       </c>
       <c r="AS15" s="8">
-        <f t="shared" ref="AS15:AW15" si="71">AS10-AS11-AS12-AS13-AS14</f>
-        <v>7124.1427489689504</v>
+        <f t="shared" ref="AS15:AW15" si="69">AS10-AS11-AS12-AS13-AS14</f>
+        <v>11929.393652391893</v>
       </c>
       <c r="AT15" s="8">
-        <f t="shared" si="71"/>
-        <v>7999.9246119266027</v>
+        <f t="shared" si="69"/>
+        <v>13491.781625761769</v>
       </c>
       <c r="AU15" s="8">
-        <f t="shared" si="71"/>
-        <v>8970.0831083754292</v>
+        <f t="shared" si="69"/>
+        <v>15005.286980546907</v>
       </c>
       <c r="AV15" s="8">
-        <f t="shared" si="71"/>
-        <v>10044.721534923588</v>
+        <f t="shared" si="69"/>
+        <v>16678.057573221733</v>
       </c>
       <c r="AW15" s="8">
-        <f t="shared" si="71"/>
-        <v>11235.046280152499</v>
+        <f t="shared" si="69"/>
+        <v>18526.798714052187</v>
       </c>
     </row>
     <row r="16" spans="2:49" x14ac:dyDescent="0.3">
@@ -3364,12 +3357,11 @@
         <v>3.6</v>
       </c>
       <c r="AC16" s="5">
-        <f t="shared" ref="AC16:AD16" si="72">AC15*0.04</f>
-        <v>14.060216000000006</v>
+        <v>3.8</v>
       </c>
       <c r="AD16" s="5">
-        <f t="shared" si="72"/>
-        <v>10.079560000000006</v>
+        <f t="shared" ref="AC16:AD16" si="70">AD15*0.04</f>
+        <v>13.421320000000005</v>
       </c>
       <c r="AF16" s="5">
         <v>9.1</v>
@@ -3399,47 +3391,47 @@
       </c>
       <c r="AM16" s="5">
         <f>SUM(AA16:AD16)</f>
-        <v>33.339776000000015</v>
+        <v>26.421320000000005</v>
       </c>
       <c r="AN16" s="5">
-        <f t="shared" ref="AN16:AQ16" si="73">AN15*0.1</f>
-        <v>183.62226750000011</v>
+        <f t="shared" ref="AN16:AQ16" si="71">AN15*0.1</f>
+        <v>251.04873199999994</v>
       </c>
       <c r="AO16" s="5">
-        <f t="shared" si="73"/>
-        <v>281.12528253000011</v>
+        <f t="shared" si="71"/>
+        <v>393.04010370000009</v>
       </c>
       <c r="AP16" s="5">
-        <f t="shared" si="73"/>
-        <v>402.19047885740008</v>
+        <f t="shared" si="71"/>
+        <v>580.00447062299997</v>
       </c>
       <c r="AQ16" s="5">
-        <f t="shared" si="73"/>
-        <v>517.67006165745613</v>
+        <f t="shared" si="71"/>
+        <v>784.72680595869008</v>
       </c>
       <c r="AR16" s="5">
         <f>AR15*0.15</f>
-        <v>932.66602565130688</v>
+        <v>1503.2076950143576</v>
       </c>
       <c r="AS16" s="5">
-        <f t="shared" ref="AS16:AW16" si="74">AS15*0.15</f>
-        <v>1068.6214123453426</v>
+        <f t="shared" ref="AS16:AW16" si="72">AS15*0.15</f>
+        <v>1789.4090478587839</v>
       </c>
       <c r="AT16" s="5">
-        <f t="shared" si="74"/>
-        <v>1199.9886917889903</v>
+        <f t="shared" si="72"/>
+        <v>2023.7672438642653</v>
       </c>
       <c r="AU16" s="5">
-        <f t="shared" si="74"/>
-        <v>1345.5124662563144</v>
+        <f t="shared" si="72"/>
+        <v>2250.7930470820361</v>
       </c>
       <c r="AV16" s="5">
-        <f t="shared" si="74"/>
-        <v>1506.7082302385381</v>
+        <f t="shared" si="72"/>
+        <v>2501.7086359832597</v>
       </c>
       <c r="AW16" s="5">
-        <f t="shared" si="74"/>
-        <v>1685.2569420228749</v>
+        <f t="shared" si="72"/>
+        <v>2779.019807107828</v>
       </c>
     </row>
     <row r="17" spans="2:166" x14ac:dyDescent="0.3">
@@ -3481,12 +3473,11 @@
         <v>1.8</v>
       </c>
       <c r="AC17" s="5">
-        <f t="shared" ref="AC17:AD17" si="75">AC15*0.01</f>
-        <v>3.5150540000000015</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="AD17" s="5">
-        <f t="shared" si="75"/>
-        <v>2.5198900000000015</v>
+        <f t="shared" ref="AC17:AD17" si="73">AD15*0.01</f>
+        <v>3.3553300000000013</v>
       </c>
       <c r="AF17" s="5"/>
       <c r="AG17" s="5"/>
@@ -3500,47 +3491,47 @@
       </c>
       <c r="AM17" s="5">
         <f>SUM(AA17:AD17)</f>
-        <v>11.534944000000003</v>
+        <v>9.95533</v>
       </c>
       <c r="AN17" s="5">
-        <f t="shared" ref="AN17:AW17" si="76">AN15*0.02</f>
-        <v>36.724453500000017</v>
+        <f t="shared" ref="AN17:AW17" si="74">AN15*0.02</f>
+        <v>50.209746399999986</v>
       </c>
       <c r="AO17" s="5">
-        <f t="shared" si="76"/>
-        <v>56.225056506000023</v>
+        <f t="shared" si="74"/>
+        <v>78.608020740000015</v>
       </c>
       <c r="AP17" s="5">
-        <f t="shared" si="76"/>
-        <v>80.438095771480008</v>
+        <f t="shared" si="74"/>
+        <v>116.00089412459999</v>
       </c>
       <c r="AQ17" s="5">
-        <f t="shared" si="76"/>
-        <v>103.53401233149121</v>
+        <f t="shared" si="74"/>
+        <v>156.94536119173802</v>
       </c>
       <c r="AR17" s="5">
-        <f t="shared" si="76"/>
-        <v>124.35547008684092</v>
+        <f t="shared" si="74"/>
+        <v>200.42769266858102</v>
       </c>
       <c r="AS17" s="5">
-        <f t="shared" si="76"/>
-        <v>142.482854979379</v>
+        <f t="shared" si="74"/>
+        <v>238.58787304783786</v>
       </c>
       <c r="AT17" s="5">
-        <f t="shared" si="76"/>
-        <v>159.99849223853207</v>
+        <f t="shared" si="74"/>
+        <v>269.83563251523537</v>
       </c>
       <c r="AU17" s="5">
-        <f t="shared" si="76"/>
-        <v>179.40166216750859</v>
+        <f t="shared" si="74"/>
+        <v>300.10573961093814</v>
       </c>
       <c r="AV17" s="5">
-        <f t="shared" si="76"/>
-        <v>200.89443069847178</v>
+        <f t="shared" si="74"/>
+        <v>333.56115146443466</v>
       </c>
       <c r="AW17" s="5">
-        <f t="shared" si="76"/>
-        <v>224.70092560305</v>
+        <f t="shared" si="74"/>
+        <v>370.53597428104376</v>
       </c>
     </row>
     <row r="18" spans="2:166" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -3564,7 +3555,7 @@
         <v>-159.29999999999995</v>
       </c>
       <c r="G18" s="8">
-        <f t="shared" ref="G18" si="77">G15-G16</f>
+        <f t="shared" ref="G18" si="75">G15-G16</f>
         <v>-54.400000000000006</v>
       </c>
       <c r="H18" s="11">
@@ -3580,59 +3571,59 @@
         <v>-148.20000000000002</v>
       </c>
       <c r="K18" s="8">
-        <f t="shared" ref="K18:M18" si="78">K15-K16</f>
+        <f t="shared" ref="K18:M18" si="76">K15-K16</f>
         <v>-123.49999999999996</v>
       </c>
       <c r="L18" s="8">
+        <f t="shared" si="76"/>
+        <v>-142.79999999999993</v>
+      </c>
+      <c r="M18" s="8">
+        <f t="shared" si="76"/>
+        <v>-101.99999999999997</v>
+      </c>
+      <c r="N18" s="8">
+        <f t="shared" ref="N18:O18" si="77">N15-N16</f>
+        <v>-156.20000000000005</v>
+      </c>
+      <c r="O18" s="8">
+        <f t="shared" si="77"/>
+        <v>-101.39999999999998</v>
+      </c>
+      <c r="P18" s="8">
+        <f t="shared" ref="P18:Q18" si="78">P15-P16</f>
+        <v>-179.4</v>
+      </c>
+      <c r="Q18" s="8">
         <f t="shared" si="78"/>
-        <v>-142.79999999999993</v>
-      </c>
-      <c r="M18" s="8">
-        <f t="shared" si="78"/>
-        <v>-101.99999999999997</v>
-      </c>
-      <c r="N18" s="8">
-        <f t="shared" ref="N18:O18" si="79">N15-N16</f>
-        <v>-156.20000000000005</v>
-      </c>
-      <c r="O18" s="8">
-        <f t="shared" si="79"/>
-        <v>-101.39999999999998</v>
-      </c>
-      <c r="P18" s="8">
-        <f t="shared" ref="P18:Q18" si="80">P15-P16</f>
-        <v>-179.4</v>
-      </c>
-      <c r="Q18" s="8">
-        <f t="shared" si="80"/>
         <v>-123.90000000000003</v>
       </c>
       <c r="R18" s="8">
-        <f t="shared" ref="R18" si="81">R15-R16</f>
+        <f t="shared" ref="R18" si="79">R15-R16</f>
         <v>33.499999999999993</v>
       </c>
       <c r="S18" s="8">
-        <f t="shared" ref="S18" si="82">S15-S16</f>
+        <f t="shared" ref="S18" si="80">S15-S16</f>
         <v>19.300000000000043</v>
       </c>
       <c r="T18" s="8">
-        <f t="shared" ref="T18:U18" si="83">T15-T16</f>
+        <f t="shared" ref="T18:U18" si="81">T15-T16</f>
         <v>27.90000000000002</v>
       </c>
       <c r="U18" s="8">
+        <f t="shared" si="81"/>
+        <v>73.600000000000065</v>
+      </c>
+      <c r="V18" s="8">
+        <f t="shared" ref="V18" si="82">V15-V16</f>
+        <v>96.899999999999963</v>
+      </c>
+      <c r="W18" s="8">
+        <f t="shared" ref="W18:X18" si="83">W15-W16</f>
+        <v>106.00000000000001</v>
+      </c>
+      <c r="X18" s="8">
         <f t="shared" si="83"/>
-        <v>73.600000000000065</v>
-      </c>
-      <c r="V18" s="8">
-        <f t="shared" ref="V18" si="84">V15-V16</f>
-        <v>96.899999999999963</v>
-      </c>
-      <c r="W18" s="8">
-        <f t="shared" ref="W18:X18" si="85">W15-W16</f>
-        <v>106.00000000000001</v>
-      </c>
-      <c r="X18" s="8">
-        <f t="shared" si="85"/>
         <v>135.49999999999997</v>
       </c>
       <c r="Y18" s="8">
@@ -3640,24 +3631,24 @@
         <v>143.49999999999994</v>
       </c>
       <c r="Z18" s="8">
-        <f t="shared" ref="Z18:AD18" si="86">Z15-Z16-Z17</f>
+        <f t="shared" ref="Z18:AD18" si="84">Z15-Z16-Z17</f>
         <v>79.100000000000023</v>
       </c>
       <c r="AA18" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="84"/>
         <v>213.99999999999994</v>
       </c>
       <c r="AB18" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="84"/>
         <v>326.90000000000009</v>
       </c>
       <c r="AC18" s="8">
-        <f t="shared" si="86"/>
-        <v>333.93013000000008</v>
+        <f t="shared" si="84"/>
+        <v>475.69999999999993</v>
       </c>
       <c r="AD18" s="8">
-        <f t="shared" si="86"/>
-        <v>239.38955000000013</v>
+        <f t="shared" si="84"/>
+        <v>318.75635000000017</v>
       </c>
       <c r="AF18" s="8">
         <f>AF15-AF16</f>
@@ -3672,532 +3663,532 @@
         <v>-1166.3000000000002</v>
       </c>
       <c r="AI18" s="8">
-        <f t="shared" ref="AI18" si="87">AI15-AI16</f>
+        <f t="shared" ref="AI18" si="85">AI15-AI16</f>
         <v>-524.49999999999977</v>
       </c>
       <c r="AJ18" s="8">
-        <f t="shared" ref="AJ18" si="88">AJ15-AJ16</f>
+        <f t="shared" ref="AJ18" si="86">AJ15-AJ16</f>
         <v>-371.19999999999987</v>
       </c>
       <c r="AK18" s="8">
-        <f t="shared" ref="AK18" si="89">AK15-AK16</f>
+        <f t="shared" ref="AK18" si="87">AK15-AK16</f>
         <v>217.7000000000001</v>
       </c>
       <c r="AL18" s="8">
-        <f t="shared" ref="AL18:AW18" si="90">AL15-AL16-AL17</f>
+        <f t="shared" ref="AL18:AW18" si="88">AL15-AL16-AL17</f>
         <v>464.10000000000019</v>
       </c>
       <c r="AM18" s="8">
+        <f t="shared" si="88"/>
+        <v>1335.3563499999998</v>
+      </c>
+      <c r="AN18" s="8">
+        <f t="shared" si="88"/>
+        <v>2209.2288415999997</v>
+      </c>
+      <c r="AO18" s="8">
+        <f t="shared" si="88"/>
+        <v>3458.7529125600004</v>
+      </c>
+      <c r="AP18" s="8">
+        <f t="shared" si="88"/>
+        <v>5104.0393414824002</v>
+      </c>
+      <c r="AQ18" s="8">
+        <f t="shared" si="88"/>
+        <v>6905.5958924364722</v>
+      </c>
+      <c r="AR18" s="8">
+        <f t="shared" si="88"/>
+        <v>8317.7492457461103</v>
+      </c>
+      <c r="AS18" s="8">
+        <f t="shared" si="88"/>
+        <v>9901.3967314852707</v>
+      </c>
+      <c r="AT18" s="8">
+        <f t="shared" si="88"/>
+        <v>11198.178749382267</v>
+      </c>
+      <c r="AU18" s="8">
+        <f t="shared" si="88"/>
+        <v>12454.388193853934</v>
+      </c>
+      <c r="AV18" s="8">
+        <f t="shared" si="88"/>
+        <v>13842.787785774039</v>
+      </c>
+      <c r="AW18" s="8">
+        <f t="shared" si="88"/>
+        <v>15377.242932663316</v>
+      </c>
+      <c r="AX18" s="1">
+        <f t="shared" ref="AX18:CC18" si="89">AW18*(1+$AZ$25)</f>
+        <v>15223.470503336683</v>
+      </c>
+      <c r="AY18" s="1">
+        <f t="shared" si="89"/>
+        <v>15071.235798303316</v>
+      </c>
+      <c r="AZ18" s="1">
+        <f t="shared" si="89"/>
+        <v>14920.523440320283</v>
+      </c>
+      <c r="BA18" s="1">
+        <f t="shared" si="89"/>
+        <v>14771.318205917079</v>
+      </c>
+      <c r="BB18" s="1">
+        <f t="shared" si="89"/>
+        <v>14623.605023857908</v>
+      </c>
+      <c r="BC18" s="1">
+        <f t="shared" si="89"/>
+        <v>14477.368973619328</v>
+      </c>
+      <c r="BD18" s="1">
+        <f t="shared" si="89"/>
+        <v>14332.595283883134</v>
+      </c>
+      <c r="BE18" s="1">
+        <f t="shared" si="89"/>
+        <v>14189.269331044303</v>
+      </c>
+      <c r="BF18" s="1">
+        <f t="shared" si="89"/>
+        <v>14047.37663773386</v>
+      </c>
+      <c r="BG18" s="1">
+        <f t="shared" si="89"/>
+        <v>13906.90287135652</v>
+      </c>
+      <c r="BH18" s="1">
+        <f t="shared" si="89"/>
+        <v>13767.833842642955</v>
+      </c>
+      <c r="BI18" s="1">
+        <f t="shared" si="89"/>
+        <v>13630.155504216526</v>
+      </c>
+      <c r="BJ18" s="1">
+        <f t="shared" si="89"/>
+        <v>13493.85394917436</v>
+      </c>
+      <c r="BK18" s="1">
+        <f t="shared" si="89"/>
+        <v>13358.915409682615</v>
+      </c>
+      <c r="BL18" s="1">
+        <f t="shared" si="89"/>
+        <v>13225.326255585789</v>
+      </c>
+      <c r="BM18" s="1">
+        <f t="shared" si="89"/>
+        <v>13093.072993029931</v>
+      </c>
+      <c r="BN18" s="1">
+        <f t="shared" si="89"/>
+        <v>12962.142263099631</v>
+      </c>
+      <c r="BO18" s="1">
+        <f t="shared" si="89"/>
+        <v>12832.520840468635</v>
+      </c>
+      <c r="BP18" s="1">
+        <f t="shared" si="89"/>
+        <v>12704.195632063947</v>
+      </c>
+      <c r="BQ18" s="1">
+        <f t="shared" si="89"/>
+        <v>12577.153675743308</v>
+      </c>
+      <c r="BR18" s="1">
+        <f t="shared" si="89"/>
+        <v>12451.382138985875</v>
+      </c>
+      <c r="BS18" s="1">
+        <f t="shared" si="89"/>
+        <v>12326.868317596016</v>
+      </c>
+      <c r="BT18" s="1">
+        <f t="shared" si="89"/>
+        <v>12203.599634420056</v>
+      </c>
+      <c r="BU18" s="1">
+        <f t="shared" si="89"/>
+        <v>12081.563638075855</v>
+      </c>
+      <c r="BV18" s="1">
+        <f t="shared" si="89"/>
+        <v>11960.748001695096</v>
+      </c>
+      <c r="BW18" s="1">
+        <f t="shared" si="89"/>
+        <v>11841.140521678144</v>
+      </c>
+      <c r="BX18" s="1">
+        <f t="shared" si="89"/>
+        <v>11722.729116461362</v>
+      </c>
+      <c r="BY18" s="1">
+        <f t="shared" si="89"/>
+        <v>11605.501825296747</v>
+      </c>
+      <c r="BZ18" s="1">
+        <f t="shared" si="89"/>
+        <v>11489.44680704378</v>
+      </c>
+      <c r="CA18" s="1">
+        <f t="shared" si="89"/>
+        <v>11374.552338973343</v>
+      </c>
+      <c r="CB18" s="1">
+        <f t="shared" si="89"/>
+        <v>11260.80681558361</v>
+      </c>
+      <c r="CC18" s="1">
+        <f t="shared" si="89"/>
+        <v>11148.198747427774</v>
+      </c>
+      <c r="CD18" s="1">
+        <f t="shared" ref="CD18:DI18" si="90">CC18*(1+$AZ$25)</f>
+        <v>11036.716759953497</v>
+      </c>
+      <c r="CE18" s="1">
         <f t="shared" si="90"/>
-        <v>1114.2196799999997</v>
-      </c>
-      <c r="AN18" s="8">
+        <v>10926.349592353961</v>
+      </c>
+      <c r="CF18" s="1">
         <f t="shared" si="90"/>
-        <v>1615.8759540000008</v>
-      </c>
-      <c r="AO18" s="8">
+        <v>10817.086096430421</v>
+      </c>
+      <c r="CG18" s="1">
         <f t="shared" si="90"/>
-        <v>2473.9024862640008</v>
-      </c>
-      <c r="AP18" s="8">
+        <v>10708.915235466116</v>
+      </c>
+      <c r="CH18" s="1">
         <f t="shared" si="90"/>
-        <v>3539.2762139451202</v>
-      </c>
-      <c r="AQ18" s="8">
+        <v>10601.826083111455</v>
+      </c>
+      <c r="CI18" s="1">
         <f t="shared" si="90"/>
-        <v>4555.4965425856135</v>
-      </c>
-      <c r="AR18" s="8">
+        <v>10495.80782228034</v>
+      </c>
+      <c r="CJ18" s="1">
         <f t="shared" si="90"/>
-        <v>5160.7520086038985</v>
-      </c>
-      <c r="AS18" s="8">
+        <v>10390.849744057536</v>
+      </c>
+      <c r="CK18" s="1">
         <f t="shared" si="90"/>
-        <v>5913.0384816442283</v>
-      </c>
-      <c r="AT18" s="8">
+        <v>10286.94124661696</v>
+      </c>
+      <c r="CL18" s="1">
         <f t="shared" si="90"/>
-        <v>6639.9374278990799</v>
-      </c>
-      <c r="AU18" s="8">
+        <v>10184.071834150791</v>
+      </c>
+      <c r="CM18" s="1">
         <f t="shared" si="90"/>
-        <v>7445.1689799516071</v>
-      </c>
-      <c r="AV18" s="8">
+        <v>10082.231115809283</v>
+      </c>
+      <c r="CN18" s="1">
         <f t="shared" si="90"/>
-        <v>8337.1188739865775</v>
-      </c>
-      <c r="AW18" s="8">
+        <v>9981.4088046511897</v>
+      </c>
+      <c r="CO18" s="1">
         <f t="shared" si="90"/>
-        <v>9325.0884125265729</v>
-      </c>
-      <c r="AX18" s="1">
-        <f t="shared" ref="AX18:CC18" si="91">AW18*(1+$AZ$25)</f>
-        <v>9231.8375284013073</v>
-      </c>
-      <c r="AY18" s="1">
+        <v>9881.5947166046772</v>
+      </c>
+      <c r="CP18" s="1">
+        <f t="shared" si="90"/>
+        <v>9782.7787694386298</v>
+      </c>
+      <c r="CQ18" s="1">
+        <f t="shared" si="90"/>
+        <v>9684.9509817442431</v>
+      </c>
+      <c r="CR18" s="1">
+        <f t="shared" si="90"/>
+        <v>9588.1014719268005</v>
+      </c>
+      <c r="CS18" s="1">
+        <f t="shared" si="90"/>
+        <v>9492.2204572075316</v>
+      </c>
+      <c r="CT18" s="1">
+        <f t="shared" si="90"/>
+        <v>9397.2982526354554</v>
+      </c>
+      <c r="CU18" s="1">
+        <f t="shared" si="90"/>
+        <v>9303.3252701091005</v>
+      </c>
+      <c r="CV18" s="1">
+        <f t="shared" si="90"/>
+        <v>9210.29201740801</v>
+      </c>
+      <c r="CW18" s="1">
+        <f t="shared" si="90"/>
+        <v>9118.1890972339297</v>
+      </c>
+      <c r="CX18" s="1">
+        <f t="shared" si="90"/>
+        <v>9027.0072062615909</v>
+      </c>
+      <c r="CY18" s="1">
+        <f t="shared" si="90"/>
+        <v>8936.7371341989747</v>
+      </c>
+      <c r="CZ18" s="1">
+        <f t="shared" si="90"/>
+        <v>8847.3697628569844</v>
+      </c>
+      <c r="DA18" s="1">
+        <f t="shared" si="90"/>
+        <v>8758.896065228415</v>
+      </c>
+      <c r="DB18" s="1">
+        <f t="shared" si="90"/>
+        <v>8671.3071045761299</v>
+      </c>
+      <c r="DC18" s="1">
+        <f t="shared" si="90"/>
+        <v>8584.5940335303676</v>
+      </c>
+      <c r="DD18" s="1">
+        <f t="shared" si="90"/>
+        <v>8498.7480931950631</v>
+      </c>
+      <c r="DE18" s="1">
+        <f t="shared" si="90"/>
+        <v>8413.7606122631132</v>
+      </c>
+      <c r="DF18" s="1">
+        <f t="shared" si="90"/>
+        <v>8329.6230061404822</v>
+      </c>
+      <c r="DG18" s="1">
+        <f t="shared" si="90"/>
+        <v>8246.3267760790768</v>
+      </c>
+      <c r="DH18" s="1">
+        <f t="shared" si="90"/>
+        <v>8163.8635083182862</v>
+      </c>
+      <c r="DI18" s="1">
+        <f t="shared" si="90"/>
+        <v>8082.2248732351036</v>
+      </c>
+      <c r="DJ18" s="1">
+        <f t="shared" ref="DJ18:EO18" si="91">DI18*(1+$AZ$25)</f>
+        <v>8001.4026245027526</v>
+      </c>
+      <c r="DK18" s="1">
         <f t="shared" si="91"/>
-        <v>9139.519153117295</v>
-      </c>
-      <c r="AZ18" s="1">
+        <v>7921.3885982577249</v>
+      </c>
+      <c r="DL18" s="1">
         <f t="shared" si="91"/>
-        <v>9048.1239615861214</v>
-      </c>
-      <c r="BA18" s="1">
+        <v>7842.1747122751476</v>
+      </c>
+      <c r="DM18" s="1">
         <f t="shared" si="91"/>
-        <v>8957.64272197026</v>
-      </c>
-      <c r="BB18" s="1">
+        <v>7763.7529651523964</v>
+      </c>
+      <c r="DN18" s="1">
         <f t="shared" si="91"/>
-        <v>8868.0662947505571</v>
-      </c>
-      <c r="BC18" s="1">
+        <v>7686.1154355008721</v>
+      </c>
+      <c r="DO18" s="1">
         <f t="shared" si="91"/>
-        <v>8779.3856318030521</v>
-      </c>
-      <c r="BD18" s="1">
+        <v>7609.2542811458634</v>
+      </c>
+      <c r="DP18" s="1">
         <f t="shared" si="91"/>
-        <v>8691.5917754850216</v>
-      </c>
-      <c r="BE18" s="1">
+        <v>7533.1617383344046</v>
+      </c>
+      <c r="DQ18" s="1">
         <f t="shared" si="91"/>
-        <v>8604.6758577301716</v>
-      </c>
-      <c r="BF18" s="1">
+        <v>7457.8301209510601</v>
+      </c>
+      <c r="DR18" s="1">
         <f t="shared" si="91"/>
-        <v>8518.6290991528695</v>
-      </c>
-      <c r="BG18" s="1">
+        <v>7383.2518197415493</v>
+      </c>
+      <c r="DS18" s="1">
         <f t="shared" si="91"/>
-        <v>8433.4428081613405</v>
-      </c>
-      <c r="BH18" s="1">
+        <v>7309.4193015441333</v>
+      </c>
+      <c r="DT18" s="1">
         <f t="shared" si="91"/>
-        <v>8349.1083800797278</v>
-      </c>
-      <c r="BI18" s="1">
+        <v>7236.325108528692</v>
+      </c>
+      <c r="DU18" s="1">
         <f t="shared" si="91"/>
-        <v>8265.6172962789296</v>
-      </c>
-      <c r="BJ18" s="1">
+        <v>7163.9618574434053</v>
+      </c>
+      <c r="DV18" s="1">
         <f t="shared" si="91"/>
-        <v>8182.9611233161404</v>
-      </c>
-      <c r="BK18" s="1">
+        <v>7092.322238868971</v>
+      </c>
+      <c r="DW18" s="1">
         <f t="shared" si="91"/>
-        <v>8101.1315120829786</v>
-      </c>
-      <c r="BL18" s="1">
+        <v>7021.3990164802808</v>
+      </c>
+      <c r="DX18" s="1">
         <f t="shared" si="91"/>
-        <v>8020.1201969621488</v>
-      </c>
-      <c r="BM18" s="1">
+        <v>6951.1850263154784</v>
+      </c>
+      <c r="DY18" s="1">
         <f t="shared" si="91"/>
-        <v>7939.9189949925276</v>
-      </c>
-      <c r="BN18" s="1">
+        <v>6881.6731760523235</v>
+      </c>
+      <c r="DZ18" s="1">
         <f t="shared" si="91"/>
-        <v>7860.5198050426025</v>
-      </c>
-      <c r="BO18" s="1">
+        <v>6812.8564442918005</v>
+      </c>
+      <c r="EA18" s="1">
         <f t="shared" si="91"/>
-        <v>7781.9146069921762</v>
-      </c>
-      <c r="BP18" s="1">
+        <v>6744.7278798488824</v>
+      </c>
+      <c r="EB18" s="1">
         <f t="shared" si="91"/>
-        <v>7704.0954609222545</v>
-      </c>
-      <c r="BQ18" s="1">
+        <v>6677.2806010503937</v>
+      </c>
+      <c r="EC18" s="1">
         <f t="shared" si="91"/>
-        <v>7627.0545063130321</v>
-      </c>
-      <c r="BR18" s="1">
+        <v>6610.50779503989</v>
+      </c>
+      <c r="ED18" s="1">
         <f t="shared" si="91"/>
-        <v>7550.7839612499019</v>
-      </c>
-      <c r="BS18" s="1">
+        <v>6544.4027170894906</v>
+      </c>
+      <c r="EE18" s="1">
         <f t="shared" si="91"/>
-        <v>7475.2761216374029</v>
-      </c>
-      <c r="BT18" s="1">
+        <v>6478.9586899185961</v>
+      </c>
+      <c r="EF18" s="1">
         <f t="shared" si="91"/>
-        <v>7400.5233604210289</v>
-      </c>
-      <c r="BU18" s="1">
+        <v>6414.1691030194097</v>
+      </c>
+      <c r="EG18" s="1">
         <f t="shared" si="91"/>
-        <v>7326.5181268168189</v>
-      </c>
-      <c r="BV18" s="1">
+        <v>6350.0274119892156</v>
+      </c>
+      <c r="EH18" s="1">
         <f t="shared" si="91"/>
-        <v>7253.252945548651</v>
-      </c>
-      <c r="BW18" s="1">
+        <v>6286.5271378693233</v>
+      </c>
+      <c r="EI18" s="1">
         <f t="shared" si="91"/>
-        <v>7180.7204160931642</v>
-      </c>
-      <c r="BX18" s="1">
+        <v>6223.66186649063</v>
+      </c>
+      <c r="EJ18" s="1">
         <f t="shared" si="91"/>
-        <v>7108.9132119322321</v>
-      </c>
-      <c r="BY18" s="1">
+        <v>6161.425247825724</v>
+      </c>
+      <c r="EK18" s="1">
         <f t="shared" si="91"/>
-        <v>7037.82407981291</v>
-      </c>
-      <c r="BZ18" s="1">
+        <v>6099.8109953474668</v>
+      </c>
+      <c r="EL18" s="1">
         <f t="shared" si="91"/>
-        <v>6967.4458390147811</v>
-      </c>
-      <c r="CA18" s="1">
+        <v>6038.8128853939925</v>
+      </c>
+      <c r="EM18" s="1">
         <f t="shared" si="91"/>
-        <v>6897.7713806246329</v>
-      </c>
-      <c r="CB18" s="1">
+        <v>5978.4247565400528</v>
+      </c>
+      <c r="EN18" s="1">
         <f t="shared" si="91"/>
-        <v>6828.7936668183866</v>
-      </c>
-      <c r="CC18" s="1">
+        <v>5918.6405089746522</v>
+      </c>
+      <c r="EO18" s="1">
         <f t="shared" si="91"/>
-        <v>6760.5057301502029</v>
-      </c>
-      <c r="CD18" s="1">
-        <f t="shared" ref="CD18:DI18" si="92">CC18*(1+$AZ$25)</f>
-        <v>6692.9006728487011</v>
-      </c>
-      <c r="CE18" s="1">
+        <v>5859.4541038849056</v>
+      </c>
+      <c r="EP18" s="1">
+        <f t="shared" ref="EP18:FJ18" si="92">EO18*(1+$AZ$25)</f>
+        <v>5800.8595628460562</v>
+      </c>
+      <c r="EQ18" s="1">
         <f t="shared" si="92"/>
-        <v>6625.9716661202137</v>
-      </c>
-      <c r="CF18" s="1">
+        <v>5742.850967217596</v>
+      </c>
+      <c r="ER18" s="1">
         <f t="shared" si="92"/>
-        <v>6559.7119494590115</v>
-      </c>
-      <c r="CG18" s="1">
+        <v>5685.42245754542</v>
+      </c>
+      <c r="ES18" s="1">
         <f t="shared" si="92"/>
-        <v>6494.114829964421</v>
-      </c>
-      <c r="CH18" s="1">
+        <v>5628.5682329699657</v>
+      </c>
+      <c r="ET18" s="1">
         <f t="shared" si="92"/>
-        <v>6429.1736816647772</v>
-      </c>
-      <c r="CI18" s="1">
+        <v>5572.282550640266</v>
+      </c>
+      <c r="EU18" s="1">
         <f t="shared" si="92"/>
-        <v>6364.881944848129</v>
-      </c>
-      <c r="CJ18" s="1">
+        <v>5516.5597251338631</v>
+      </c>
+      <c r="EV18" s="1">
         <f t="shared" si="92"/>
-        <v>6301.2331253996481</v>
-      </c>
-      <c r="CK18" s="1">
+        <v>5461.3941278825241</v>
+      </c>
+      <c r="EW18" s="1">
         <f t="shared" si="92"/>
-        <v>6238.2207941456518</v>
-      </c>
-      <c r="CL18" s="1">
+        <v>5406.7801866036989</v>
+      </c>
+      <c r="EX18" s="1">
         <f t="shared" si="92"/>
-        <v>6175.8385862041951</v>
-      </c>
-      <c r="CM18" s="1">
+        <v>5352.7123847376615</v>
+      </c>
+      <c r="EY18" s="1">
         <f t="shared" si="92"/>
-        <v>6114.0802003421531</v>
-      </c>
-      <c r="CN18" s="1">
+        <v>5299.1852608902846</v>
+      </c>
+      <c r="EZ18" s="1">
         <f t="shared" si="92"/>
-        <v>6052.9393983387317</v>
-      </c>
-      <c r="CO18" s="1">
+        <v>5246.1934082813814</v>
+      </c>
+      <c r="FA18" s="1">
         <f t="shared" si="92"/>
-        <v>5992.4100043553444</v>
-      </c>
-      <c r="CP18" s="1">
+        <v>5193.7314741985674</v>
+      </c>
+      <c r="FB18" s="1">
         <f t="shared" si="92"/>
-        <v>5932.4859043117913</v>
-      </c>
-      <c r="CQ18" s="1">
+        <v>5141.7941594565818</v>
+      </c>
+      <c r="FC18" s="1">
         <f t="shared" si="92"/>
-        <v>5873.1610452686737</v>
-      </c>
-      <c r="CR18" s="1">
+        <v>5090.3762178620163</v>
+      </c>
+      <c r="FD18" s="1">
         <f t="shared" si="92"/>
-        <v>5814.4294348159865</v>
-      </c>
-      <c r="CS18" s="1">
+        <v>5039.4724556833962</v>
+      </c>
+      <c r="FE18" s="1">
         <f t="shared" si="92"/>
-        <v>5756.2851404678267</v>
-      </c>
-      <c r="CT18" s="1">
+        <v>4989.077731126562</v>
+      </c>
+      <c r="FF18" s="1">
         <f t="shared" si="92"/>
-        <v>5698.7222890631483</v>
-      </c>
-      <c r="CU18" s="1">
+        <v>4939.186953815296</v>
+      </c>
+      <c r="FG18" s="1">
         <f t="shared" si="92"/>
-        <v>5641.7350661725168</v>
-      </c>
-      <c r="CV18" s="1">
+        <v>4889.7950842771434</v>
+      </c>
+      <c r="FH18" s="1">
         <f t="shared" si="92"/>
-        <v>5585.3177155107915</v>
-      </c>
-      <c r="CW18" s="1">
+        <v>4840.8971334343723</v>
+      </c>
+      <c r="FI18" s="1">
         <f t="shared" si="92"/>
-        <v>5529.4645383556835</v>
-      </c>
-      <c r="CX18" s="1">
+        <v>4792.4881621000286</v>
+      </c>
+      <c r="FJ18" s="1">
         <f t="shared" si="92"/>
-        <v>5474.1698929721269</v>
-      </c>
-      <c r="CY18" s="1">
-        <f t="shared" si="92"/>
-        <v>5419.4281940424053</v>
-      </c>
-      <c r="CZ18" s="1">
-        <f t="shared" si="92"/>
-        <v>5365.2339121019813</v>
-      </c>
-      <c r="DA18" s="1">
-        <f t="shared" si="92"/>
-        <v>5311.581572980961</v>
-      </c>
-      <c r="DB18" s="1">
-        <f t="shared" si="92"/>
-        <v>5258.4657572511514</v>
-      </c>
-      <c r="DC18" s="1">
-        <f t="shared" si="92"/>
-        <v>5205.8810996786397</v>
-      </c>
-      <c r="DD18" s="1">
-        <f t="shared" si="92"/>
-        <v>5153.822288681853</v>
-      </c>
-      <c r="DE18" s="1">
-        <f t="shared" si="92"/>
-        <v>5102.2840657950346</v>
-      </c>
-      <c r="DF18" s="1">
-        <f t="shared" si="92"/>
-        <v>5051.2612251370838</v>
-      </c>
-      <c r="DG18" s="1">
-        <f t="shared" si="92"/>
-        <v>5000.7486128857126</v>
-      </c>
-      <c r="DH18" s="1">
-        <f t="shared" si="92"/>
-        <v>4950.7411267568559</v>
-      </c>
-      <c r="DI18" s="1">
-        <f t="shared" si="92"/>
-        <v>4901.2337154892875</v>
-      </c>
-      <c r="DJ18" s="1">
-        <f t="shared" ref="DJ18:EO18" si="93">DI18*(1+$AZ$25)</f>
-        <v>4852.221378334395</v>
-      </c>
-      <c r="DK18" s="1">
-        <f t="shared" si="93"/>
-        <v>4803.6991645510507</v>
-      </c>
-      <c r="DL18" s="1">
-        <f t="shared" si="93"/>
-        <v>4755.6621729055405</v>
-      </c>
-      <c r="DM18" s="1">
-        <f t="shared" si="93"/>
-        <v>4708.1055511764853</v>
-      </c>
-      <c r="DN18" s="1">
-        <f t="shared" si="93"/>
-        <v>4661.0244956647202</v>
-      </c>
-      <c r="DO18" s="1">
-        <f t="shared" si="93"/>
-        <v>4614.4142507080733</v>
-      </c>
-      <c r="DP18" s="1">
-        <f t="shared" si="93"/>
-        <v>4568.2701082009926</v>
-      </c>
-      <c r="DQ18" s="1">
-        <f t="shared" si="93"/>
-        <v>4522.5874071189828</v>
-      </c>
-      <c r="DR18" s="1">
-        <f t="shared" si="93"/>
-        <v>4477.3615330477933</v>
-      </c>
-      <c r="DS18" s="1">
-        <f t="shared" si="93"/>
-        <v>4432.5879177173156</v>
-      </c>
-      <c r="DT18" s="1">
-        <f t="shared" si="93"/>
-        <v>4388.2620385401424</v>
-      </c>
-      <c r="DU18" s="1">
-        <f t="shared" si="93"/>
-        <v>4344.379418154741</v>
-      </c>
-      <c r="DV18" s="1">
-        <f t="shared" si="93"/>
-        <v>4300.9356239731933</v>
-      </c>
-      <c r="DW18" s="1">
-        <f t="shared" si="93"/>
-        <v>4257.9262677334609</v>
-      </c>
-      <c r="DX18" s="1">
-        <f t="shared" si="93"/>
-        <v>4215.3470050561264</v>
-      </c>
-      <c r="DY18" s="1">
-        <f t="shared" si="93"/>
-        <v>4173.1935350055646</v>
-      </c>
-      <c r="DZ18" s="1">
-        <f t="shared" si="93"/>
-        <v>4131.4615996555085</v>
-      </c>
-      <c r="EA18" s="1">
-        <f t="shared" si="93"/>
-        <v>4090.1469836589536</v>
-      </c>
-      <c r="EB18" s="1">
-        <f t="shared" si="93"/>
-        <v>4049.245513822364</v>
-      </c>
-      <c r="EC18" s="1">
-        <f t="shared" si="93"/>
-        <v>4008.7530586841403</v>
-      </c>
-      <c r="ED18" s="1">
-        <f t="shared" si="93"/>
-        <v>3968.6655280972991</v>
-      </c>
-      <c r="EE18" s="1">
-        <f t="shared" si="93"/>
-        <v>3928.9788728163262</v>
-      </c>
-      <c r="EF18" s="1">
-        <f t="shared" si="93"/>
-        <v>3889.6890840881629</v>
-      </c>
-      <c r="EG18" s="1">
-        <f t="shared" si="93"/>
-        <v>3850.7921932472814</v>
-      </c>
-      <c r="EH18" s="1">
-        <f t="shared" si="93"/>
-        <v>3812.2842713148084</v>
-      </c>
-      <c r="EI18" s="1">
-        <f t="shared" si="93"/>
-        <v>3774.1614286016602</v>
-      </c>
-      <c r="EJ18" s="1">
-        <f t="shared" si="93"/>
-        <v>3736.4198143156436</v>
-      </c>
-      <c r="EK18" s="1">
-        <f t="shared" si="93"/>
-        <v>3699.0556161724871</v>
-      </c>
-      <c r="EL18" s="1">
-        <f t="shared" si="93"/>
-        <v>3662.0650600107624</v>
-      </c>
-      <c r="EM18" s="1">
-        <f t="shared" si="93"/>
-        <v>3625.4444094106548</v>
-      </c>
-      <c r="EN18" s="1">
-        <f t="shared" si="93"/>
-        <v>3589.1899653165483</v>
-      </c>
-      <c r="EO18" s="1">
-        <f t="shared" si="93"/>
-        <v>3553.2980656633827</v>
-      </c>
-      <c r="EP18" s="1">
-        <f t="shared" ref="EP18:FJ18" si="94">EO18*(1+$AZ$25)</f>
-        <v>3517.7650850067489</v>
-      </c>
-      <c r="EQ18" s="1">
-        <f t="shared" si="94"/>
-        <v>3482.5874341566814</v>
-      </c>
-      <c r="ER18" s="1">
-        <f t="shared" si="94"/>
-        <v>3447.7615598151147</v>
-      </c>
-      <c r="ES18" s="1">
-        <f t="shared" si="94"/>
-        <v>3413.2839442169634</v>
-      </c>
-      <c r="ET18" s="1">
-        <f t="shared" si="94"/>
-        <v>3379.1511047747936</v>
-      </c>
-      <c r="EU18" s="1">
-        <f t="shared" si="94"/>
-        <v>3345.3595937270456</v>
-      </c>
-      <c r="EV18" s="1">
-        <f t="shared" si="94"/>
-        <v>3311.905997789775</v>
-      </c>
-      <c r="EW18" s="1">
-        <f t="shared" si="94"/>
-        <v>3278.7869378118771</v>
-      </c>
-      <c r="EX18" s="1">
-        <f t="shared" si="94"/>
-        <v>3245.9990684337581</v>
-      </c>
-      <c r="EY18" s="1">
-        <f t="shared" si="94"/>
-        <v>3213.5390777494204</v>
-      </c>
-      <c r="EZ18" s="1">
-        <f t="shared" si="94"/>
-        <v>3181.4036869719262</v>
-      </c>
-      <c r="FA18" s="1">
-        <f t="shared" si="94"/>
-        <v>3149.5896501022071</v>
-      </c>
-      <c r="FB18" s="1">
-        <f t="shared" si="94"/>
-        <v>3118.0937536011852</v>
-      </c>
-      <c r="FC18" s="1">
-        <f t="shared" si="94"/>
-        <v>3086.9128160651735</v>
-      </c>
-      <c r="FD18" s="1">
-        <f t="shared" si="94"/>
-        <v>3056.0436879045219</v>
-      </c>
-      <c r="FE18" s="1">
-        <f t="shared" si="94"/>
-        <v>3025.4832510254769</v>
-      </c>
-      <c r="FF18" s="1">
-        <f t="shared" si="94"/>
-        <v>2995.2284185152221</v>
-      </c>
-      <c r="FG18" s="1">
-        <f t="shared" si="94"/>
-        <v>2965.2761343300699</v>
-      </c>
-      <c r="FH18" s="1">
-        <f t="shared" si="94"/>
-        <v>2935.623372986769</v>
-      </c>
-      <c r="FI18" s="1">
-        <f t="shared" si="94"/>
-        <v>2906.2671392569014</v>
-      </c>
-      <c r="FJ18" s="1">
-        <f t="shared" si="94"/>
-        <v>2877.2044678643324</v>
+        <v>4744.5632804790284</v>
       </c>
     </row>
     <row r="19" spans="2:166" x14ac:dyDescent="0.3">
@@ -4288,12 +4279,12 @@
         <v>2365.1999999999998</v>
       </c>
       <c r="AC19" s="5">
-        <f>2365.2</f>
-        <v>2365.1999999999998</v>
+        <f>2377.2</f>
+        <v>2377.1999999999998</v>
       </c>
       <c r="AD19" s="5">
-        <f>2365.2</f>
-        <v>2365.1999999999998</v>
+        <f>2377.2</f>
+        <v>2377.1999999999998</v>
       </c>
       <c r="AF19" s="5">
         <v>1742</v>
@@ -4314,52 +4305,52 @@
         <v>1821.2</v>
       </c>
       <c r="AL19" s="5">
-        <f t="shared" ref="AL19" si="95">2249+95.4+1</f>
+        <f t="shared" ref="AL19" si="93">2249+95.4+1</f>
         <v>2345.4</v>
       </c>
       <c r="AM19" s="5">
-        <f t="shared" ref="AM19:AW19" si="96">2365.2</f>
-        <v>2365.1999999999998</v>
+        <f>2377.2</f>
+        <v>2377.1999999999998</v>
       </c>
       <c r="AN19" s="5">
-        <f t="shared" si="96"/>
-        <v>2365.1999999999998</v>
+        <f>2377.2</f>
+        <v>2377.1999999999998</v>
       </c>
       <c r="AO19" s="5">
-        <f t="shared" si="96"/>
-        <v>2365.1999999999998</v>
+        <f>2377.2</f>
+        <v>2377.1999999999998</v>
       </c>
       <c r="AP19" s="5">
-        <f t="shared" si="96"/>
-        <v>2365.1999999999998</v>
+        <f>2377.2</f>
+        <v>2377.1999999999998</v>
       </c>
       <c r="AQ19" s="5">
-        <f t="shared" si="96"/>
-        <v>2365.1999999999998</v>
+        <f>2377.2</f>
+        <v>2377.1999999999998</v>
       </c>
       <c r="AR19" s="5">
-        <f t="shared" si="96"/>
-        <v>2365.1999999999998</v>
+        <f>2377.2</f>
+        <v>2377.1999999999998</v>
       </c>
       <c r="AS19" s="5">
-        <f t="shared" si="96"/>
-        <v>2365.1999999999998</v>
+        <f>2377.2</f>
+        <v>2377.1999999999998</v>
       </c>
       <c r="AT19" s="5">
-        <f t="shared" si="96"/>
-        <v>2365.1999999999998</v>
+        <f>2377.2</f>
+        <v>2377.1999999999998</v>
       </c>
       <c r="AU19" s="5">
-        <f t="shared" si="96"/>
-        <v>2365.1999999999998</v>
+        <f>2377.2</f>
+        <v>2377.1999999999998</v>
       </c>
       <c r="AV19" s="5">
-        <f t="shared" si="96"/>
-        <v>2365.1999999999998</v>
+        <f>2377.2</f>
+        <v>2377.1999999999998</v>
       </c>
       <c r="AW19" s="5">
-        <f t="shared" si="96"/>
-        <v>2365.1999999999998</v>
+        <f>2377.2</f>
+        <v>2377.1999999999998</v>
       </c>
     </row>
     <row r="20" spans="2:166" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -4383,7 +4374,7 @@
         <v>-9.1446613088404113E-2</v>
       </c>
       <c r="G20" s="7">
-        <f t="shared" ref="G20" si="97">G18/G19</f>
+        <f t="shared" ref="G20" si="94">G18/G19</f>
         <v>-2.9870415110915882E-2</v>
       </c>
       <c r="H20" s="13">
@@ -4399,84 +4390,84 @@
         <v>-8.5074626865671646E-2</v>
       </c>
       <c r="K20" s="7">
-        <f t="shared" ref="K20:M20" si="98">K18/K19</f>
+        <f t="shared" ref="K20:M20" si="95">K18/K19</f>
         <v>-6.7812431363935846E-2</v>
       </c>
       <c r="L20" s="7">
-        <f t="shared" si="98"/>
+        <f t="shared" si="95"/>
         <v>-7.8409839666154141E-2</v>
       </c>
       <c r="M20" s="7">
-        <f t="shared" si="98"/>
+        <f t="shared" si="95"/>
         <v>-5.6007028332967258E-2</v>
       </c>
       <c r="N20" s="7">
-        <f t="shared" ref="N20:O20" si="99">N18/N19</f>
+        <f t="shared" ref="N20:O20" si="96">N18/N19</f>
         <v>-8.5767625741269518E-2</v>
       </c>
       <c r="O20" s="7">
-        <f t="shared" si="99"/>
+        <f t="shared" si="96"/>
         <v>-5.5677575225126279E-2</v>
       </c>
       <c r="P20" s="7">
-        <f t="shared" ref="P20:Q20" si="100">P18/P19</f>
+        <f t="shared" ref="P20:Q20" si="97">P18/P19</f>
         <v>-9.8506479244454201E-2</v>
       </c>
       <c r="Q20" s="7">
+        <f t="shared" si="97"/>
+        <v>-6.8032066769163207E-2</v>
+      </c>
+      <c r="R20" s="7">
+        <f t="shared" ref="R20" si="98">R18/R19</f>
+        <v>1.8394465187788266E-2</v>
+      </c>
+      <c r="S20" s="7">
+        <f t="shared" ref="S20" si="99">S18/S19</f>
+        <v>1.0597408302218341E-2</v>
+      </c>
+      <c r="T20" s="7">
+        <f t="shared" ref="T20:U20" si="100">T18/T19</f>
+        <v>1.5319569514605764E-2</v>
+      </c>
+      <c r="U20" s="7">
         <f t="shared" si="100"/>
-        <v>-6.8032066769163207E-2</v>
-      </c>
-      <c r="R20" s="7">
-        <f t="shared" ref="R20" si="101">R18/R19</f>
-        <v>1.8394465187788266E-2</v>
-      </c>
-      <c r="S20" s="7">
-        <f t="shared" ref="S20" si="102">S18/S19</f>
-        <v>1.0597408302218341E-2</v>
-      </c>
-      <c r="T20" s="7">
-        <f t="shared" ref="T20:U20" si="103">T18/T19</f>
-        <v>1.5319569514605764E-2</v>
-      </c>
-      <c r="U20" s="7">
+        <v>4.0412914561827398E-2</v>
+      </c>
+      <c r="V20" s="7">
+        <f t="shared" ref="V20" si="101">V18/V19</f>
+        <v>5.320667691631889E-2</v>
+      </c>
+      <c r="W20" s="7">
+        <f t="shared" ref="W20:X20" si="102">W18/W19</f>
+        <v>5.8203382385240504E-2</v>
+      </c>
+      <c r="X20" s="7">
+        <f t="shared" si="102"/>
+        <v>6.0507278735375529E-2</v>
+      </c>
+      <c r="Y20" s="7">
+        <f t="shared" ref="Y20:Z20" si="103">Y18/Y19</f>
+        <v>6.2991089065449257E-2</v>
+      </c>
+      <c r="Z20" s="7">
         <f t="shared" si="103"/>
-        <v>4.0412914561827398E-2</v>
-      </c>
-      <c r="V20" s="7">
-        <f t="shared" ref="V20" si="104">V18/V19</f>
-        <v>5.320667691631889E-2</v>
-      </c>
-      <c r="W20" s="7">
-        <f t="shared" ref="W20:X20" si="105">W18/W19</f>
-        <v>5.8203382385240504E-2</v>
-      </c>
-      <c r="X20" s="7">
-        <f t="shared" si="105"/>
-        <v>6.0507278735375529E-2</v>
-      </c>
-      <c r="Y20" s="7">
-        <f t="shared" ref="Y20:Z20" si="106">Y18/Y19</f>
-        <v>6.2991089065449257E-2</v>
-      </c>
-      <c r="Z20" s="7">
-        <f t="shared" si="106"/>
         <v>3.3725590517608948E-2</v>
       </c>
       <c r="AA20" s="7">
-        <f t="shared" ref="AA20:AD20" si="107">AA18/AA19</f>
+        <f t="shared" ref="AA20:AD20" si="104">AA18/AA19</f>
         <v>9.1114233405713785E-2</v>
       </c>
       <c r="AB20" s="7">
-        <f t="shared" si="107"/>
+        <f t="shared" si="104"/>
         <v>0.13821241332656864</v>
       </c>
       <c r="AC20" s="7">
-        <f t="shared" si="107"/>
-        <v>0.14118473279215293</v>
+        <f t="shared" si="104"/>
+        <v>0.20010937237085646</v>
       </c>
       <c r="AD20" s="7">
-        <f t="shared" si="107"/>
-        <v>0.10121323778116022</v>
+        <f t="shared" si="104"/>
+        <v>0.1340889912502104</v>
       </c>
       <c r="AF20" s="7">
         <f>AF18/AF19</f>
@@ -4491,64 +4482,64 @@
         <v>-0.66951779563719871</v>
       </c>
       <c r="AI20" s="7">
-        <f t="shared" ref="AI20" si="108">AI18/AI19</f>
+        <f t="shared" ref="AI20" si="105">AI18/AI19</f>
         <v>-0.28799692510432667</v>
       </c>
       <c r="AJ20" s="7">
-        <f t="shared" ref="AJ20" si="109">AJ18/AJ19</f>
+        <f t="shared" ref="AJ20" si="106">AJ18/AJ19</f>
         <v>-0.20382165605095534</v>
       </c>
       <c r="AK20" s="7">
-        <f t="shared" ref="AK20" si="110">AK18/AK19</f>
+        <f t="shared" ref="AK20" si="107">AK18/AK19</f>
         <v>0.1195365692949704</v>
       </c>
       <c r="AL20" s="7">
-        <f t="shared" ref="AL20" si="111">AL18/AL19</f>
+        <f t="shared" ref="AL20" si="108">AL18/AL19</f>
         <v>0.19787669480685605</v>
       </c>
       <c r="AM20" s="7">
-        <f t="shared" ref="AM20" si="112">AM18/AM19</f>
-        <v>0.47108899036022317</v>
+        <f t="shared" ref="AM20" si="109">AM18/AM19</f>
+        <v>0.56173496129900724</v>
       </c>
       <c r="AN20" s="7">
-        <f t="shared" ref="AN20" si="113">AN18/AN19</f>
-        <v>0.68318787163876238</v>
+        <f t="shared" ref="AN20" si="110">AN18/AN19</f>
+        <v>0.92934075450109366</v>
       </c>
       <c r="AO20" s="7">
-        <f t="shared" ref="AO20" si="114">AO18/AO19</f>
-        <v>1.04595910970066</v>
+        <f t="shared" ref="AO20" si="111">AO18/AO19</f>
+        <v>1.4549692548207978</v>
       </c>
       <c r="AP20" s="7">
-        <f t="shared" ref="AP20" si="115">AP18/AP19</f>
-        <v>1.4963961668971422</v>
+        <f t="shared" ref="AP20" si="112">AP18/AP19</f>
+        <v>2.1470803220100962</v>
       </c>
       <c r="AQ20" s="7">
-        <f t="shared" ref="AQ20" si="116">AQ18/AQ19</f>
-        <v>1.9260513033086479</v>
+        <f t="shared" ref="AQ20" si="113">AQ18/AQ19</f>
+        <v>2.9049284420479862</v>
       </c>
       <c r="AR20" s="7">
-        <f t="shared" ref="AR20:AS20" si="117">AR18/AR19</f>
-        <v>2.1819516356349986</v>
+        <f t="shared" ref="AR20:AS20" si="114">AR18/AR19</f>
+        <v>3.4989690584494828</v>
       </c>
       <c r="AS20" s="7">
-        <f t="shared" si="117"/>
-        <v>2.5000162699324493</v>
+        <f t="shared" si="114"/>
+        <v>4.1651509050501732</v>
       </c>
       <c r="AT20" s="7">
-        <f t="shared" ref="AT20:AW20" si="118">AT18/AT19</f>
-        <v>2.8073471283185696</v>
+        <f t="shared" ref="AT20:AW20" si="115">AT18/AT19</f>
+        <v>4.7106590734402944</v>
       </c>
       <c r="AU20" s="7">
-        <f t="shared" si="118"/>
-        <v>3.1477967951765633</v>
+        <f t="shared" si="115"/>
+        <v>5.2390998628024299</v>
       </c>
       <c r="AV20" s="7">
-        <f t="shared" si="118"/>
-        <v>3.5249107365070937</v>
+        <f t="shared" si="115"/>
+        <v>5.8231481515118793</v>
       </c>
       <c r="AW20" s="7">
-        <f t="shared" si="118"/>
-        <v>3.9426215172190826</v>
+        <f t="shared" si="115"/>
+        <v>6.4686366030049287</v>
       </c>
     </row>
     <row r="21" spans="2:166" x14ac:dyDescent="0.3">
@@ -4573,88 +4564,88 @@
         <v>0.51916010498687659</v>
       </c>
       <c r="J22" s="9">
-        <f t="shared" ref="J22" si="119">J3/F3-1</f>
+        <f t="shared" ref="J22" si="116">J3/F3-1</f>
         <v>0.40409764603313003</v>
       </c>
       <c r="K22" s="9">
-        <f t="shared" ref="K22" si="120">K3/G3-1</f>
+        <f t="shared" ref="K22" si="117">K3/G3-1</f>
         <v>0.48800697775839508</v>
       </c>
       <c r="L22" s="9">
-        <f t="shared" ref="L22" si="121">L3/H3-1</f>
+        <f t="shared" ref="L22" si="118">L3/H3-1</f>
         <v>0.49106788408098478</v>
       </c>
       <c r="M22" s="9">
-        <f t="shared" ref="M22" si="122">M3/I3-1</f>
+        <f t="shared" ref="M22" si="119">M3/I3-1</f>
         <v>0.35487214927436095</v>
       </c>
       <c r="N22" s="9">
-        <f t="shared" ref="N22" si="123">N3/J3-1</f>
+        <f t="shared" ref="N22" si="120">N3/J3-1</f>
         <v>0.34399254889785769</v>
       </c>
       <c r="O22" s="9">
-        <f t="shared" ref="O22" si="124">O3/K3-1</f>
+        <f t="shared" ref="O22" si="121">O3/K3-1</f>
         <v>0.30832356389214532</v>
       </c>
       <c r="P22" s="9">
-        <f t="shared" ref="P22" si="125">P3/L3-1</f>
+        <f t="shared" ref="P22" si="122">P3/L3-1</f>
         <v>0.2593184238551649</v>
       </c>
       <c r="Q22" s="9">
-        <f t="shared" ref="Q22" si="126">Q3/M3-1</f>
+        <f t="shared" ref="Q22" si="123">Q3/M3-1</f>
         <v>0.21882172915072662</v>
       </c>
       <c r="R22" s="9">
-        <f t="shared" ref="R22" si="127">R3/N3-1</f>
+        <f t="shared" ref="R22" si="124">R3/N3-1</f>
         <v>0.17486717486717507</v>
       </c>
       <c r="S22" s="9">
-        <f t="shared" ref="S22" si="128">S3/O3-1</f>
+        <f t="shared" ref="S22" si="125">S3/O3-1</f>
         <v>0.17652329749103957</v>
       </c>
       <c r="T22" s="9">
-        <f t="shared" ref="T22" si="129">T3/P3-1</f>
+        <f t="shared" ref="T22" si="126">T3/P3-1</f>
         <v>0.12748414376321349</v>
       </c>
       <c r="U22" s="9">
-        <f t="shared" ref="U22" si="130">U3/Q3-1</f>
+        <f t="shared" ref="U22" si="127">U3/Q3-1</f>
         <v>0.16802678384599301</v>
       </c>
       <c r="V22" s="9">
-        <f t="shared" ref="V22" si="131">V3/R3-1</f>
+        <f t="shared" ref="V22" si="128">V3/R3-1</f>
         <v>0.19622493118364126</v>
       </c>
       <c r="W22" s="9">
-        <f t="shared" ref="W22" si="132">W3/S3-1</f>
+        <f t="shared" ref="W22" si="129">W3/S3-1</f>
         <v>0.20773038842345759</v>
       </c>
       <c r="X22" s="9">
-        <f t="shared" ref="X22" si="133">X3/T3-1</f>
+        <f t="shared" ref="X22" si="130">X3/T3-1</f>
         <v>0.27151696981061324</v>
       </c>
       <c r="Y22" s="9">
-        <f t="shared" ref="Y22" si="134">Y3/U3-1</f>
+        <f t="shared" ref="Y22" si="131">Y3/U3-1</f>
         <v>0.29971336438552476</v>
       </c>
       <c r="Z22" s="9">
-        <f t="shared" ref="Z22" si="135">Z3/V3-1</f>
+        <f t="shared" ref="Z22" si="132">Z3/V3-1</f>
         <v>0.36012491781722566</v>
       </c>
       <c r="AA22" s="9">
-        <f t="shared" ref="AA22" si="136">AA3/W3-1</f>
+        <f t="shared" ref="AA22" si="133">AA3/W3-1</f>
         <v>0.39350465079615327</v>
       </c>
       <c r="AB22" s="9">
-        <f t="shared" ref="AB22" si="137">AB3/X3-1</f>
+        <f t="shared" ref="AB22" si="134">AB3/X3-1</f>
         <v>0.48016516737944248</v>
       </c>
       <c r="AC22" s="9">
-        <f t="shared" ref="AC22" si="138">AC3/Y3-1</f>
-        <v>0.52</v>
+        <f t="shared" ref="AC22" si="135">AC3/Y3-1</f>
+        <v>0.62798070296347341</v>
       </c>
       <c r="AD22" s="9">
-        <f t="shared" ref="AD22" si="139">AD3/Z3-1</f>
-        <v>0.47</v>
+        <f t="shared" ref="AD22" si="136">AD3/Z3-1</f>
+        <v>0.60604229607250759</v>
       </c>
       <c r="AG22" s="9">
         <f>AG3/AF3-1</f>
@@ -4665,63 +4656,63 @@
         <v>0.47145165634257991</v>
       </c>
       <c r="AI22" s="9">
-        <f t="shared" ref="AI22:AR22" si="140">AI3/AH3-1</f>
+        <f t="shared" ref="AI22:AR22" si="137">AI3/AH3-1</f>
         <v>0.41100027454928201</v>
       </c>
       <c r="AJ22" s="9">
-        <f t="shared" si="140"/>
+        <f t="shared" si="137"/>
         <v>0.23615254896873772</v>
       </c>
       <c r="AK22" s="9">
-        <f t="shared" si="140"/>
+        <f t="shared" si="137"/>
         <v>0.1674799307413819</v>
       </c>
       <c r="AL22" s="9">
-        <f t="shared" si="140"/>
+        <f t="shared" si="137"/>
         <v>0.28776234775965137</v>
       </c>
       <c r="AM22" s="9">
-        <f t="shared" si="140"/>
-        <v>0.46813184895651561</v>
+        <f t="shared" si="137"/>
+        <v>0.53475954491519495</v>
       </c>
       <c r="AN22" s="9">
-        <f t="shared" si="140"/>
+        <f t="shared" si="137"/>
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="AO22" s="9">
+        <f t="shared" si="137"/>
+        <v>0.35000000000000009</v>
+      </c>
+      <c r="AP22" s="9">
+        <f t="shared" si="137"/>
         <v>0.30000000000000004</v>
       </c>
-      <c r="AO22" s="9">
-        <f t="shared" si="140"/>
-        <v>0.27</v>
-      </c>
-      <c r="AP22" s="9">
-        <f t="shared" si="140"/>
-        <v>0.24</v>
-      </c>
       <c r="AQ22" s="9">
-        <f t="shared" si="140"/>
-        <v>0.17999999999999994</v>
+        <f t="shared" si="137"/>
+        <v>0.25</v>
       </c>
       <c r="AR22" s="9">
-        <f t="shared" si="140"/>
-        <v>0.1399999999999999</v>
+        <f t="shared" si="137"/>
+        <v>0.19999999999999996</v>
       </c>
       <c r="AS22" s="9">
-        <f t="shared" ref="AS22" si="141">AS3/AR3-1</f>
+        <f t="shared" ref="AS22" si="138">AS3/AR3-1</f>
+        <v>0.14999999999999991</v>
+      </c>
+      <c r="AT22" s="9">
+        <f t="shared" ref="AT22" si="139">AT3/AS3-1</f>
         <v>0.10000000000000009</v>
       </c>
-      <c r="AT22" s="9">
-        <f t="shared" ref="AT22" si="142">AT3/AS3-1</f>
+      <c r="AU22" s="9">
+        <f t="shared" ref="AU22" si="140">AU3/AT3-1</f>
         <v>0.10000000000000009</v>
       </c>
-      <c r="AU22" s="9">
-        <f t="shared" ref="AU22" si="143">AU3/AT3-1</f>
+      <c r="AV22" s="9">
+        <f t="shared" ref="AV22" si="141">AV3/AU3-1</f>
         <v>0.10000000000000009</v>
       </c>
-      <c r="AV22" s="9">
-        <f t="shared" ref="AV22" si="144">AV3/AU3-1</f>
-        <v>0.10000000000000009</v>
-      </c>
       <c r="AW22" s="9">
-        <f t="shared" ref="AW22" si="145">AW3/AV3-1</f>
+        <f t="shared" ref="AW22" si="142">AW3/AV3-1</f>
         <v>0.10000000000000009</v>
       </c>
     </row>
@@ -4730,184 +4721,184 @@
         <v>35</v>
       </c>
       <c r="D23" s="15">
-        <f t="shared" ref="D23:I23" si="146">D5/D3</f>
+        <f t="shared" ref="D23:I23" si="143">D5/D3</f>
         <v>0.6734221192819918</v>
       </c>
       <c r="E23" s="9">
+        <f t="shared" si="143"/>
+        <v>0.65826771653543314</v>
+      </c>
+      <c r="F23" s="9">
+        <f t="shared" si="143"/>
+        <v>0.66913687881429817</v>
+      </c>
+      <c r="G23" s="15">
+        <f t="shared" si="143"/>
+        <v>0.71958133449629302</v>
+      </c>
+      <c r="H23" s="15">
+        <f t="shared" si="143"/>
+        <v>0.72846367606192941</v>
+      </c>
+      <c r="I23" s="9">
+        <f t="shared" si="143"/>
+        <v>0.48410504492052514</v>
+      </c>
+      <c r="J23" s="9">
+        <f t="shared" ref="J23:N23" si="144">J5/J3</f>
+        <v>0.78112387457311394</v>
+      </c>
+      <c r="K23" s="9">
+        <f t="shared" si="144"/>
+        <v>0.78282532239155933</v>
+      </c>
+      <c r="L23" s="9">
+        <f t="shared" si="144"/>
+        <v>0.75798722044728439</v>
+      </c>
+      <c r="M23" s="9">
+        <f t="shared" si="144"/>
+        <v>0.7786279010456516</v>
+      </c>
+      <c r="N23" s="9">
+        <f t="shared" si="144"/>
+        <v>0.79764379764379756</v>
+      </c>
+      <c r="O23" s="9">
+        <f t="shared" ref="O23:Z23" si="145">O5/O3</f>
+        <v>0.78853046594982079</v>
+      </c>
+      <c r="P23" s="9">
+        <f t="shared" si="145"/>
+        <v>0.78393234672304446</v>
+      </c>
+      <c r="Q23" s="9">
+        <f t="shared" si="145"/>
+        <v>0.77484829462230587</v>
+      </c>
+      <c r="R23" s="9">
+        <f t="shared" si="145"/>
+        <v>0.79492725127801811</v>
+      </c>
+      <c r="S23" s="9">
+        <f t="shared" si="145"/>
+        <v>0.79512566641279514</v>
+      </c>
+      <c r="T23" s="9">
+        <f t="shared" si="145"/>
+        <v>0.79954997187324206</v>
+      </c>
+      <c r="U23" s="9">
+        <f t="shared" si="145"/>
+        <v>0.80670010748835552</v>
+      </c>
+      <c r="V23" s="9">
+        <f t="shared" si="145"/>
+        <v>0.82149901380670609</v>
+      </c>
+      <c r="W23" s="9">
+        <f t="shared" si="145"/>
+        <v>0.81664827368752957</v>
+      </c>
+      <c r="X23" s="9">
+        <f t="shared" si="145"/>
+        <v>0.8103524553900604</v>
+      </c>
+      <c r="Y23" s="9">
+        <f t="shared" si="145"/>
+        <v>0.79793246037215715</v>
+      </c>
+      <c r="Z23" s="9">
+        <f t="shared" si="145"/>
+        <v>0.78912386706948645</v>
+      </c>
+      <c r="AA23" s="9">
+        <f t="shared" ref="AA23:AD23" si="146">AA5/AA3</f>
+        <v>0.80427650186672694</v>
+      </c>
+      <c r="AB23" s="9">
         <f t="shared" si="146"/>
-        <v>0.65826771653543314</v>
-      </c>
-      <c r="F23" s="9">
+        <v>0.80781109893394443</v>
+      </c>
+      <c r="AC23" s="9">
         <f t="shared" si="146"/>
-        <v>0.66913687881429817</v>
-      </c>
-      <c r="G23" s="15">
+        <v>0.82448564897129795</v>
+      </c>
+      <c r="AD23" s="9">
         <f t="shared" si="146"/>
-        <v>0.71958133449629302</v>
-      </c>
-      <c r="H23" s="15">
-        <f t="shared" si="146"/>
-        <v>0.72846367606192941</v>
-      </c>
-      <c r="I23" s="9">
-        <f t="shared" si="146"/>
-        <v>0.48410504492052514</v>
-      </c>
-      <c r="J23" s="9">
-        <f t="shared" ref="J23:N23" si="147">J5/J3</f>
-        <v>0.78112387457311394</v>
-      </c>
-      <c r="K23" s="9">
+        <v>0.79</v>
+      </c>
+      <c r="AF23" s="9">
+        <f t="shared" ref="AF23:AH23" si="147">AF5/AF3</f>
+        <v>0.72220356063150826</v>
+      </c>
+      <c r="AG23" s="9">
         <f t="shared" si="147"/>
-        <v>0.78282532239155933</v>
-      </c>
-      <c r="L23" s="9">
+        <v>0.67357931591704823</v>
+      </c>
+      <c r="AH23" s="9">
         <f t="shared" si="147"/>
-        <v>0.75798722044728439</v>
-      </c>
-      <c r="M23" s="9">
-        <f t="shared" si="147"/>
-        <v>0.7786279010456516</v>
-      </c>
-      <c r="N23" s="9">
-        <f t="shared" si="147"/>
-        <v>0.79764379764379756</v>
-      </c>
-      <c r="O23" s="9">
-        <f t="shared" ref="O23:Z23" si="148">O5/O3</f>
-        <v>0.78853046594982079</v>
-      </c>
-      <c r="P23" s="9">
+        <v>0.67740459412464527</v>
+      </c>
+      <c r="AI23" s="9">
+        <f t="shared" ref="AI23:AR23" si="148">AI5/AI3</f>
+        <v>0.77986768711895182</v>
+      </c>
+      <c r="AJ23" s="9">
         <f t="shared" si="148"/>
-        <v>0.78393234672304446</v>
-      </c>
-      <c r="Q23" s="9">
+        <v>0.78566556482501704</v>
+      </c>
+      <c r="AK23" s="9">
         <f t="shared" si="148"/>
-        <v>0.77484829462230587</v>
-      </c>
-      <c r="R23" s="9">
+        <v>0.80630084041166683</v>
+      </c>
+      <c r="AL23" s="9">
         <f t="shared" si="148"/>
-        <v>0.79492725127801811</v>
-      </c>
-      <c r="S23" s="9">
+        <v>0.80247085921686323</v>
+      </c>
+      <c r="AM23" s="9">
         <f t="shared" si="148"/>
-        <v>0.79512566641279514</v>
-      </c>
-      <c r="T23" s="9">
+        <v>0.80619642085635668</v>
+      </c>
+      <c r="AN23" s="9">
         <f t="shared" si="148"/>
-        <v>0.79954997187324206</v>
-      </c>
-      <c r="U23" s="9">
+        <v>0.80999999999999994</v>
+      </c>
+      <c r="AO23" s="9">
         <f t="shared" si="148"/>
-        <v>0.80670010748835552</v>
-      </c>
-      <c r="V23" s="9">
+        <v>0.81</v>
+      </c>
+      <c r="AP23" s="9">
         <f t="shared" si="148"/>
-        <v>0.82149901380670609</v>
-      </c>
-      <c r="W23" s="9">
+        <v>0.80999999999999994</v>
+      </c>
+      <c r="AQ23" s="9">
         <f t="shared" si="148"/>
-        <v>0.81664827368752957</v>
-      </c>
-      <c r="X23" s="9">
+        <v>0.81</v>
+      </c>
+      <c r="AR23" s="9">
         <f t="shared" si="148"/>
-        <v>0.8103524553900604</v>
-      </c>
-      <c r="Y23" s="9">
-        <f t="shared" si="148"/>
-        <v>0.79793246037215715</v>
-      </c>
-      <c r="Z23" s="9">
-        <f t="shared" si="148"/>
-        <v>0.78912386706948645</v>
-      </c>
-      <c r="AA23" s="9">
-        <f t="shared" ref="AA23:AD23" si="149">AA5/AA3</f>
-        <v>0.80427650186672694</v>
-      </c>
-      <c r="AB23" s="9">
+        <v>0.81</v>
+      </c>
+      <c r="AS23" s="9">
+        <f t="shared" ref="AS23:AW23" si="149">AS5/AS3</f>
+        <v>0.81</v>
+      </c>
+      <c r="AT23" s="9">
         <f t="shared" si="149"/>
-        <v>0.80781109893394443</v>
-      </c>
-      <c r="AC23" s="9">
+        <v>0.81</v>
+      </c>
+      <c r="AU23" s="9">
         <f t="shared" si="149"/>
-        <v>0.8</v>
-      </c>
-      <c r="AD23" s="9">
+        <v>0.81</v>
+      </c>
+      <c r="AV23" s="9">
         <f t="shared" si="149"/>
-        <v>0.79</v>
-      </c>
-      <c r="AF23" s="9">
-        <f t="shared" ref="AF23:AH23" si="150">AF5/AF3</f>
-        <v>0.72220356063150826</v>
-      </c>
-      <c r="AG23" s="9">
-        <f t="shared" si="150"/>
-        <v>0.67357931591704823</v>
-      </c>
-      <c r="AH23" s="9">
-        <f t="shared" si="150"/>
-        <v>0.67740459412464527</v>
-      </c>
-      <c r="AI23" s="9">
-        <f t="shared" ref="AI23:AR23" si="151">AI5/AI3</f>
-        <v>0.77986768711895182</v>
-      </c>
-      <c r="AJ23" s="9">
-        <f t="shared" si="151"/>
-        <v>0.78566556482501704</v>
-      </c>
-      <c r="AK23" s="9">
-        <f t="shared" si="151"/>
-        <v>0.80630084041166683</v>
-      </c>
-      <c r="AL23" s="9">
-        <f t="shared" si="151"/>
-        <v>0.80247085921686323</v>
-      </c>
-      <c r="AM23" s="9">
-        <f t="shared" si="151"/>
-        <v>0.79987062566781997</v>
-      </c>
-      <c r="AN23" s="9">
-        <f t="shared" si="151"/>
-        <v>0.8</v>
-      </c>
-      <c r="AO23" s="9">
-        <f t="shared" si="151"/>
-        <v>0.8</v>
-      </c>
-      <c r="AP23" s="9">
-        <f t="shared" si="151"/>
-        <v>0.8</v>
-      </c>
-      <c r="AQ23" s="9">
-        <f t="shared" si="151"/>
-        <v>0.8</v>
-      </c>
-      <c r="AR23" s="9">
-        <f t="shared" si="151"/>
-        <v>0.8</v>
-      </c>
-      <c r="AS23" s="9">
-        <f t="shared" ref="AS23:AW23" si="152">AS5/AS3</f>
-        <v>0.8</v>
-      </c>
-      <c r="AT23" s="9">
-        <f t="shared" si="152"/>
-        <v>0.8</v>
-      </c>
-      <c r="AU23" s="9">
-        <f t="shared" si="152"/>
-        <v>0.8</v>
-      </c>
-      <c r="AV23" s="9">
-        <f t="shared" si="152"/>
-        <v>0.8</v>
+        <v>0.81</v>
       </c>
       <c r="AW23" s="9">
-        <f t="shared" si="152"/>
-        <v>0.8</v>
+        <f t="shared" si="149"/>
+        <v>0.81</v>
       </c>
     </row>
     <row r="24" spans="2:166" x14ac:dyDescent="0.3">
@@ -4919,180 +4910,180 @@
         <v>-0.87319050376375251</v>
       </c>
       <c r="E24" s="9">
-        <f t="shared" ref="E24:G24" si="153">E10/E3</f>
+        <f t="shared" ref="E24:G24" si="150">E10/E3</f>
         <v>-0.75748031496063017</v>
       </c>
       <c r="F24" s="9">
+        <f t="shared" si="150"/>
+        <v>-0.6425457715780295</v>
+      </c>
+      <c r="G24" s="15">
+        <f t="shared" si="150"/>
+        <v>-0.30658525948539034</v>
+      </c>
+      <c r="H24" s="15">
+        <f t="shared" ref="H24:J24" si="151">H10/H3</f>
+        <v>-0.39341008336641514</v>
+      </c>
+      <c r="I24" s="9">
+        <f t="shared" si="151"/>
+        <v>-2.9291637871458192</v>
+      </c>
+      <c r="J24" s="9">
+        <f t="shared" si="151"/>
+        <v>-0.48587395218876123</v>
+      </c>
+      <c r="K24" s="9">
+        <f t="shared" ref="K24:N24" si="152">K10/K3</f>
+        <v>-0.33440797186400928</v>
+      </c>
+      <c r="L24" s="9">
+        <f t="shared" si="152"/>
+        <v>-0.38924387646432357</v>
+      </c>
+      <c r="M24" s="9">
+        <f t="shared" si="152"/>
+        <v>-0.23437898495281809</v>
+      </c>
+      <c r="N24" s="9">
+        <f t="shared" si="152"/>
+        <v>-0.13629013629013642</v>
+      </c>
+      <c r="O24" s="9">
+        <f t="shared" ref="O24:Z24" si="153">O10/O3</f>
+        <v>-8.8261648745519672E-2</v>
+      </c>
+      <c r="P24" s="9">
         <f t="shared" si="153"/>
-        <v>-0.6425457715780295</v>
-      </c>
-      <c r="G24" s="15">
+        <v>-8.837209302325584E-2</v>
+      </c>
+      <c r="Q24" s="9">
         <f t="shared" si="153"/>
-        <v>-0.30658525948539034</v>
-      </c>
-      <c r="H24" s="15">
-        <f t="shared" ref="H24:J24" si="154">H10/H3</f>
-        <v>-0.39341008336641514</v>
-      </c>
-      <c r="I24" s="9">
+        <v>-0.13015275162167828</v>
+      </c>
+      <c r="R24" s="9">
+        <f t="shared" si="153"/>
+        <v>-3.4998033818324836E-2</v>
+      </c>
+      <c r="S24" s="9">
+        <f t="shared" si="153"/>
+        <v>7.9969535415080825E-3</v>
+      </c>
+      <c r="T24" s="9">
+        <f t="shared" si="153"/>
+        <v>1.8938683667729276E-2</v>
+      </c>
+      <c r="U24" s="9">
+        <f t="shared" si="153"/>
+        <v>7.1658903618774722E-2</v>
+      </c>
+      <c r="V24" s="9">
+        <f t="shared" si="153"/>
+        <v>0.10815253122945423</v>
+      </c>
+      <c r="W24" s="9">
+        <f t="shared" si="153"/>
+        <v>0.12738451836670348</v>
+      </c>
+      <c r="X24" s="9">
+        <f t="shared" si="153"/>
+        <v>0.15528683085090689</v>
+      </c>
+      <c r="Y24" s="9">
+        <f t="shared" si="153"/>
+        <v>0.15589248793935212</v>
+      </c>
+      <c r="Z24" s="9">
+        <f t="shared" si="153"/>
+        <v>1.3413897280966794E-2</v>
+      </c>
+      <c r="AA24" s="9">
+        <f t="shared" ref="AA24:AD24" si="154">AA10/AA3</f>
+        <v>0.19923068220386911</v>
+      </c>
+      <c r="AB24" s="9">
         <f t="shared" si="154"/>
-        <v>-2.9291637871458192</v>
-      </c>
-      <c r="J24" s="9">
+        <v>0.26840689449038563</v>
+      </c>
+      <c r="AC24" s="9">
         <f t="shared" si="154"/>
-        <v>-0.48587395218876123</v>
-      </c>
-      <c r="K24" s="9">
-        <f t="shared" ref="K24:N24" si="155">K10/K3</f>
-        <v>-0.33440797186400928</v>
-      </c>
-      <c r="L24" s="9">
+        <v>0.33299466598933197</v>
+      </c>
+      <c r="AD24" s="9">
+        <f t="shared" si="154"/>
+        <v>0.19555530474040642</v>
+      </c>
+      <c r="AF24" s="9">
+        <f t="shared" ref="AF24:AR24" si="155">AF10/AF3</f>
+        <v>-1.047195162915687</v>
+      </c>
+      <c r="AG24" s="9">
         <f t="shared" si="155"/>
-        <v>-0.38924387646432357</v>
-      </c>
-      <c r="M24" s="9">
+        <v>-0.77619175868569867</v>
+      </c>
+      <c r="AH24" s="9">
         <f t="shared" si="155"/>
-        <v>-0.23437898495281809</v>
-      </c>
-      <c r="N24" s="9">
+        <v>-1.0740367896037342</v>
+      </c>
+      <c r="AI24" s="9">
         <f t="shared" si="155"/>
-        <v>-0.13629013629013642</v>
-      </c>
-      <c r="O24" s="9">
-        <f t="shared" ref="O24:Z24" si="156">O10/O3</f>
-        <v>-8.8261648745519672E-2</v>
-      </c>
-      <c r="P24" s="9">
+        <v>-0.26670125826955493</v>
+      </c>
+      <c r="AJ24" s="9">
+        <f t="shared" si="155"/>
+        <v>-8.4579463770397087E-2</v>
+      </c>
+      <c r="AK24" s="9">
+        <f t="shared" si="155"/>
+        <v>5.3975102242595899E-2</v>
+      </c>
+      <c r="AL24" s="9">
+        <f t="shared" si="155"/>
+        <v>0.10829203601591407</v>
+      </c>
+      <c r="AM24" s="9">
+        <f t="shared" si="155"/>
+        <v>0.2498335493553448</v>
+      </c>
+      <c r="AN24" s="9">
+        <f t="shared" si="155"/>
+        <v>0.35183380654307533</v>
+      </c>
+      <c r="AO24" s="9">
+        <f t="shared" si="155"/>
+        <v>0.42090919835577589</v>
+      </c>
+      <c r="AP24" s="9">
+        <f t="shared" si="155"/>
+        <v>0.48672735868462069</v>
+      </c>
+      <c r="AQ24" s="9">
+        <f t="shared" si="155"/>
+        <v>0.53194334355612749</v>
+      </c>
+      <c r="AR24" s="9">
+        <f t="shared" si="155"/>
+        <v>0.56917332291850808</v>
+      </c>
+      <c r="AS24" s="9">
+        <f t="shared" ref="AS24:AW24" si="156">AS10/AS3</f>
+        <v>0.59014253452134946</v>
+      </c>
+      <c r="AT24" s="9">
         <f t="shared" si="156"/>
-        <v>-8.837209302325584E-2</v>
-      </c>
-      <c r="Q24" s="9">
+        <v>0.60627630994142057</v>
+      </c>
+      <c r="AU24" s="9">
         <f t="shared" si="156"/>
-        <v>-0.13015275162167828</v>
-      </c>
-      <c r="R24" s="9">
+        <v>0.61198953070229212</v>
+      </c>
+      <c r="AV24" s="9">
         <f t="shared" si="156"/>
-        <v>-3.4998033818324836E-2</v>
-      </c>
-      <c r="S24" s="9">
+        <v>0.61731115744563003</v>
+      </c>
+      <c r="AW24" s="9">
         <f t="shared" si="156"/>
-        <v>7.9969535415080825E-3</v>
-      </c>
-      <c r="T24" s="9">
-        <f t="shared" si="156"/>
-        <v>1.8938683667729276E-2</v>
-      </c>
-      <c r="U24" s="9">
-        <f t="shared" si="156"/>
-        <v>7.1658903618774722E-2</v>
-      </c>
-      <c r="V24" s="9">
-        <f t="shared" si="156"/>
-        <v>0.10815253122945423</v>
-      </c>
-      <c r="W24" s="9">
-        <f t="shared" si="156"/>
-        <v>0.12738451836670348</v>
-      </c>
-      <c r="X24" s="9">
-        <f t="shared" si="156"/>
-        <v>0.15528683085090689</v>
-      </c>
-      <c r="Y24" s="9">
-        <f t="shared" si="156"/>
-        <v>0.15589248793935212</v>
-      </c>
-      <c r="Z24" s="9">
-        <f t="shared" si="156"/>
-        <v>1.3413897280966794E-2</v>
-      </c>
-      <c r="AA24" s="9">
-        <f t="shared" ref="AA24:AD24" si="157">AA10/AA3</f>
-        <v>0.19923068220386911</v>
-      </c>
-      <c r="AB24" s="9">
-        <f t="shared" si="157"/>
-        <v>0.26840689449038563</v>
-      </c>
-      <c r="AC24" s="9">
-        <f t="shared" si="157"/>
-        <v>0.26205647647720276</v>
-      </c>
-      <c r="AD24" s="9">
-        <f t="shared" si="157"/>
-        <v>0.15319399058717156</v>
-      </c>
-      <c r="AF24" s="9">
-        <f t="shared" ref="AF24:AR24" si="158">AF10/AF3</f>
-        <v>-1.047195162915687</v>
-      </c>
-      <c r="AG24" s="9">
-        <f t="shared" si="158"/>
-        <v>-0.77619175868569867</v>
-      </c>
-      <c r="AH24" s="9">
-        <f t="shared" si="158"/>
-        <v>-1.0740367896037342</v>
-      </c>
-      <c r="AI24" s="9">
-        <f t="shared" si="158"/>
-        <v>-0.26670125826955493</v>
-      </c>
-      <c r="AJ24" s="9">
-        <f t="shared" si="158"/>
-        <v>-8.4579463770397087E-2</v>
-      </c>
-      <c r="AK24" s="9">
-        <f t="shared" si="158"/>
-        <v>5.3975102242595899E-2</v>
-      </c>
-      <c r="AL24" s="9">
-        <f t="shared" si="158"/>
-        <v>0.10829203601591407</v>
-      </c>
-      <c r="AM24" s="9">
-        <f t="shared" si="158"/>
-        <v>0.21889266981792505</v>
-      </c>
-      <c r="AN24" s="9">
-        <f t="shared" si="158"/>
-        <v>0.28637503735951858</v>
-      </c>
-      <c r="AO24" s="9">
-        <f t="shared" si="158"/>
-        <v>0.36004402087862736</v>
-      </c>
-      <c r="AP24" s="9">
-        <f t="shared" si="158"/>
-        <v>0.42552079170465512</v>
-      </c>
-      <c r="AQ24" s="9">
-        <f t="shared" si="158"/>
-        <v>0.46897153852185997</v>
-      </c>
-      <c r="AR24" s="9">
-        <f t="shared" si="158"/>
-        <v>0.49592190288798005</v>
-      </c>
-      <c r="AS24" s="9">
-        <f t="shared" ref="AS24:AW24" si="159">AS10/AS3</f>
-        <v>0.51640030995067243</v>
-      </c>
-      <c r="AT24" s="9">
-        <f t="shared" si="159"/>
-        <v>0.52611665104516891</v>
-      </c>
-      <c r="AU24" s="9">
-        <f t="shared" si="159"/>
-        <v>0.53512634915097479</v>
-      </c>
-      <c r="AV24" s="9">
-        <f t="shared" si="159"/>
-        <v>0.54348079648544945</v>
-      </c>
-      <c r="AW24" s="9">
-        <f t="shared" si="159"/>
-        <v>0.55122764765014398</v>
+        <v>0.62226814800336161</v>
       </c>
     </row>
     <row r="25" spans="2:166" x14ac:dyDescent="0.3">
@@ -5104,180 +5095,180 @@
         <v>0.68094962362478284</v>
       </c>
       <c r="E25" s="9">
-        <f t="shared" ref="E25:G25" si="160">E6/E3</f>
+        <f t="shared" ref="E25:G25" si="157">E6/E3</f>
         <v>0.62834645669291345</v>
       </c>
       <c r="F25" s="9">
+        <f t="shared" si="157"/>
+        <v>0.49215344376634701</v>
+      </c>
+      <c r="G25" s="15">
+        <f t="shared" si="157"/>
+        <v>0.43044047099869165</v>
+      </c>
+      <c r="H25" s="15">
+        <f t="shared" ref="H25:J25" si="158">H6/H3</f>
+        <v>0.40690750297737194</v>
+      </c>
+      <c r="I25" s="9">
+        <f t="shared" si="158"/>
+        <v>1.1572218382861093</v>
+      </c>
+      <c r="J25" s="9">
+        <f t="shared" si="158"/>
+        <v>0.45824278174479971</v>
+      </c>
+      <c r="K25" s="9">
+        <f t="shared" ref="K25:N25" si="159">K6/K3</f>
+        <v>0.39888628370457208</v>
+      </c>
+      <c r="L25" s="9">
+        <f t="shared" si="159"/>
+        <v>0.4323748668796592</v>
+      </c>
+      <c r="M25" s="9">
+        <f t="shared" si="159"/>
+        <v>0.39122672787554197</v>
+      </c>
+      <c r="N25" s="9">
+        <f t="shared" si="159"/>
+        <v>0.37560637560637561</v>
+      </c>
+      <c r="O25" s="9">
+        <f t="shared" ref="O25:Z25" si="160">O6/O3</f>
+        <v>0.35954301075268819</v>
+      </c>
+      <c r="P25" s="9">
         <f t="shared" si="160"/>
-        <v>0.49215344376634701</v>
-      </c>
-      <c r="G25" s="15">
+        <v>0.35708245243128967</v>
+      </c>
+      <c r="Q25" s="9">
         <f t="shared" si="160"/>
-        <v>0.43044047099869165</v>
-      </c>
-      <c r="H25" s="15">
-        <f t="shared" ref="H25:J25" si="161">H6/H3</f>
-        <v>0.40690750297737194</v>
-      </c>
-      <c r="I25" s="9">
+        <v>0.38271604938271608</v>
+      </c>
+      <c r="R25" s="9">
+        <f t="shared" si="160"/>
+        <v>0.37396775462052689</v>
+      </c>
+      <c r="S25" s="9">
+        <f t="shared" si="160"/>
+        <v>0.35624523990860618</v>
+      </c>
+      <c r="T25" s="9">
+        <f t="shared" si="160"/>
+        <v>0.34539658728670541</v>
+      </c>
+      <c r="U25" s="9">
+        <f t="shared" si="160"/>
+        <v>0.31601576495879613</v>
+      </c>
+      <c r="V25" s="9">
+        <f t="shared" si="160"/>
+        <v>0.32445759368836297</v>
+      </c>
+      <c r="W25" s="9">
+        <f t="shared" si="160"/>
+        <v>0.30458773451048399</v>
+      </c>
+      <c r="X25" s="9">
+        <f t="shared" si="160"/>
+        <v>0.29022268102049847</v>
+      </c>
+      <c r="Y25" s="9">
+        <f t="shared" si="160"/>
+        <v>0.28876636802205374</v>
+      </c>
+      <c r="Z25" s="9">
+        <f t="shared" si="160"/>
+        <v>0.34839879154078551</v>
+      </c>
+      <c r="AA25" s="9">
+        <f t="shared" ref="AA25:AD25" si="161">AA6/AA3</f>
+        <v>0.26733793415544749</v>
+      </c>
+      <c r="AB25" s="9">
         <f t="shared" si="161"/>
-        <v>1.1572218382861093</v>
-      </c>
-      <c r="J25" s="9">
+        <v>0.24290126531832221</v>
+      </c>
+      <c r="AC25" s="9">
         <f t="shared" si="161"/>
-        <v>0.45824278174479971</v>
-      </c>
-      <c r="K25" s="9">
-        <f t="shared" ref="K25:N25" si="162">K6/K3</f>
-        <v>0.39888628370457208</v>
-      </c>
-      <c r="L25" s="9">
+        <v>0.23249513165693</v>
+      </c>
+      <c r="AD25" s="9">
+        <f t="shared" si="161"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AF25" s="9">
+        <f t="shared" ref="AF25:AH25" si="162">AF6/AF3</f>
+        <v>0.77561303325495468</v>
+      </c>
+      <c r="AG25" s="9">
         <f t="shared" si="162"/>
-        <v>0.4323748668796592</v>
-      </c>
-      <c r="M25" s="9">
+        <v>0.60611365472663614</v>
+      </c>
+      <c r="AH25" s="9">
         <f t="shared" si="162"/>
-        <v>0.39122672787554197</v>
-      </c>
-      <c r="N25" s="9">
-        <f t="shared" si="162"/>
-        <v>0.37560637560637561</v>
-      </c>
-      <c r="O25" s="9">
-        <f t="shared" ref="O25:Z25" si="163">O6/O3</f>
-        <v>0.35954301075268819</v>
-      </c>
-      <c r="P25" s="9">
+        <v>0.62569781275739</v>
+      </c>
+      <c r="AI25" s="9">
+        <f t="shared" ref="AI25:AR25" si="163">AI6/AI3</f>
+        <v>0.39856012452977035</v>
+      </c>
+      <c r="AJ25" s="9">
         <f t="shared" si="163"/>
-        <v>0.35708245243128967</v>
-      </c>
-      <c r="Q25" s="9">
+        <v>0.36859226612099266</v>
+      </c>
+      <c r="AK25" s="9">
         <f t="shared" si="163"/>
-        <v>0.38271604938271608</v>
-      </c>
-      <c r="R25" s="9">
+        <v>0.33486135454586308</v>
+      </c>
+      <c r="AL25" s="9">
         <f t="shared" si="163"/>
-        <v>0.37396775462052689</v>
-      </c>
-      <c r="S25" s="9">
+        <v>0.30983457806937947</v>
+      </c>
+      <c r="AM25" s="9">
         <f t="shared" si="163"/>
-        <v>0.35624523990860618</v>
-      </c>
-      <c r="T25" s="9">
+        <v>0.25925142688223396</v>
+      </c>
+      <c r="AN25" s="9">
         <f t="shared" si="163"/>
-        <v>0.34539658728670541</v>
-      </c>
-      <c r="U25" s="9">
+        <v>0.23000000000000004</v>
+      </c>
+      <c r="AO25" s="9">
         <f t="shared" si="163"/>
-        <v>0.31601576495879613</v>
-      </c>
-      <c r="V25" s="9">
+        <v>0.21</v>
+      </c>
+      <c r="AP25" s="9">
         <f t="shared" si="163"/>
-        <v>0.32445759368836297</v>
-      </c>
-      <c r="W25" s="9">
+        <v>0.18</v>
+      </c>
+      <c r="AQ25" s="9">
         <f t="shared" si="163"/>
-        <v>0.30458773451048399</v>
-      </c>
-      <c r="X25" s="9">
+        <v>0.16</v>
+      </c>
+      <c r="AR25" s="9">
         <f t="shared" si="163"/>
-        <v>0.29022268102049847</v>
-      </c>
-      <c r="Y25" s="9">
-        <f t="shared" si="163"/>
-        <v>0.28876636802205374</v>
-      </c>
-      <c r="Z25" s="9">
-        <f t="shared" si="163"/>
-        <v>0.34839879154078551</v>
-      </c>
-      <c r="AA25" s="9">
-        <f t="shared" ref="AA25:AD25" si="164">AA6/AA3</f>
-        <v>0.26733793415544749</v>
-      </c>
-      <c r="AB25" s="9">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="AS25" s="9">
+        <f t="shared" ref="AS25:AW25" si="164">AS6/AS3</f>
+        <v>0.13</v>
+      </c>
+      <c r="AT25" s="9">
         <f t="shared" si="164"/>
-        <v>0.24290126531832221</v>
-      </c>
-      <c r="AC25" s="9">
+        <v>0.12</v>
+      </c>
+      <c r="AU25" s="9">
         <f t="shared" si="164"/>
-        <v>0.26</v>
-      </c>
-      <c r="AD25" s="9">
+        <v>0.12000000000000001</v>
+      </c>
+      <c r="AV25" s="9">
         <f t="shared" si="164"/>
-        <v>0.31</v>
-      </c>
-      <c r="AF25" s="9">
-        <f t="shared" ref="AF25:AH25" si="165">AF6/AF3</f>
-        <v>0.77561303325495468</v>
-      </c>
-      <c r="AG25" s="9">
-        <f t="shared" si="165"/>
-        <v>0.60611365472663614</v>
-      </c>
-      <c r="AH25" s="9">
-        <f t="shared" si="165"/>
-        <v>0.62569781275739</v>
-      </c>
-      <c r="AI25" s="9">
-        <f t="shared" ref="AI25:AR25" si="166">AI6/AI3</f>
-        <v>0.39856012452977035</v>
-      </c>
-      <c r="AJ25" s="9">
-        <f t="shared" si="166"/>
-        <v>0.36859226612099266</v>
-      </c>
-      <c r="AK25" s="9">
-        <f t="shared" si="166"/>
-        <v>0.33486135454586308</v>
-      </c>
-      <c r="AL25" s="9">
-        <f t="shared" si="166"/>
-        <v>0.30983457806937947</v>
-      </c>
-      <c r="AM25" s="9">
-        <f t="shared" si="166"/>
-        <v>0.27192008861874334</v>
-      </c>
-      <c r="AN25" s="9">
-        <f t="shared" si="166"/>
-        <v>0.25</v>
-      </c>
-      <c r="AO25" s="9">
-        <f t="shared" si="166"/>
-        <v>0.22</v>
-      </c>
-      <c r="AP25" s="9">
-        <f t="shared" si="166"/>
-        <v>0.19</v>
-      </c>
-      <c r="AQ25" s="9">
-        <f t="shared" si="166"/>
-        <v>0.17</v>
-      </c>
-      <c r="AR25" s="9">
-        <f t="shared" si="166"/>
-        <v>0.16</v>
-      </c>
-      <c r="AS25" s="9">
-        <f t="shared" ref="AS25:AW25" si="167">AS6/AS3</f>
-        <v>0.15</v>
-      </c>
-      <c r="AT25" s="9">
-        <f t="shared" si="167"/>
-        <v>0.15</v>
-      </c>
-      <c r="AU25" s="9">
-        <f t="shared" si="167"/>
-        <v>0.15</v>
-      </c>
-      <c r="AV25" s="9">
-        <f t="shared" si="167"/>
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="AW25" s="9">
-        <f t="shared" si="167"/>
-        <v>0.15</v>
+        <f t="shared" si="164"/>
+        <v>0.12</v>
       </c>
       <c r="AY25" t="s">
         <v>37</v>
@@ -5294,169 +5285,169 @@
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
       <c r="G26" s="15">
-        <f t="shared" ref="G26:J26" si="168">G7/C7-1</f>
+        <f t="shared" ref="G26:J26" si="165">G7/C7-1</f>
         <v>-0.13421052631578956</v>
       </c>
       <c r="H26" s="15">
-        <f t="shared" si="168"/>
+        <f t="shared" si="165"/>
         <v>0.11568123393316165</v>
       </c>
       <c r="I26" s="9">
-        <f t="shared" si="168"/>
+        <f t="shared" si="165"/>
         <v>3.1357048748353087</v>
       </c>
       <c r="J26" s="9">
-        <f t="shared" si="168"/>
+        <f t="shared" si="165"/>
         <v>0.24142480211081785</v>
       </c>
       <c r="K26" s="9">
-        <f t="shared" ref="K26:Z27" si="169">K7/G7-1</f>
+        <f t="shared" ref="K26:Z27" si="166">K7/G7-1</f>
         <v>0.49696048632218859</v>
       </c>
       <c r="L26" s="9">
-        <f t="shared" si="169"/>
+        <f t="shared" si="166"/>
         <v>0.27304147465437789</v>
       </c>
       <c r="M26" s="9">
-        <f t="shared" si="169"/>
+        <f t="shared" si="166"/>
         <v>-0.69958585536795148</v>
       </c>
       <c r="N26" s="9">
-        <f t="shared" si="169"/>
+        <f t="shared" si="166"/>
         <v>-0.10520722635494151</v>
       </c>
       <c r="O26" s="9">
-        <f t="shared" si="169"/>
+        <f t="shared" si="166"/>
         <v>-0.10050761421319798</v>
       </c>
       <c r="P26" s="9">
-        <f t="shared" si="169"/>
+        <f t="shared" si="166"/>
         <v>-0.20180995475113117</v>
       </c>
       <c r="Q26" s="9">
-        <f t="shared" si="169"/>
+        <f t="shared" si="166"/>
         <v>6.9989395546129485E-2</v>
       </c>
       <c r="R26" s="9">
-        <f t="shared" si="169"/>
+        <f t="shared" si="166"/>
         <v>-2.6128266033254244E-2</v>
       </c>
       <c r="S26" s="9">
-        <f t="shared" si="169"/>
+        <f t="shared" si="166"/>
         <v>1.6930022573363512E-2</v>
       </c>
       <c r="T26" s="9">
-        <f t="shared" si="169"/>
+        <f t="shared" si="166"/>
         <v>0.1281179138321995</v>
       </c>
       <c r="U26" s="9">
-        <f t="shared" si="169"/>
+        <f t="shared" si="166"/>
         <v>4.7571853320118818E-2</v>
       </c>
       <c r="V26" s="9">
-        <f t="shared" si="169"/>
+        <f t="shared" si="166"/>
         <v>0.33292682926829276</v>
       </c>
       <c r="W26" s="9">
-        <f t="shared" si="169"/>
+        <f t="shared" si="166"/>
         <v>0.22086570477247514</v>
       </c>
       <c r="X26" s="9">
-        <f t="shared" si="169"/>
+        <f t="shared" si="166"/>
         <v>9.3467336683417113E-2</v>
       </c>
       <c r="Y26" s="9">
-        <f t="shared" si="169"/>
+        <f t="shared" si="166"/>
         <v>0.11258278145695355</v>
       </c>
       <c r="Z26" s="9">
-        <f t="shared" si="169"/>
+        <f t="shared" si="166"/>
         <v>0.56907593778591048</v>
       </c>
       <c r="AA26" s="9">
-        <f t="shared" ref="AA26:AA27" si="170">AA7/W7-1</f>
+        <f t="shared" ref="AA26:AA27" si="167">AA7/W7-1</f>
         <v>0.22636363636363632</v>
       </c>
       <c r="AB26" s="9">
-        <f t="shared" ref="AB26:AB27" si="171">AB7/X7-1</f>
+        <f t="shared" ref="AB26:AB27" si="168">AB7/X7-1</f>
         <v>0.24080882352941169</v>
       </c>
       <c r="AC26" s="9">
-        <f t="shared" ref="AC26:AC27" si="172">AC7/Y7-1</f>
-        <v>0.25</v>
+        <f t="shared" ref="AC26:AC27" si="169">AC7/Y7-1</f>
+        <v>0.22619047619047605</v>
       </c>
       <c r="AD26" s="9">
-        <f t="shared" ref="AD26:AD27" si="173">AD7/Z7-1</f>
-        <v>0.14999999999999991</v>
+        <f t="shared" ref="AD26:AD27" si="170">AD7/Z7-1</f>
+        <v>0.16999999999999993</v>
       </c>
       <c r="AF26" s="9"/>
       <c r="AG26" s="9">
-        <f t="shared" ref="AG26:AR26" si="174">AG7/AF7-1</f>
+        <f t="shared" ref="AG26:AR26" si="171">AG7/AF7-1</f>
         <v>7.0402802101576345E-2</v>
       </c>
       <c r="AH26" s="9">
-        <f t="shared" si="174"/>
+        <f t="shared" si="171"/>
         <v>0.83442408376963351</v>
       </c>
       <c r="AI26" s="9">
-        <f t="shared" si="174"/>
+        <f t="shared" si="171"/>
         <v>-0.30877631109525516</v>
       </c>
       <c r="AJ26" s="9">
-        <f t="shared" si="174"/>
+        <f t="shared" si="171"/>
         <v>-7.1741935483870867E-2</v>
       </c>
       <c r="AK26" s="9">
-        <f t="shared" si="174"/>
+        <f t="shared" si="171"/>
         <v>0.12482624409229914</v>
       </c>
       <c r="AL26" s="9">
-        <f t="shared" si="174"/>
+        <f t="shared" si="171"/>
         <v>0.25531389026198692</v>
       </c>
       <c r="AM26" s="9">
-        <f t="shared" si="174"/>
-        <v>0.20914550108289043</v>
+        <f t="shared" si="171"/>
+        <v>0.21038590273675917</v>
       </c>
       <c r="AN26" s="9">
-        <f t="shared" si="174"/>
-        <v>0.12999999999999989</v>
+        <f t="shared" si="171"/>
+        <v>0.1399999999999999</v>
       </c>
       <c r="AO26" s="9">
-        <f t="shared" si="174"/>
+        <f t="shared" si="171"/>
         <v>7.0000000000000062E-2</v>
       </c>
       <c r="AP26" s="9">
-        <f t="shared" si="174"/>
+        <f t="shared" si="171"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AQ26" s="9">
-        <f t="shared" si="174"/>
+        <f t="shared" si="171"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AR26" s="9">
-        <f t="shared" si="174"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="171"/>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AS26" s="9">
-        <f t="shared" ref="AS26:AW27" si="175">AS7/AR7-1</f>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" ref="AS26:AW27" si="172">AS7/AR7-1</f>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AT26" s="9">
-        <f t="shared" si="175"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="172"/>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AU26" s="9">
-        <f t="shared" si="175"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="172"/>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AV26" s="9">
-        <f t="shared" si="175"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="172"/>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AW26" s="9">
-        <f t="shared" si="175"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="172"/>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AY26" t="s">
         <v>38</v>
@@ -5473,168 +5464,168 @@
       <c r="E27" s="9"/>
       <c r="F27" s="9"/>
       <c r="G27" s="15">
-        <f t="shared" ref="G27:J27" si="176">G8/C8-1</f>
+        <f t="shared" ref="G27:J27" si="173">G8/C8-1</f>
         <v>0.12380952380952381</v>
       </c>
       <c r="H27" s="15">
-        <f t="shared" si="176"/>
+        <f t="shared" si="173"/>
         <v>0.30125523012552313</v>
       </c>
       <c r="I27" s="9">
-        <f t="shared" si="176"/>
+        <f t="shared" si="173"/>
         <v>3.574898785425102</v>
       </c>
       <c r="J27" s="9">
-        <f t="shared" si="176"/>
+        <f t="shared" si="173"/>
         <v>0.48306595365418903</v>
       </c>
       <c r="K27" s="9">
+        <f t="shared" si="166"/>
+        <v>1.0706214689265536</v>
+      </c>
+      <c r="L27" s="9">
+        <f t="shared" si="166"/>
+        <v>0.69346195069667749</v>
+      </c>
+      <c r="M27" s="9">
+        <f t="shared" si="166"/>
+        <v>-0.55899705014749257</v>
+      </c>
+      <c r="N27" s="9">
+        <f t="shared" si="166"/>
+        <v>-5.3485576923076983E-2</v>
+      </c>
+      <c r="O27" s="9">
+        <f t="shared" si="166"/>
+        <v>-2.9331514324692942E-2</v>
+      </c>
+      <c r="P27" s="9">
+        <f t="shared" si="166"/>
+        <v>-1.5822784810126556E-2</v>
+      </c>
+      <c r="Q27" s="9">
+        <f t="shared" si="166"/>
+        <v>-5.351170568561936E-3</v>
+      </c>
+      <c r="R27" s="9">
+        <f t="shared" si="166"/>
+        <v>-4.8253968253968216E-2</v>
+      </c>
+      <c r="S27" s="9">
+        <f t="shared" si="166"/>
+        <v>-4.2867182009838523E-2</v>
+      </c>
+      <c r="T27" s="9">
+        <f t="shared" si="166"/>
+        <v>-0.14726688102893892</v>
+      </c>
+      <c r="U27" s="9">
+        <f t="shared" si="166"/>
+        <v>-0.13786146603900473</v>
+      </c>
+      <c r="V27" s="9">
+        <f t="shared" si="166"/>
+        <v>-0.15076717811874585</v>
+      </c>
+      <c r="W27" s="9">
+        <f t="shared" si="166"/>
+        <v>-1.6152716593245131E-2</v>
+      </c>
+      <c r="X27" s="9">
+        <f t="shared" si="166"/>
+        <v>4.5248868778280604E-2</v>
+      </c>
+      <c r="Y27" s="9">
+        <f t="shared" si="166"/>
+        <v>8.19032761310452E-2</v>
+      </c>
+      <c r="Z27" s="9">
+        <f t="shared" si="166"/>
+        <v>0.43047918303220745</v>
+      </c>
+      <c r="AA27" s="9">
+        <f t="shared" si="167"/>
+        <v>0.22089552238805976</v>
+      </c>
+      <c r="AB27" s="9">
+        <f t="shared" si="168"/>
+        <v>0.17316017316017307</v>
+      </c>
+      <c r="AC27" s="9">
         <f t="shared" si="169"/>
-        <v>1.0706214689265536</v>
-      </c>
-      <c r="L27" s="9">
-        <f t="shared" si="169"/>
-        <v>0.69346195069667749</v>
-      </c>
-      <c r="M27" s="9">
-        <f t="shared" si="169"/>
-        <v>-0.55899705014749257</v>
-      </c>
-      <c r="N27" s="9">
-        <f t="shared" si="169"/>
-        <v>-5.3485576923076983E-2</v>
-      </c>
-      <c r="O27" s="9">
-        <f t="shared" si="169"/>
-        <v>-2.9331514324692942E-2</v>
-      </c>
-      <c r="P27" s="9">
-        <f t="shared" si="169"/>
-        <v>-1.5822784810126556E-2</v>
-      </c>
-      <c r="Q27" s="9">
-        <f t="shared" si="169"/>
-        <v>-5.351170568561936E-3</v>
-      </c>
-      <c r="R27" s="9">
-        <f t="shared" si="169"/>
-        <v>-4.8253968253968216E-2</v>
-      </c>
-      <c r="S27" s="9">
-        <f t="shared" si="169"/>
-        <v>-4.2867182009838523E-2</v>
-      </c>
-      <c r="T27" s="9">
-        <f t="shared" si="169"/>
-        <v>-0.14726688102893892</v>
-      </c>
-      <c r="U27" s="9">
-        <f t="shared" si="169"/>
-        <v>-0.13786146603900473</v>
-      </c>
-      <c r="V27" s="9">
-        <f t="shared" si="169"/>
-        <v>-0.15076717811874585</v>
-      </c>
-      <c r="W27" s="9">
-        <f t="shared" si="169"/>
-        <v>-1.6152716593245131E-2</v>
-      </c>
-      <c r="X27" s="9">
-        <f t="shared" si="169"/>
-        <v>4.5248868778280604E-2</v>
-      </c>
-      <c r="Y27" s="9">
-        <f t="shared" si="169"/>
-        <v>8.19032761310452E-2</v>
-      </c>
-      <c r="Z27" s="9">
-        <f t="shared" si="169"/>
-        <v>0.43047918303220745</v>
-      </c>
-      <c r="AA27" s="9">
+        <v>0.16582552271088691</v>
+      </c>
+      <c r="AD27" s="9">
         <f t="shared" si="170"/>
-        <v>0.22089552238805976</v>
-      </c>
-      <c r="AB27" s="9">
-        <f t="shared" si="171"/>
-        <v>0.17316017316017307</v>
-      </c>
-      <c r="AC27" s="9">
-        <f t="shared" si="172"/>
-        <v>0.14999999999999991</v>
-      </c>
-      <c r="AD27" s="9">
-        <f t="shared" si="173"/>
-        <v>0.10000000000000009</v>
+        <v>0.12000000000000011</v>
       </c>
       <c r="AF27" s="9"/>
       <c r="AG27" s="9">
-        <f t="shared" ref="AG27:AR27" si="177">AG8/AF8-1</f>
+        <f t="shared" ref="AG27:AR27" si="174">AG8/AF8-1</f>
         <v>4.8007838014369586E-2</v>
       </c>
       <c r="AH27" s="9">
-        <f t="shared" si="177"/>
+        <f t="shared" si="174"/>
         <v>1.0863197257712685</v>
       </c>
       <c r="AI27" s="9">
-        <f t="shared" si="177"/>
+        <f t="shared" si="174"/>
         <v>-8.6482449589245669E-2</v>
       </c>
       <c r="AJ27" s="9">
-        <f t="shared" si="177"/>
+        <f t="shared" si="174"/>
         <v>-2.4852844996730017E-2</v>
       </c>
       <c r="AK27" s="9">
-        <f t="shared" si="177"/>
+        <f t="shared" si="174"/>
         <v>-0.12089201877934275</v>
       </c>
       <c r="AL27" s="9">
-        <f t="shared" si="177"/>
+        <f t="shared" si="174"/>
         <v>0.13179477398436013</v>
       </c>
       <c r="AM27" s="9">
-        <f t="shared" si="177"/>
-        <v>0.15607516009437128</v>
+        <f t="shared" si="174"/>
+        <v>0.16591169531513317</v>
       </c>
       <c r="AN27" s="9">
-        <f t="shared" si="177"/>
+        <f t="shared" si="174"/>
         <v>9.000000000000008E-2</v>
       </c>
       <c r="AO27" s="9">
-        <f t="shared" si="177"/>
+        <f t="shared" si="174"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AP27" s="9">
-        <f t="shared" si="177"/>
+        <f t="shared" si="174"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AQ27" s="9">
-        <f t="shared" si="177"/>
+        <f t="shared" si="174"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AR27" s="9">
-        <f t="shared" si="177"/>
+        <f t="shared" si="174"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AS27" s="9">
-        <f t="shared" si="175"/>
+        <f t="shared" si="172"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AT27" s="9">
-        <f t="shared" si="175"/>
+        <f t="shared" si="172"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AU27" s="9">
-        <f t="shared" si="175"/>
+        <f t="shared" si="172"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AV27" s="9">
-        <f t="shared" si="175"/>
+        <f t="shared" si="172"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AW27" s="9">
-        <f t="shared" si="175"/>
+        <f t="shared" si="172"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AY27" t="s">
@@ -5642,7 +5633,7 @@
       </c>
       <c r="AZ27" s="5">
         <f>NPV(AZ26,AM18:FJ18)</f>
-        <v>128931.12409030413</v>
+        <v>210409.00277446004</v>
       </c>
     </row>
     <row r="28" spans="2:166" x14ac:dyDescent="0.3">
@@ -5650,183 +5641,183 @@
         <v>30</v>
       </c>
       <c r="D28" s="15">
-        <f t="shared" ref="D28:J28" si="178">D16/D15</f>
+        <f t="shared" ref="D28:J28" si="175">D16/D15</f>
         <v>-2.4005486968449924E-2</v>
       </c>
       <c r="E28" s="9">
+        <f t="shared" si="175"/>
+        <v>-1.4492753623188406E-2</v>
+      </c>
+      <c r="F28" s="9">
+        <f t="shared" si="175"/>
+        <v>-2.5096525096525105E-2</v>
+      </c>
+      <c r="G28" s="15">
+        <f t="shared" si="175"/>
+        <v>-5.019305019305019E-2</v>
+      </c>
+      <c r="H28" s="15">
+        <f t="shared" si="175"/>
+        <v>-8.2191780821917835E-3</v>
+      </c>
+      <c r="I28" s="9">
+        <f t="shared" si="175"/>
+        <v>9.8630772801113938E-3</v>
+      </c>
+      <c r="J28" s="9">
+        <f t="shared" si="175"/>
+        <v>4.8780487804878044E-2</v>
+      </c>
+      <c r="K28" s="9">
+        <f t="shared" ref="K28:N28" si="176">K16/K15</f>
+        <v>-2.574750830564785E-2</v>
+      </c>
+      <c r="L28" s="9">
+        <f t="shared" si="176"/>
+        <v>3.8383838383838409E-2</v>
+      </c>
+      <c r="M28" s="9">
+        <f t="shared" si="176"/>
+        <v>-1.3916500994035789E-2</v>
+      </c>
+      <c r="N28" s="9">
+        <f t="shared" si="176"/>
+        <v>-0.26785714285714274</v>
+      </c>
+      <c r="O28" s="9">
+        <f t="shared" ref="O28:Z28" si="177">O16/O15</f>
+        <v>-2.0120724346076462E-2</v>
+      </c>
+      <c r="P28" s="9">
+        <f t="shared" si="177"/>
+        <v>-1.4705882352941176E-2</v>
+      </c>
+      <c r="Q28" s="9">
+        <f t="shared" si="177"/>
+        <v>-8.9576547231270329E-3</v>
+      </c>
+      <c r="R28" s="9">
+        <f t="shared" si="177"/>
+        <v>0.1160949868073879</v>
+      </c>
+      <c r="S28" s="9">
+        <f t="shared" si="177"/>
+        <v>8.095238095238079E-2</v>
+      </c>
+      <c r="T28" s="9">
+        <f t="shared" si="177"/>
+        <v>7.3089700996677706E-2</v>
+      </c>
+      <c r="U28" s="9">
+        <f t="shared" si="177"/>
+        <v>8.1148564294631645E-2</v>
+      </c>
+      <c r="V28" s="9">
+        <f t="shared" si="177"/>
+        <v>8.7570621468926593E-2</v>
+      </c>
+      <c r="W28" s="9">
+        <f t="shared" si="177"/>
+        <v>4.2457091237579035E-2</v>
+      </c>
+      <c r="X28" s="9">
+        <f t="shared" si="177"/>
+        <v>3.6958066808813091E-2</v>
+      </c>
+      <c r="Y28" s="9">
+        <f t="shared" si="177"/>
+        <v>4.9649904519414395E-2</v>
+      </c>
+      <c r="Z28" s="9">
+        <f t="shared" si="177"/>
+        <v>4.4665012406947882E-2</v>
+      </c>
+      <c r="AA28" s="9">
+        <f t="shared" ref="AA28:AD28" si="178">AA16/AA15</f>
+        <v>2.5078369905956119E-2</v>
+      </c>
+      <c r="AB28" s="9">
         <f t="shared" si="178"/>
-        <v>-1.4492753623188406E-2</v>
-      </c>
-      <c r="F28" s="9">
+        <v>1.08335841107433E-2</v>
+      </c>
+      <c r="AC28" s="9">
         <f t="shared" si="178"/>
-        <v>-2.5096525096525105E-2</v>
-      </c>
-      <c r="G28" s="15">
+        <v>7.9067831876820649E-3</v>
+      </c>
+      <c r="AD28" s="9">
         <f t="shared" si="178"/>
-        <v>-5.019305019305019E-2</v>
-      </c>
-      <c r="H28" s="15">
-        <f t="shared" si="178"/>
-        <v>-8.2191780821917835E-3</v>
-      </c>
-      <c r="I28" s="9">
-        <f t="shared" si="178"/>
-        <v>9.8630772801113938E-3</v>
-      </c>
-      <c r="J28" s="9">
-        <f t="shared" si="178"/>
-        <v>4.8780487804878044E-2</v>
-      </c>
-      <c r="K28" s="9">
-        <f t="shared" ref="K28:N28" si="179">K16/K15</f>
-        <v>-2.574750830564785E-2</v>
-      </c>
-      <c r="L28" s="9">
+        <v>0.04</v>
+      </c>
+      <c r="AF28" s="9">
+        <f t="shared" ref="AF28:AH28" si="179">AF16/AF15</f>
+        <v>-1.5939744263443686E-2</v>
+      </c>
+      <c r="AG28" s="9">
         <f t="shared" si="179"/>
-        <v>3.8383838383838409E-2</v>
-      </c>
-      <c r="M28" s="9">
+        <v>-2.1857923497267766E-2</v>
+      </c>
+      <c r="AH28" s="9">
         <f t="shared" si="179"/>
-        <v>-1.3916500994035789E-2</v>
-      </c>
-      <c r="N28" s="9">
-        <f t="shared" si="179"/>
-        <v>-0.26785714285714274</v>
-      </c>
-      <c r="O28" s="9">
-        <f t="shared" ref="O28:Z28" si="180">O16/O15</f>
-        <v>-2.0120724346076462E-2</v>
-      </c>
-      <c r="P28" s="9">
+        <v>1.0687929425735855E-2</v>
+      </c>
+      <c r="AI28" s="9">
+        <f t="shared" ref="AI28:AR28" si="180">AI16/AI15</f>
+        <v>-6.4542317840470903E-2</v>
+      </c>
+      <c r="AJ28" s="9">
         <f t="shared" si="180"/>
-        <v>-1.4705882352941176E-2</v>
-      </c>
-      <c r="Q28" s="9">
+        <v>-2.7970091387427315E-2</v>
+      </c>
+      <c r="AK28" s="9">
         <f t="shared" si="180"/>
-        <v>-8.9576547231270329E-3</v>
-      </c>
-      <c r="R28" s="9">
+        <v>8.2982308340353805E-2</v>
+      </c>
+      <c r="AL28" s="9">
         <f t="shared" si="180"/>
-        <v>0.1160949868073879</v>
-      </c>
-      <c r="S28" s="9">
+        <v>4.3549376405642999E-2</v>
+      </c>
+      <c r="AM28" s="9">
         <f t="shared" si="180"/>
-        <v>8.095238095238079E-2</v>
-      </c>
-      <c r="T28" s="9">
+        <v>1.9261270232618161E-2</v>
+      </c>
+      <c r="AN28" s="9">
         <f t="shared" si="180"/>
-        <v>7.3089700996677706E-2</v>
-      </c>
-      <c r="U28" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="AO28" s="9">
         <f t="shared" si="180"/>
-        <v>8.1148564294631645E-2</v>
-      </c>
-      <c r="V28" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="AP28" s="9">
         <f t="shared" si="180"/>
-        <v>8.7570621468926593E-2</v>
-      </c>
-      <c r="W28" s="9">
+        <v>9.9999999999999992E-2</v>
+      </c>
+      <c r="AQ28" s="9">
         <f t="shared" si="180"/>
-        <v>4.2457091237579035E-2</v>
-      </c>
-      <c r="X28" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="AR28" s="9">
         <f t="shared" si="180"/>
-        <v>3.6958066808813091E-2</v>
-      </c>
-      <c r="Y28" s="9">
-        <f t="shared" si="180"/>
-        <v>4.9649904519414395E-2</v>
-      </c>
-      <c r="Z28" s="9">
-        <f t="shared" si="180"/>
-        <v>4.4665012406947882E-2</v>
-      </c>
-      <c r="AA28" s="9">
-        <f t="shared" ref="AA28:AD28" si="181">AA16/AA15</f>
-        <v>2.5078369905956119E-2</v>
-      </c>
-      <c r="AB28" s="9">
+        <v>0.15</v>
+      </c>
+      <c r="AS28" s="9">
+        <f t="shared" ref="AS28:AW28" si="181">AS16/AS15</f>
+        <v>0.15</v>
+      </c>
+      <c r="AT28" s="9">
         <f t="shared" si="181"/>
-        <v>1.08335841107433E-2</v>
-      </c>
-      <c r="AC28" s="9">
+        <v>0.15</v>
+      </c>
+      <c r="AU28" s="9">
         <f t="shared" si="181"/>
-        <v>0.04</v>
-      </c>
-      <c r="AD28" s="9">
+        <v>0.15</v>
+      </c>
+      <c r="AV28" s="9">
         <f t="shared" si="181"/>
-        <v>0.04</v>
-      </c>
-      <c r="AF28" s="9">
-        <f t="shared" ref="AF28:AH28" si="182">AF16/AF15</f>
-        <v>-1.5939744263443686E-2</v>
-      </c>
-      <c r="AG28" s="9">
-        <f t="shared" si="182"/>
-        <v>-2.1857923497267766E-2</v>
-      </c>
-      <c r="AH28" s="9">
-        <f t="shared" si="182"/>
-        <v>1.0687929425735855E-2</v>
-      </c>
-      <c r="AI28" s="9">
-        <f t="shared" ref="AI28:AR28" si="183">AI16/AI15</f>
-        <v>-6.4542317840470903E-2</v>
-      </c>
-      <c r="AJ28" s="9">
-        <f t="shared" si="183"/>
-        <v>-2.7970091387427315E-2</v>
-      </c>
-      <c r="AK28" s="9">
-        <f t="shared" si="183"/>
-        <v>8.2982308340353805E-2</v>
-      </c>
-      <c r="AL28" s="9">
-        <f t="shared" si="183"/>
-        <v>4.3549376405642999E-2</v>
-      </c>
-      <c r="AM28" s="9">
-        <f t="shared" si="183"/>
-        <v>2.8763641684404671E-2</v>
-      </c>
-      <c r="AN28" s="9">
-        <f t="shared" si="183"/>
-        <v>0.1</v>
-      </c>
-      <c r="AO28" s="9">
-        <f t="shared" si="183"/>
-        <v>0.1</v>
-      </c>
-      <c r="AP28" s="9">
-        <f t="shared" si="183"/>
-        <v>0.1</v>
-      </c>
-      <c r="AQ28" s="9">
-        <f t="shared" si="183"/>
-        <v>0.10000000000000002</v>
-      </c>
-      <c r="AR28" s="9">
-        <f t="shared" si="183"/>
         <v>0.15</v>
       </c>
-      <c r="AS28" s="9">
-        <f t="shared" ref="AS28:AW28" si="184">AS16/AS15</f>
-        <v>0.15</v>
-      </c>
-      <c r="AT28" s="9">
-        <f t="shared" si="184"/>
-        <v>0.15</v>
-      </c>
-      <c r="AU28" s="9">
-        <f t="shared" si="184"/>
-        <v>0.15</v>
-      </c>
-      <c r="AV28" s="9">
-        <f t="shared" si="184"/>
-        <v>0.15</v>
-      </c>
       <c r="AW28" s="9">
-        <f t="shared" si="184"/>
+        <f t="shared" si="181"/>
         <v>0.15</v>
       </c>
       <c r="AY28" t="s">
@@ -5834,7 +5825,7 @@
       </c>
       <c r="AZ28" s="5">
         <f>Main!D8</f>
-        <v>5230</v>
+        <v>6437.9</v>
       </c>
     </row>
     <row r="29" spans="2:166" x14ac:dyDescent="0.3">
@@ -5871,19 +5862,19 @@
         <v>-2.6054590570719596E-2</v>
       </c>
       <c r="AA29" s="9">
-        <f t="shared" ref="AA29:AD29" si="185">AA17/AA15</f>
+        <f t="shared" ref="AA29:AD29" si="182">AA17/AA15</f>
         <v>1.6569637259292436E-2</v>
       </c>
       <c r="AB29" s="9">
-        <f t="shared" si="185"/>
+        <f t="shared" si="182"/>
         <v>5.4167920553716501E-3</v>
       </c>
       <c r="AC29" s="9">
-        <f t="shared" si="185"/>
-        <v>0.01</v>
+        <f t="shared" si="182"/>
+        <v>2.288805659592177E-3</v>
       </c>
       <c r="AD29" s="9">
-        <f t="shared" si="185"/>
+        <f t="shared" si="182"/>
         <v>0.01</v>
       </c>
       <c r="AF29" s="9"/>
@@ -5893,51 +5884,51 @@
       <c r="AJ29" s="9"/>
       <c r="AK29" s="9"/>
       <c r="AL29" s="9">
-        <f t="shared" ref="AL29:AW29" si="186">AL17/AL15</f>
+        <f t="shared" ref="AL29:AW29" si="183">AL17/AL15</f>
         <v>7.564915150276014E-3</v>
       </c>
       <c r="AM29" s="9">
-        <f t="shared" si="186"/>
-        <v>9.9516864200189445E-3</v>
+        <f t="shared" si="183"/>
+        <v>7.2574837814647622E-3</v>
       </c>
       <c r="AN29" s="9">
-        <f t="shared" si="186"/>
+        <f t="shared" si="183"/>
         <v>0.02</v>
       </c>
       <c r="AO29" s="9">
-        <f t="shared" si="186"/>
+        <f t="shared" si="183"/>
         <v>0.02</v>
       </c>
       <c r="AP29" s="9">
-        <f t="shared" si="186"/>
+        <f t="shared" si="183"/>
         <v>0.02</v>
       </c>
       <c r="AQ29" s="9">
-        <f t="shared" si="186"/>
+        <f t="shared" si="183"/>
         <v>0.02</v>
       </c>
       <c r="AR29" s="9">
-        <f t="shared" si="186"/>
+        <f t="shared" si="183"/>
         <v>0.02</v>
       </c>
       <c r="AS29" s="9">
-        <f t="shared" si="186"/>
+        <f t="shared" si="183"/>
         <v>0.02</v>
       </c>
       <c r="AT29" s="9">
-        <f t="shared" si="186"/>
+        <f t="shared" si="183"/>
         <v>0.02</v>
       </c>
       <c r="AU29" s="9">
-        <f t="shared" si="186"/>
+        <f t="shared" si="183"/>
         <v>0.02</v>
       </c>
       <c r="AV29" s="9">
-        <f t="shared" si="186"/>
+        <f t="shared" si="183"/>
         <v>0.02</v>
       </c>
       <c r="AW29" s="9">
-        <f t="shared" si="186"/>
+        <f t="shared" si="183"/>
         <v>0.02</v>
       </c>
       <c r="AY29" t="s">
@@ -5945,7 +5936,7 @@
       </c>
       <c r="AZ29" s="5">
         <f>AZ27+AZ28</f>
-        <v>134161.12409030413</v>
+        <v>216846.90277446003</v>
       </c>
     </row>
     <row r="30" spans="2:166" x14ac:dyDescent="0.3">
@@ -5954,191 +5945,191 @@
       </c>
       <c r="C30" s="9"/>
       <c r="D30" s="9">
-        <f t="shared" ref="D30:N30" si="187">D18/D3</f>
+        <f t="shared" ref="D30:N30" si="184">D18/D3</f>
         <v>-0.86450492182976291</v>
       </c>
       <c r="E30" s="9">
+        <f t="shared" si="184"/>
+        <v>-0.73490813648293962</v>
+      </c>
+      <c r="F30" s="9">
+        <f t="shared" si="184"/>
+        <v>-0.69442022667829095</v>
+      </c>
+      <c r="G30" s="9">
+        <f t="shared" ref="G30" si="185">G18/G3</f>
+        <v>-0.23724378543392935</v>
+      </c>
+      <c r="H30" s="9">
+        <f t="shared" si="184"/>
+        <v>-0.43826915442635955</v>
+      </c>
+      <c r="I30" s="9">
+        <f t="shared" si="184"/>
+        <v>-2.9485141672425712</v>
+      </c>
+      <c r="J30" s="9">
+        <f t="shared" si="184"/>
+        <v>-0.46010555728034774</v>
+      </c>
+      <c r="K30" s="9">
+        <f t="shared" si="184"/>
+        <v>-0.36195779601406786</v>
+      </c>
+      <c r="L30" s="9">
+        <f t="shared" si="184"/>
+        <v>-0.3801916932907346</v>
+      </c>
+      <c r="M30" s="9">
+        <f t="shared" si="184"/>
+        <v>-0.2601377199693955</v>
+      </c>
+      <c r="N30" s="9">
+        <f t="shared" si="184"/>
+        <v>-0.36082236082236097</v>
+      </c>
+      <c r="O30" s="9">
+        <f t="shared" ref="O30:Z30" si="186">O18/O3</f>
+        <v>-0.22715053763440857</v>
+      </c>
+      <c r="P30" s="9">
+        <f t="shared" si="186"/>
+        <v>-0.37928118393234672</v>
+      </c>
+      <c r="Q30" s="9">
+        <f t="shared" si="186"/>
+        <v>-0.25925925925925936</v>
+      </c>
+      <c r="R30" s="9">
+        <f t="shared" si="186"/>
+        <v>6.5867086118757356E-2</v>
+      </c>
+      <c r="S30" s="9">
+        <f t="shared" si="186"/>
+        <v>3.6747905559786825E-2</v>
+      </c>
+      <c r="T30" s="9">
+        <f t="shared" si="186"/>
+        <v>5.2315769735608517E-2</v>
+      </c>
+      <c r="U30" s="9">
+        <f t="shared" si="186"/>
+        <v>0.13185238265854543</v>
+      </c>
+      <c r="V30" s="9">
+        <f t="shared" si="186"/>
+        <v>0.15927021696252461</v>
+      </c>
+      <c r="W30" s="9">
+        <f t="shared" si="186"/>
+        <v>0.16711335330285357</v>
+      </c>
+      <c r="X30" s="9">
+        <f t="shared" si="186"/>
+        <v>0.19982303495059719</v>
+      </c>
+      <c r="Y30" s="9">
+        <f t="shared" si="186"/>
+        <v>0.19779462439696752</v>
+      </c>
+      <c r="Z30" s="9">
+        <f t="shared" si="186"/>
+        <v>9.5589123867069511E-2</v>
+      </c>
+      <c r="AA30" s="9">
+        <f t="shared" ref="AA30:AD30" si="187">AA18/AA3</f>
+        <v>0.24210883584115844</v>
+      </c>
+      <c r="AB30" s="9">
         <f t="shared" si="187"/>
-        <v>-0.73490813648293962</v>
-      </c>
-      <c r="F30" s="9">
+        <v>0.32569492876357486</v>
+      </c>
+      <c r="AC30" s="9">
         <f t="shared" si="187"/>
-        <v>-0.69442022667829095</v>
-      </c>
-      <c r="G30" s="9">
-        <f t="shared" ref="G30" si="188">G18/G3</f>
-        <v>-0.23724378543392935</v>
-      </c>
-      <c r="H30" s="9">
+        <v>0.402760138853611</v>
+      </c>
+      <c r="AD30" s="9">
         <f t="shared" si="187"/>
-        <v>-0.43826915442635955</v>
-      </c>
-      <c r="I30" s="9">
-        <f t="shared" si="187"/>
-        <v>-2.9485141672425712</v>
-      </c>
-      <c r="J30" s="9">
-        <f t="shared" si="187"/>
-        <v>-0.46010555728034774</v>
-      </c>
-      <c r="K30" s="9">
-        <f t="shared" si="187"/>
-        <v>-0.36195779601406786</v>
-      </c>
-      <c r="L30" s="9">
-        <f t="shared" si="187"/>
-        <v>-0.3801916932907346</v>
-      </c>
-      <c r="M30" s="9">
-        <f t="shared" si="187"/>
-        <v>-0.2601377199693955</v>
-      </c>
-      <c r="N30" s="9">
-        <f t="shared" si="187"/>
-        <v>-0.36082236082236097</v>
-      </c>
-      <c r="O30" s="9">
-        <f t="shared" ref="O30:Z30" si="189">O18/O3</f>
-        <v>-0.22715053763440857</v>
-      </c>
-      <c r="P30" s="9">
+        <v>0.23984676448457498</v>
+      </c>
+      <c r="AF30" s="9">
+        <f t="shared" ref="AF30:AS30" si="188">AF18/AF3</f>
+        <v>-0.97413503527040646</v>
+      </c>
+      <c r="AG30" s="9">
+        <f t="shared" si="188"/>
+        <v>-0.78063560463237247</v>
+      </c>
+      <c r="AH30" s="9">
+        <f t="shared" si="188"/>
+        <v>-1.0673560904182304</v>
+      </c>
+      <c r="AI30" s="9">
+        <f t="shared" si="188"/>
+        <v>-0.34018679465559715</v>
+      </c>
+      <c r="AJ30" s="9">
+        <f t="shared" si="188"/>
+        <v>-0.19476362873183264</v>
+      </c>
+      <c r="AK30" s="9">
+        <f t="shared" si="188"/>
+        <v>9.7838299402274106E-2</v>
+      </c>
+      <c r="AL30" s="9">
+        <f t="shared" si="188"/>
+        <v>0.16196691561387597</v>
+      </c>
+      <c r="AM30" s="9">
+        <f t="shared" si="188"/>
+        <v>0.30364880505718894</v>
+      </c>
+      <c r="AN30" s="9">
+        <f t="shared" si="188"/>
+        <v>0.34645521469294682</v>
+      </c>
+      <c r="AO30" s="9">
+        <f t="shared" si="188"/>
+        <v>0.40178356468293208</v>
+      </c>
+      <c r="AP30" s="9">
+        <f t="shared" si="188"/>
+        <v>0.4560823761419483</v>
+      </c>
+      <c r="AQ30" s="9">
+        <f t="shared" si="188"/>
+        <v>0.49365145878891564</v>
+      </c>
+      <c r="AR30" s="9">
+        <f t="shared" si="188"/>
+        <v>0.49550020893203511</v>
+      </c>
+      <c r="AS30" s="9">
+        <f t="shared" si="188"/>
+        <v>0.51290465456239354</v>
+      </c>
+      <c r="AT30" s="9">
+        <f t="shared" ref="AT30:AW30" si="189">AT18/AT3</f>
+        <v>0.52734506774785583</v>
+      </c>
+      <c r="AU30" s="9">
         <f t="shared" si="189"/>
-        <v>-0.37928118393234672</v>
-      </c>
-      <c r="Q30" s="9">
+        <v>0.53318411963831003</v>
+      </c>
+      <c r="AV30" s="9">
         <f t="shared" si="189"/>
-        <v>-0.25925925925925936</v>
-      </c>
-      <c r="R30" s="9">
+        <v>0.53874801570598085</v>
+      </c>
+      <c r="AW30" s="9">
         <f t="shared" si="189"/>
-        <v>6.5867086118757356E-2</v>
-      </c>
-      <c r="S30" s="9">
-        <f t="shared" si="189"/>
-        <v>3.6747905559786825E-2</v>
-      </c>
-      <c r="T30" s="9">
-        <f t="shared" si="189"/>
-        <v>5.2315769735608517E-2</v>
-      </c>
-      <c r="U30" s="9">
-        <f t="shared" si="189"/>
-        <v>0.13185238265854543</v>
-      </c>
-      <c r="V30" s="9">
-        <f t="shared" si="189"/>
-        <v>0.15927021696252461</v>
-      </c>
-      <c r="W30" s="9">
-        <f t="shared" si="189"/>
-        <v>0.16711335330285357</v>
-      </c>
-      <c r="X30" s="9">
-        <f t="shared" si="189"/>
-        <v>0.19982303495059719</v>
-      </c>
-      <c r="Y30" s="9">
-        <f t="shared" si="189"/>
-        <v>0.19779462439696752</v>
-      </c>
-      <c r="Z30" s="9">
-        <f t="shared" si="189"/>
-        <v>9.5589123867069511E-2</v>
-      </c>
-      <c r="AA30" s="9">
-        <f t="shared" ref="AA30:AD30" si="190">AA18/AA3</f>
-        <v>0.24210883584115844</v>
-      </c>
-      <c r="AB30" s="9">
-        <f t="shared" si="190"/>
-        <v>0.32569492876357486</v>
-      </c>
-      <c r="AC30" s="9">
-        <f t="shared" si="190"/>
-        <v>0.30281305995864927</v>
-      </c>
-      <c r="AD30" s="9">
-        <f t="shared" si="190"/>
-        <v>0.19679762418562602</v>
-      </c>
-      <c r="AF30" s="9">
-        <f t="shared" ref="AF30:AS30" si="191">AF18/AF3</f>
-        <v>-0.97413503527040646</v>
-      </c>
-      <c r="AG30" s="9">
-        <f t="shared" si="191"/>
-        <v>-0.78063560463237247</v>
-      </c>
-      <c r="AH30" s="9">
-        <f t="shared" si="191"/>
-        <v>-1.0673560904182304</v>
-      </c>
-      <c r="AI30" s="9">
-        <f t="shared" si="191"/>
-        <v>-0.34018679465559715</v>
-      </c>
-      <c r="AJ30" s="9">
-        <f t="shared" si="191"/>
-        <v>-0.19476362873183264</v>
-      </c>
-      <c r="AK30" s="9">
-        <f t="shared" si="191"/>
-        <v>9.7838299402274106E-2</v>
-      </c>
-      <c r="AL30" s="9">
-        <f t="shared" si="191"/>
-        <v>0.16196691561387597</v>
-      </c>
-      <c r="AM30" s="9">
-        <f t="shared" si="191"/>
-        <v>0.26486252090373047</v>
-      </c>
-      <c r="AN30" s="9">
-        <f t="shared" si="191"/>
-        <v>0.2954706511212063</v>
-      </c>
-      <c r="AO30" s="9">
-        <f t="shared" si="191"/>
-        <v>0.35619284150827429</v>
-      </c>
-      <c r="AP30" s="9">
-        <f t="shared" si="191"/>
-        <v>0.41095605363989046</v>
-      </c>
-      <c r="AQ30" s="9">
-        <f t="shared" si="191"/>
-        <v>0.44826480176429023</v>
-      </c>
-      <c r="AR30" s="9">
-        <f t="shared" si="191"/>
-        <v>0.44545830119446517</v>
-      </c>
-      <c r="AS30" s="9">
-        <f t="shared" si="191"/>
-        <v>0.46399370277456525</v>
-      </c>
-      <c r="AT30" s="9">
-        <f t="shared" ref="AT30:AW30" si="192">AT18/AT3</f>
-        <v>0.47366651340642957</v>
-      </c>
-      <c r="AU30" s="9">
-        <f t="shared" si="192"/>
-        <v>0.48282591251783663</v>
-      </c>
-      <c r="AV30" s="9">
-        <f t="shared" si="192"/>
-        <v>0.49151787847465622</v>
-      </c>
-      <c r="AW30" s="9">
-        <f t="shared" si="192"/>
-        <v>0.49978543845915879</v>
+        <v>0.54406139764281203</v>
       </c>
       <c r="AY30" t="s">
         <v>42</v>
       </c>
       <c r="AZ30" s="4">
         <f>AZ29/AR19</f>
-        <v>56.722951162820962</v>
+        <v>91.219461035865748</v>
       </c>
     </row>
     <row r="31" spans="2:166" x14ac:dyDescent="0.3">
@@ -6147,7 +6138,7 @@
       </c>
       <c r="AZ31" s="4">
         <f>Main!D3</f>
-        <v>182.39</v>
+        <v>192.48</v>
       </c>
     </row>
     <row r="32" spans="2:166" x14ac:dyDescent="0.3">
@@ -6156,7 +6147,7 @@
       </c>
       <c r="AZ32" s="10">
         <f>AZ30/AZ31-1</f>
-        <v>-0.68900185776182377</v>
+        <v>-0.52608343185855277</v>
       </c>
     </row>
     <row r="33" spans="2:52" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -6164,35 +6155,35 @@
         <v>73</v>
       </c>
       <c r="W33" s="8">
-        <f t="shared" ref="W33:X33" si="193">W18</f>
+        <f t="shared" ref="W33:X33" si="190">W18</f>
         <v>106.00000000000001</v>
       </c>
       <c r="X33" s="8">
-        <f t="shared" si="193"/>
+        <f t="shared" si="190"/>
         <v>135.49999999999997</v>
       </c>
       <c r="AA33" s="8">
-        <f t="shared" ref="AA33:AD33" si="194">AA18</f>
+        <f t="shared" ref="AA33:AD33" si="191">AA18</f>
         <v>213.99999999999994</v>
       </c>
       <c r="AB33" s="8">
-        <f t="shared" si="194"/>
+        <f t="shared" si="191"/>
         <v>326.90000000000009</v>
       </c>
       <c r="AC33" s="8">
-        <f t="shared" si="194"/>
-        <v>333.93013000000008</v>
+        <f t="shared" si="191"/>
+        <v>475.69999999999993</v>
       </c>
       <c r="AD33" s="8">
-        <f t="shared" si="194"/>
-        <v>239.38955000000013</v>
+        <f t="shared" si="191"/>
+        <v>318.75635000000017</v>
       </c>
       <c r="AJ33" s="8">
-        <f t="shared" ref="AJ33:AK33" si="195">AJ18</f>
+        <f t="shared" ref="AJ33:AK33" si="192">AJ18</f>
         <v>-371.19999999999987</v>
       </c>
       <c r="AK33" s="8">
-        <f t="shared" si="195"/>
+        <f t="shared" si="192"/>
         <v>217.7000000000001</v>
       </c>
       <c r="AL33" s="8">
@@ -6200,48 +6191,48 @@
         <v>464.10000000000019</v>
       </c>
       <c r="AM33" s="8">
-        <f t="shared" ref="AM33:AW33" si="196">AM18</f>
-        <v>1114.2196799999997</v>
+        <f t="shared" ref="AM33:AW33" si="193">AM18</f>
+        <v>1335.3563499999998</v>
       </c>
       <c r="AN33" s="8">
-        <f t="shared" si="196"/>
-        <v>1615.8759540000008</v>
+        <f t="shared" si="193"/>
+        <v>2209.2288415999997</v>
       </c>
       <c r="AO33" s="8">
-        <f t="shared" si="196"/>
-        <v>2473.9024862640008</v>
+        <f t="shared" si="193"/>
+        <v>3458.7529125600004</v>
       </c>
       <c r="AP33" s="8">
-        <f t="shared" si="196"/>
-        <v>3539.2762139451202</v>
+        <f t="shared" si="193"/>
+        <v>5104.0393414824002</v>
       </c>
       <c r="AQ33" s="8">
-        <f t="shared" si="196"/>
-        <v>4555.4965425856135</v>
+        <f t="shared" si="193"/>
+        <v>6905.5958924364722</v>
       </c>
       <c r="AR33" s="8">
-        <f t="shared" si="196"/>
-        <v>5160.7520086038985</v>
+        <f t="shared" si="193"/>
+        <v>8317.7492457461103</v>
       </c>
       <c r="AS33" s="8">
-        <f t="shared" si="196"/>
-        <v>5913.0384816442283</v>
+        <f t="shared" si="193"/>
+        <v>9901.3967314852707</v>
       </c>
       <c r="AT33" s="8">
-        <f t="shared" si="196"/>
-        <v>6639.9374278990799</v>
+        <f t="shared" si="193"/>
+        <v>11198.178749382267</v>
       </c>
       <c r="AU33" s="8">
-        <f t="shared" si="196"/>
-        <v>7445.1689799516071</v>
+        <f t="shared" si="193"/>
+        <v>12454.388193853934</v>
       </c>
       <c r="AV33" s="8">
-        <f t="shared" si="196"/>
-        <v>8337.1188739865775</v>
+        <f t="shared" si="193"/>
+        <v>13842.787785774039</v>
       </c>
       <c r="AW33" s="8">
-        <f t="shared" si="196"/>
-        <v>9325.0884125265729</v>
+        <f t="shared" si="193"/>
+        <v>15377.242932663316</v>
       </c>
       <c r="AY33" t="s">
         <v>45</v>
@@ -6258,22 +6249,22 @@
         <v>8.4</v>
       </c>
       <c r="X34" s="5">
-        <f t="shared" ref="X34:X48" si="197">X56-W34</f>
+        <f t="shared" ref="X34:X48" si="194">X56-W34</f>
         <v>8.1</v>
       </c>
       <c r="AA34" s="5">
         <v>6.6</v>
       </c>
       <c r="AB34" s="5">
-        <f t="shared" ref="AB34:AB48" si="198">AB56-AA34</f>
+        <f t="shared" ref="AB34:AB48" si="195">AB56-AA34</f>
         <v>6.6</v>
       </c>
       <c r="AC34" s="5">
-        <f t="shared" ref="AC34:AD34" si="199">AB34*1.05</f>
+        <f t="shared" ref="AC34:AD34" si="196">AB34*1.05</f>
         <v>6.93</v>
       </c>
       <c r="AD34" s="5">
-        <f t="shared" si="199"/>
+        <f t="shared" si="196"/>
         <v>7.2765000000000004</v>
       </c>
       <c r="AJ34" s="5">
@@ -6290,43 +6281,43 @@
         <v>27.406500000000001</v>
       </c>
       <c r="AN34" s="5">
-        <f t="shared" ref="AN34:AW34" si="200">AM34*1.05</f>
+        <f t="shared" ref="AN34:AW34" si="197">AM34*1.05</f>
         <v>28.776825000000002</v>
       </c>
       <c r="AO34" s="5">
-        <f t="shared" si="200"/>
+        <f t="shared" si="197"/>
         <v>30.215666250000005</v>
       </c>
       <c r="AP34" s="5">
-        <f t="shared" si="200"/>
+        <f t="shared" si="197"/>
         <v>31.726449562500008</v>
       </c>
       <c r="AQ34" s="5">
-        <f t="shared" si="200"/>
+        <f t="shared" si="197"/>
         <v>33.312772040625006</v>
       </c>
       <c r="AR34" s="5">
-        <f t="shared" si="200"/>
+        <f t="shared" si="197"/>
         <v>34.978410642656257</v>
       </c>
       <c r="AS34" s="5">
-        <f t="shared" si="200"/>
+        <f t="shared" si="197"/>
         <v>36.727331174789072</v>
       </c>
       <c r="AT34" s="5">
-        <f t="shared" si="200"/>
+        <f t="shared" si="197"/>
         <v>38.563697733528528</v>
       </c>
       <c r="AU34" s="5">
-        <f t="shared" si="200"/>
+        <f t="shared" si="197"/>
         <v>40.491882620204954</v>
       </c>
       <c r="AV34" s="5">
-        <f t="shared" si="200"/>
+        <f t="shared" si="197"/>
         <v>42.516476751215201</v>
       </c>
       <c r="AW34" s="5">
-        <f t="shared" si="200"/>
+        <f t="shared" si="197"/>
         <v>44.64230058877596</v>
       </c>
     </row>
@@ -6338,22 +6329,22 @@
         <v>125.7</v>
       </c>
       <c r="X35" s="5">
-        <f t="shared" si="197"/>
+        <f t="shared" si="194"/>
         <v>141.69999999999999</v>
       </c>
       <c r="AA35" s="5">
         <v>155.30000000000001</v>
       </c>
       <c r="AB35" s="5">
+        <f t="shared" si="195"/>
+        <v>160</v>
+      </c>
+      <c r="AC35" s="5">
+        <f t="shared" ref="AC35:AD35" si="198">AB35*1.1</f>
+        <v>176</v>
+      </c>
+      <c r="AD35" s="5">
         <f t="shared" si="198"/>
-        <v>160</v>
-      </c>
-      <c r="AC35" s="5">
-        <f t="shared" ref="AC35:AD35" si="201">AB35*1.1</f>
-        <v>176</v>
-      </c>
-      <c r="AD35" s="5">
-        <f t="shared" si="201"/>
         <v>193.60000000000002</v>
       </c>
       <c r="AJ35" s="5">
@@ -6366,7 +6357,7 @@
         <v>691.6</v>
       </c>
       <c r="AM35" s="5">
-        <f t="shared" ref="AM35:AM50" si="202">SUM(AA35:AD35)</f>
+        <f t="shared" ref="AM35:AM50" si="199">SUM(AA35:AD35)</f>
         <v>684.90000000000009</v>
       </c>
       <c r="AN35" s="5">
@@ -6386,27 +6377,27 @@
         <v>808.42109859000027</v>
       </c>
       <c r="AR35" s="5">
-        <f t="shared" ref="AR35:AW35" si="203">AQ35*1.02</f>
+        <f t="shared" ref="AR35:AW35" si="200">AQ35*1.02</f>
         <v>824.58952056180033</v>
       </c>
       <c r="AS35" s="5">
-        <f t="shared" si="203"/>
+        <f t="shared" si="200"/>
         <v>841.08131097303635</v>
       </c>
       <c r="AT35" s="5">
-        <f t="shared" si="203"/>
+        <f t="shared" si="200"/>
         <v>857.90293719249712</v>
       </c>
       <c r="AU35" s="5">
-        <f t="shared" si="203"/>
+        <f t="shared" si="200"/>
         <v>875.06099593634713</v>
       </c>
       <c r="AV35" s="5">
-        <f t="shared" si="203"/>
+        <f t="shared" si="200"/>
         <v>892.5622158550741</v>
       </c>
       <c r="AW35" s="5">
-        <f t="shared" si="203"/>
+        <f t="shared" si="200"/>
         <v>910.41346017217563</v>
       </c>
     </row>
@@ -6418,14 +6409,14 @@
         <v>0</v>
       </c>
       <c r="X36" s="5">
-        <f t="shared" si="197"/>
+        <f t="shared" si="194"/>
         <v>0</v>
       </c>
       <c r="AA36" s="5">
         <v>0</v>
       </c>
       <c r="AB36" s="5">
-        <f t="shared" si="198"/>
+        <f t="shared" si="195"/>
         <v>0</v>
       </c>
       <c r="AC36" s="5">
@@ -6444,47 +6435,47 @@
         <v>41.2</v>
       </c>
       <c r="AM36" s="5">
-        <f t="shared" si="202"/>
+        <f t="shared" si="199"/>
         <v>0</v>
       </c>
       <c r="AN36" s="5">
-        <f t="shared" ref="AN36:AW36" si="204">AM36*1.05</f>
+        <f t="shared" ref="AN36:AW36" si="201">AM36*1.05</f>
         <v>0</v>
       </c>
       <c r="AO36" s="5">
-        <f t="shared" si="204"/>
+        <f t="shared" si="201"/>
         <v>0</v>
       </c>
       <c r="AP36" s="5">
-        <f t="shared" si="204"/>
+        <f t="shared" si="201"/>
         <v>0</v>
       </c>
       <c r="AQ36" s="5">
-        <f t="shared" si="204"/>
+        <f t="shared" si="201"/>
         <v>0</v>
       </c>
       <c r="AR36" s="5">
-        <f t="shared" si="204"/>
+        <f t="shared" si="201"/>
         <v>0</v>
       </c>
       <c r="AS36" s="5">
-        <f t="shared" si="204"/>
+        <f t="shared" si="201"/>
         <v>0</v>
       </c>
       <c r="AT36" s="5">
-        <f t="shared" si="204"/>
+        <f t="shared" si="201"/>
         <v>0</v>
       </c>
       <c r="AU36" s="5">
-        <f t="shared" si="204"/>
+        <f t="shared" si="201"/>
         <v>0</v>
       </c>
       <c r="AV36" s="5">
-        <f t="shared" si="204"/>
+        <f t="shared" si="201"/>
         <v>0</v>
       </c>
       <c r="AW36" s="5">
-        <f t="shared" si="204"/>
+        <f t="shared" si="201"/>
         <v>0</v>
       </c>
     </row>
@@ -6496,14 +6487,14 @@
         <v>12.4</v>
       </c>
       <c r="X37" s="5">
-        <f t="shared" si="197"/>
+        <f t="shared" si="194"/>
         <v>7.6</v>
       </c>
       <c r="AA37" s="5">
         <v>10.7</v>
       </c>
       <c r="AB37" s="5">
-        <f t="shared" si="198"/>
+        <f t="shared" si="195"/>
         <v>-11.2</v>
       </c>
       <c r="AC37" s="5">
@@ -6522,7 +6513,7 @@
         <v>19.3</v>
       </c>
       <c r="AM37" s="5">
-        <f t="shared" si="202"/>
+        <f t="shared" si="199"/>
         <v>21.5</v>
       </c>
       <c r="AN37" s="5">
@@ -6564,22 +6555,22 @@
         <v>-11.9</v>
       </c>
       <c r="X38" s="5">
-        <f t="shared" si="197"/>
+        <f t="shared" si="194"/>
         <v>-14.6</v>
       </c>
       <c r="AA38" s="5">
         <v>-15.5</v>
       </c>
       <c r="AB38" s="5">
-        <f t="shared" si="198"/>
+        <f t="shared" si="195"/>
         <v>-8.8999999999999986</v>
       </c>
       <c r="AC38" s="5">
-        <f t="shared" ref="AC38:AD38" si="205">AB38*1.03</f>
+        <f t="shared" ref="AC38:AD38" si="202">AB38*1.03</f>
         <v>-9.166999999999998</v>
       </c>
       <c r="AD38" s="5">
-        <f t="shared" si="205"/>
+        <f t="shared" si="202"/>
         <v>-9.442009999999998</v>
       </c>
       <c r="AJ38" s="5">
@@ -6592,47 +6583,47 @@
         <v>-52.5</v>
       </c>
       <c r="AM38" s="5">
-        <f t="shared" si="202"/>
+        <f t="shared" si="199"/>
         <v>-43.009009999999989</v>
       </c>
       <c r="AN38" s="5">
-        <f t="shared" ref="AN38:AW38" si="206">AM38*1.05</f>
+        <f t="shared" ref="AN38:AW38" si="203">AM38*1.05</f>
         <v>-45.159460499999987</v>
       </c>
       <c r="AO38" s="5">
-        <f t="shared" si="206"/>
+        <f t="shared" si="203"/>
         <v>-47.417433524999986</v>
       </c>
       <c r="AP38" s="5">
-        <f t="shared" si="206"/>
+        <f t="shared" si="203"/>
         <v>-49.78830520124999</v>
       </c>
       <c r="AQ38" s="5">
-        <f t="shared" si="206"/>
+        <f t="shared" si="203"/>
         <v>-52.277720461312491</v>
       </c>
       <c r="AR38" s="5">
-        <f t="shared" si="206"/>
+        <f t="shared" si="203"/>
         <v>-54.891606484378116</v>
       </c>
       <c r="AS38" s="5">
-        <f t="shared" si="206"/>
+        <f t="shared" si="203"/>
         <v>-57.636186808597024</v>
       </c>
       <c r="AT38" s="5">
-        <f t="shared" si="206"/>
+        <f t="shared" si="203"/>
         <v>-60.517996149026878</v>
       </c>
       <c r="AU38" s="5">
-        <f t="shared" si="206"/>
+        <f t="shared" si="203"/>
         <v>-63.543895956478224</v>
       </c>
       <c r="AV38" s="5">
-        <f t="shared" si="206"/>
+        <f t="shared" si="203"/>
         <v>-66.721090754302139</v>
       </c>
       <c r="AW38" s="5">
-        <f t="shared" si="206"/>
+        <f t="shared" si="203"/>
         <v>-70.057145292017253</v>
       </c>
     </row>
@@ -6644,14 +6635,14 @@
         <v>5.6</v>
       </c>
       <c r="X39" s="5">
-        <f t="shared" si="197"/>
+        <f t="shared" si="194"/>
         <v>5.8000000000000007</v>
       </c>
       <c r="AA39" s="5">
         <v>3.5</v>
       </c>
       <c r="AB39" s="5">
-        <f t="shared" si="198"/>
+        <f t="shared" si="195"/>
         <v>23</v>
       </c>
       <c r="AC39" s="5">
@@ -6670,7 +6661,7 @@
         <v>24.8</v>
       </c>
       <c r="AM39" s="5">
-        <f t="shared" si="202"/>
+        <f t="shared" si="199"/>
         <v>26.5</v>
       </c>
       <c r="AN39" s="5">
@@ -6712,14 +6703,14 @@
         <v>-121.9</v>
       </c>
       <c r="X40" s="5">
-        <f t="shared" si="197"/>
+        <f t="shared" si="194"/>
         <v>-176.4</v>
       </c>
       <c r="AA40" s="5">
         <v>-135</v>
       </c>
       <c r="AB40" s="5">
-        <f t="shared" si="198"/>
+        <f t="shared" si="195"/>
         <v>-28.5</v>
       </c>
       <c r="AC40" s="5">
@@ -6738,7 +6729,7 @@
         <v>-211.2</v>
       </c>
       <c r="AM40" s="5">
-        <f t="shared" si="202"/>
+        <f t="shared" si="199"/>
         <v>-163.5</v>
       </c>
       <c r="AN40" s="5">
@@ -6778,12 +6769,12 @@
       </c>
       <c r="W41" s="5"/>
       <c r="X41" s="5">
-        <f t="shared" si="197"/>
+        <f t="shared" si="194"/>
         <v>0</v>
       </c>
       <c r="AA41" s="5"/>
       <c r="AB41" s="5">
-        <f t="shared" si="198"/>
+        <f t="shared" si="195"/>
         <v>0</v>
       </c>
       <c r="AC41" s="5">
@@ -6802,7 +6793,7 @@
         <v>7.2</v>
       </c>
       <c r="AM41" s="5">
-        <f t="shared" si="202"/>
+        <f t="shared" si="199"/>
         <v>0</v>
       </c>
       <c r="AN41" s="5">
@@ -6844,14 +6835,14 @@
         <v>22.9</v>
       </c>
       <c r="X42" s="5">
-        <f t="shared" si="197"/>
+        <f t="shared" si="194"/>
         <v>-20.099999999999998</v>
       </c>
       <c r="AA42" s="5">
         <v>40.700000000000003</v>
       </c>
       <c r="AB42" s="5">
-        <f t="shared" si="198"/>
+        <f t="shared" si="195"/>
         <v>-48</v>
       </c>
       <c r="AC42" s="5">
@@ -6870,7 +6861,7 @@
         <v>4.7</v>
       </c>
       <c r="AM42" s="5">
-        <f t="shared" si="202"/>
+        <f t="shared" si="199"/>
         <v>-7.2999999999999972</v>
       </c>
       <c r="AN42" s="5">
@@ -6912,14 +6903,14 @@
         <v>4.7</v>
       </c>
       <c r="X43" s="5">
-        <f t="shared" si="197"/>
+        <f t="shared" si="194"/>
         <v>18.100000000000001</v>
       </c>
       <c r="AA43" s="5">
         <v>22.4</v>
       </c>
       <c r="AB43" s="5">
-        <f t="shared" si="198"/>
+        <f t="shared" si="195"/>
         <v>25.800000000000004</v>
       </c>
       <c r="AC43" s="5">
@@ -6938,7 +6929,7 @@
         <v>-18.8</v>
       </c>
       <c r="AM43" s="5">
-        <f t="shared" si="202"/>
+        <f t="shared" si="199"/>
         <v>48.2</v>
       </c>
       <c r="AN43" s="5">
@@ -6978,12 +6969,12 @@
       </c>
       <c r="W44" s="5"/>
       <c r="X44" s="5">
-        <f t="shared" si="197"/>
+        <f t="shared" si="194"/>
         <v>0</v>
       </c>
       <c r="AA44" s="5"/>
       <c r="AB44" s="5">
-        <f t="shared" si="198"/>
+        <f t="shared" si="195"/>
         <v>0</v>
       </c>
       <c r="AC44" s="5">
@@ -7002,7 +6993,7 @@
         <v>115.6</v>
       </c>
       <c r="AM44" s="5">
-        <f t="shared" si="202"/>
+        <f t="shared" si="199"/>
         <v>0</v>
       </c>
       <c r="AN44" s="5">
@@ -7044,14 +7035,14 @@
         <v>-6.8</v>
       </c>
       <c r="X45" s="5">
-        <f t="shared" si="197"/>
+        <f t="shared" si="194"/>
         <v>40.099999999999994</v>
       </c>
       <c r="AA45" s="5">
         <v>18.8</v>
       </c>
       <c r="AB45" s="5">
-        <f t="shared" si="198"/>
+        <f t="shared" si="195"/>
         <v>101.9</v>
       </c>
       <c r="AC45" s="5">
@@ -7070,7 +7061,7 @@
         <v>22.4</v>
       </c>
       <c r="AM45" s="5">
-        <f t="shared" si="202"/>
+        <f t="shared" si="199"/>
         <v>120.7</v>
       </c>
       <c r="AN45" s="5">
@@ -7110,12 +7101,12 @@
       </c>
       <c r="W46" s="5"/>
       <c r="X46" s="5">
-        <f t="shared" si="197"/>
+        <f t="shared" si="194"/>
         <v>0</v>
       </c>
       <c r="AA46" s="5"/>
       <c r="AB46" s="5">
-        <f t="shared" si="198"/>
+        <f t="shared" si="195"/>
         <v>0</v>
       </c>
       <c r="AC46" s="5">
@@ -7134,7 +7125,7 @@
         <v>54.4</v>
       </c>
       <c r="AM46" s="5">
-        <f t="shared" si="202"/>
+        <f t="shared" si="199"/>
         <v>0</v>
       </c>
       <c r="AN46" s="5">
@@ -7174,12 +7165,12 @@
       </c>
       <c r="W47" s="5"/>
       <c r="X47" s="5">
-        <f t="shared" si="197"/>
+        <f t="shared" si="194"/>
         <v>0</v>
       </c>
       <c r="AA47" s="5"/>
       <c r="AB47" s="5">
-        <f t="shared" si="198"/>
+        <f t="shared" si="195"/>
         <v>0</v>
       </c>
       <c r="AC47" s="5">
@@ -7198,7 +7189,7 @@
         <v>-49</v>
       </c>
       <c r="AM47" s="5">
-        <f t="shared" si="202"/>
+        <f t="shared" si="199"/>
         <v>0</v>
       </c>
       <c r="AN47" s="5">
@@ -7240,14 +7231,14 @@
         <v>-15.5</v>
       </c>
       <c r="X48" s="5">
-        <f t="shared" si="197"/>
+        <f t="shared" si="194"/>
         <v>-1.8000000000000007</v>
       </c>
       <c r="AA48" s="5">
         <v>-13.2</v>
       </c>
       <c r="AB48" s="5">
-        <f t="shared" si="198"/>
+        <f t="shared" si="195"/>
         <v>-11.7</v>
       </c>
       <c r="AC48" s="5">
@@ -7266,7 +7257,7 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="AM48" s="5">
-        <f t="shared" si="202"/>
+        <f t="shared" si="199"/>
         <v>-24.9</v>
       </c>
       <c r="AN48" s="5">
@@ -7321,12 +7312,12 @@
         <v>535.90000000000009</v>
       </c>
       <c r="AC49" s="8">
-        <f t="shared" ref="AC49:AD49" si="207">AC33+SUM(AC34:AC48)</f>
-        <v>518.69313000000011</v>
+        <f t="shared" ref="AC49:AD49" si="204">AC33+SUM(AC34:AC48)</f>
+        <v>660.46299999999997</v>
       </c>
       <c r="AD49" s="8">
-        <f t="shared" si="207"/>
-        <v>441.82404000000014</v>
+        <f t="shared" si="204"/>
+        <v>521.19084000000021</v>
       </c>
       <c r="AJ49" s="8">
         <f>AJ33+SUM(AJ34:AJ48)</f>
@@ -7341,48 +7332,48 @@
         <v>1150.0000000000002</v>
       </c>
       <c r="AM49" s="8">
-        <f t="shared" ref="AM49:AW49" si="208">AM33+SUM(AM34:AM48)</f>
-        <v>1804.7171699999999</v>
+        <f t="shared" ref="AM49:AW49" si="205">AM33+SUM(AM34:AM48)</f>
+        <v>2025.8538400000002</v>
       </c>
       <c r="AN49" s="8">
-        <f t="shared" si="208"/>
-        <v>2332.3363185000007</v>
+        <f t="shared" si="205"/>
+        <v>2925.6892060999999</v>
       </c>
       <c r="AO49" s="8">
-        <f t="shared" si="208"/>
-        <v>3226.1858689890009</v>
+        <f t="shared" si="205"/>
+        <v>4211.036295285001</v>
       </c>
       <c r="AP49" s="8">
-        <f t="shared" si="208"/>
-        <v>4313.7840628063705</v>
+        <f t="shared" si="205"/>
+        <v>5878.5471903436501</v>
       </c>
       <c r="AQ49" s="8">
-        <f t="shared" si="208"/>
-        <v>5344.9526927549259</v>
+        <f t="shared" si="205"/>
+        <v>7695.0520426057847</v>
       </c>
       <c r="AR49" s="8">
-        <f t="shared" si="208"/>
-        <v>5965.4283333239773</v>
+        <f t="shared" si="205"/>
+        <v>9122.4255704661882</v>
       </c>
       <c r="AS49" s="8">
-        <f t="shared" si="208"/>
-        <v>6733.210936983457</v>
+        <f t="shared" si="205"/>
+        <v>10721.569186824499</v>
       </c>
       <c r="AT49" s="8">
-        <f t="shared" si="208"/>
-        <v>7475.8860666760784</v>
+        <f t="shared" si="205"/>
+        <v>12034.127388159266</v>
       </c>
       <c r="AU49" s="8">
-        <f t="shared" si="208"/>
-        <v>8297.177962551681</v>
+        <f t="shared" si="205"/>
+        <v>13306.397176454007</v>
       </c>
       <c r="AV49" s="8">
-        <f t="shared" si="208"/>
-        <v>9205.4764758385645</v>
+        <f t="shared" si="205"/>
+        <v>14711.145387626026</v>
       </c>
       <c r="AW49" s="8">
-        <f t="shared" si="208"/>
-        <v>10210.087027995507</v>
+        <f t="shared" si="205"/>
+        <v>16262.24154813225</v>
       </c>
     </row>
     <row r="50" spans="2:141" x14ac:dyDescent="0.3">
@@ -7422,7 +7413,7 @@
         <v>12.6</v>
       </c>
       <c r="AM50" s="5">
-        <f t="shared" si="202"/>
+        <f t="shared" si="199"/>
         <v>32.591000000000001</v>
       </c>
       <c r="AN50" s="5">
@@ -7430,39 +7421,39 @@
         <v>37.479649999999999</v>
       </c>
       <c r="AO50" s="5">
-        <f t="shared" ref="AO50:AW50" si="209">AN50*1.15</f>
+        <f t="shared" ref="AO50:AW50" si="206">AN50*1.15</f>
         <v>43.101597499999997</v>
       </c>
       <c r="AP50" s="5">
-        <f t="shared" si="209"/>
+        <f t="shared" si="206"/>
         <v>49.566837124999992</v>
       </c>
       <c r="AQ50" s="5">
-        <f t="shared" si="209"/>
+        <f t="shared" si="206"/>
         <v>57.001862693749985</v>
       </c>
       <c r="AR50" s="5">
-        <f t="shared" si="209"/>
+        <f t="shared" si="206"/>
         <v>65.552142097812478</v>
       </c>
       <c r="AS50" s="5">
-        <f t="shared" si="209"/>
+        <f t="shared" si="206"/>
         <v>75.384963412484339</v>
       </c>
       <c r="AT50" s="5">
-        <f t="shared" si="209"/>
+        <f t="shared" si="206"/>
         <v>86.692707924356981</v>
       </c>
       <c r="AU50" s="5">
-        <f t="shared" si="209"/>
+        <f t="shared" si="206"/>
         <v>99.696614113010526</v>
       </c>
       <c r="AV50" s="5">
-        <f t="shared" si="209"/>
+        <f t="shared" si="206"/>
         <v>114.6511062299621</v>
       </c>
       <c r="AW50" s="5">
-        <f t="shared" si="209"/>
+        <f t="shared" si="206"/>
         <v>131.84877216445639</v>
       </c>
     </row>
@@ -7487,12 +7478,12 @@
         <v>528.30000000000007</v>
       </c>
       <c r="AC51" s="8">
-        <f t="shared" ref="AC51:AD51" si="210">AC49-AC50</f>
-        <v>509.9531300000001</v>
+        <f t="shared" ref="AC51:AD51" si="207">AC49-AC50</f>
+        <v>651.72299999999996</v>
       </c>
       <c r="AD51" s="8">
-        <f t="shared" si="210"/>
-        <v>431.77304000000015</v>
+        <f t="shared" si="207"/>
+        <v>511.13984000000022</v>
       </c>
       <c r="AJ51" s="8">
         <f>AJ49-AJ50</f>
@@ -7507,416 +7498,416 @@
         <v>1137.4000000000003</v>
       </c>
       <c r="AM51" s="8">
-        <f t="shared" ref="AM51:AW51" si="211">AM49-AM50</f>
-        <v>1772.12617</v>
+        <f t="shared" ref="AM51:AW51" si="208">AM49-AM50</f>
+        <v>1993.2628400000003</v>
       </c>
       <c r="AN51" s="8">
-        <f t="shared" si="211"/>
-        <v>2294.8566685000005</v>
+        <f t="shared" si="208"/>
+        <v>2888.2095560999996</v>
       </c>
       <c r="AO51" s="8">
-        <f t="shared" si="211"/>
-        <v>3183.0842714890009</v>
+        <f t="shared" si="208"/>
+        <v>4167.9346977850009</v>
       </c>
       <c r="AP51" s="8">
-        <f t="shared" si="211"/>
-        <v>4264.2172256813701</v>
+        <f t="shared" si="208"/>
+        <v>5828.9803532186497</v>
       </c>
       <c r="AQ51" s="8">
-        <f t="shared" si="211"/>
-        <v>5287.950830061176</v>
+        <f t="shared" si="208"/>
+        <v>7638.0501799120348</v>
       </c>
       <c r="AR51" s="8">
-        <f t="shared" si="211"/>
-        <v>5899.8761912261652</v>
+        <f t="shared" si="208"/>
+        <v>9056.8734283683752</v>
       </c>
       <c r="AS51" s="8">
-        <f t="shared" si="211"/>
-        <v>6657.8259735709726</v>
+        <f t="shared" si="208"/>
+        <v>10646.184223412016</v>
       </c>
       <c r="AT51" s="8">
-        <f t="shared" si="211"/>
-        <v>7389.1933587517215</v>
+        <f t="shared" si="208"/>
+        <v>11947.434680234908</v>
       </c>
       <c r="AU51" s="8">
-        <f t="shared" si="211"/>
-        <v>8197.4813484386705</v>
+        <f t="shared" si="208"/>
+        <v>13206.700562340997</v>
       </c>
       <c r="AV51" s="8">
-        <f t="shared" si="211"/>
-        <v>9090.8253696086031</v>
+        <f t="shared" si="208"/>
+        <v>14596.494281396064</v>
       </c>
       <c r="AW51" s="8">
-        <f t="shared" si="211"/>
-        <v>10078.238255831051</v>
+        <f t="shared" si="208"/>
+        <v>16130.392775967794</v>
       </c>
       <c r="AX51" s="1">
         <f>AW51*(1+$AZ$25)</f>
-        <v>9977.4558732727401</v>
+        <v>15969.088848208115</v>
       </c>
       <c r="AY51" s="1">
-        <f t="shared" ref="AY51:DJ51" si="212">AX51*(1+$AZ$25)</f>
-        <v>9877.681314540012</v>
+        <f t="shared" ref="AY51:DJ51" si="209">AX51*(1+$AZ$25)</f>
+        <v>15809.397959726035</v>
       </c>
       <c r="AZ51" s="1">
-        <f t="shared" si="212"/>
-        <v>9778.9045013946125</v>
+        <f t="shared" si="209"/>
+        <v>15651.303980128774</v>
       </c>
       <c r="BA51" s="1">
-        <f t="shared" si="212"/>
-        <v>9681.1154563806667</v>
+        <f t="shared" si="209"/>
+        <v>15494.790940327486</v>
       </c>
       <c r="BB51" s="1">
-        <f t="shared" si="212"/>
-        <v>9584.3043018168592</v>
+        <f t="shared" si="209"/>
+        <v>15339.84303092421</v>
       </c>
       <c r="BC51" s="1">
-        <f t="shared" si="212"/>
-        <v>9488.4612587986903</v>
+        <f t="shared" si="209"/>
+        <v>15186.444600614968</v>
       </c>
       <c r="BD51" s="1">
-        <f t="shared" si="212"/>
-        <v>9393.576646210704</v>
+        <f t="shared" si="209"/>
+        <v>15034.580154608819</v>
       </c>
       <c r="BE51" s="1">
-        <f t="shared" si="212"/>
-        <v>9299.6408797485965</v>
+        <f t="shared" si="209"/>
+        <v>14884.234353062729</v>
       </c>
       <c r="BF51" s="1">
-        <f t="shared" si="212"/>
-        <v>9206.6444709511106</v>
+        <f t="shared" si="209"/>
+        <v>14735.392009532103</v>
       </c>
       <c r="BG51" s="1">
-        <f t="shared" si="212"/>
-        <v>9114.5780262415992</v>
+        <f t="shared" si="209"/>
+        <v>14588.038089436781</v>
       </c>
       <c r="BH51" s="1">
-        <f t="shared" si="212"/>
-        <v>9023.4322459791838</v>
+        <f t="shared" si="209"/>
+        <v>14442.157708542412</v>
       </c>
       <c r="BI51" s="1">
-        <f t="shared" si="212"/>
-        <v>8933.1979235193921</v>
+        <f t="shared" si="209"/>
+        <v>14297.736131456988</v>
       </c>
       <c r="BJ51" s="1">
-        <f t="shared" si="212"/>
-        <v>8843.8659442841981</v>
+        <f t="shared" si="209"/>
+        <v>14154.758770142418</v>
       </c>
       <c r="BK51" s="1">
-        <f t="shared" si="212"/>
-        <v>8755.4272848413566</v>
+        <f t="shared" si="209"/>
+        <v>14013.211182440993</v>
       </c>
       <c r="BL51" s="1">
-        <f t="shared" si="212"/>
-        <v>8667.8730119929423</v>
+        <f t="shared" si="209"/>
+        <v>13873.079070616583</v>
       </c>
       <c r="BM51" s="1">
-        <f t="shared" si="212"/>
-        <v>8581.1942818730131</v>
+        <f t="shared" si="209"/>
+        <v>13734.348279910417</v>
       </c>
       <c r="BN51" s="1">
-        <f t="shared" si="212"/>
-        <v>8495.3823390542821</v>
+        <f t="shared" si="209"/>
+        <v>13597.004797111313</v>
       </c>
       <c r="BO51" s="1">
-        <f t="shared" si="212"/>
-        <v>8410.4285156637397</v>
+        <f t="shared" si="209"/>
+        <v>13461.034749140199</v>
       </c>
       <c r="BP51" s="1">
-        <f t="shared" si="212"/>
-        <v>8326.3242305071017</v>
+        <f t="shared" si="209"/>
+        <v>13326.424401648797</v>
       </c>
       <c r="BQ51" s="1">
-        <f t="shared" si="212"/>
-        <v>8243.0609882020308</v>
+        <f t="shared" si="209"/>
+        <v>13193.16015763231</v>
       </c>
       <c r="BR51" s="1">
-        <f t="shared" si="212"/>
-        <v>8160.6303783200101</v>
+        <f t="shared" si="209"/>
+        <v>13061.228556055987</v>
       </c>
       <c r="BS51" s="1">
-        <f t="shared" si="212"/>
-        <v>8079.0240745368101</v>
+        <f t="shared" si="209"/>
+        <v>12930.616270495426</v>
       </c>
       <c r="BT51" s="1">
-        <f t="shared" si="212"/>
-        <v>7998.2338337914416</v>
+        <f t="shared" si="209"/>
+        <v>12801.310107790472</v>
       </c>
       <c r="BU51" s="1">
-        <f t="shared" si="212"/>
-        <v>7918.2514954535272</v>
+        <f t="shared" si="209"/>
+        <v>12673.297006712568</v>
       </c>
       <c r="BV51" s="1">
-        <f t="shared" si="212"/>
-        <v>7839.0689804989916</v>
+        <f t="shared" si="209"/>
+        <v>12546.564036645443</v>
       </c>
       <c r="BW51" s="1">
-        <f t="shared" si="212"/>
-        <v>7760.6782906940016</v>
+        <f t="shared" si="209"/>
+        <v>12421.098396278989</v>
       </c>
       <c r="BX51" s="1">
-        <f t="shared" si="212"/>
-        <v>7683.0715077870618</v>
+        <f t="shared" si="209"/>
+        <v>12296.887412316199</v>
       </c>
       <c r="BY51" s="1">
-        <f t="shared" si="212"/>
-        <v>7606.2407927091908</v>
+        <f t="shared" si="209"/>
+        <v>12173.918538193037</v>
       </c>
       <c r="BZ51" s="1">
-        <f t="shared" si="212"/>
-        <v>7530.1783847820989</v>
+        <f t="shared" si="209"/>
+        <v>12052.179352811107</v>
       </c>
       <c r="CA51" s="1">
-        <f t="shared" si="212"/>
-        <v>7454.876600934278</v>
+        <f t="shared" si="209"/>
+        <v>11931.657559282996</v>
       </c>
       <c r="CB51" s="1">
-        <f t="shared" si="212"/>
-        <v>7380.3278349249349</v>
+        <f t="shared" si="209"/>
+        <v>11812.340983690166</v>
       </c>
       <c r="CC51" s="1">
-        <f t="shared" si="212"/>
-        <v>7306.5245565756859</v>
+        <f t="shared" si="209"/>
+        <v>11694.217573853264</v>
       </c>
       <c r="CD51" s="1">
-        <f t="shared" si="212"/>
-        <v>7233.4593110099286</v>
+        <f t="shared" si="209"/>
+        <v>11577.275398114731</v>
       </c>
       <c r="CE51" s="1">
-        <f t="shared" si="212"/>
-        <v>7161.1247178998292</v>
+        <f t="shared" si="209"/>
+        <v>11461.502644133583</v>
       </c>
       <c r="CF51" s="1">
-        <f t="shared" si="212"/>
-        <v>7089.5134707208308</v>
+        <f t="shared" si="209"/>
+        <v>11346.887617692248</v>
       </c>
       <c r="CG51" s="1">
-        <f t="shared" si="212"/>
-        <v>7018.6183360136229</v>
+        <f t="shared" si="209"/>
+        <v>11233.418741515325</v>
       </c>
       <c r="CH51" s="1">
-        <f t="shared" si="212"/>
-        <v>6948.4321526534868</v>
+        <f t="shared" si="209"/>
+        <v>11121.084554100171</v>
       </c>
       <c r="CI51" s="1">
-        <f t="shared" si="212"/>
-        <v>6878.9478311269522</v>
+        <f t="shared" si="209"/>
+        <v>11009.873708559169</v>
       </c>
       <c r="CJ51" s="1">
-        <f t="shared" si="212"/>
-        <v>6810.1583528156825</v>
+        <f t="shared" si="209"/>
+        <v>10899.774971473578</v>
       </c>
       <c r="CK51" s="1">
-        <f t="shared" si="212"/>
-        <v>6742.0567692875256</v>
+        <f t="shared" si="209"/>
+        <v>10790.777221758843</v>
       </c>
       <c r="CL51" s="1">
-        <f t="shared" si="212"/>
-        <v>6674.6362015946506</v>
+        <f t="shared" si="209"/>
+        <v>10682.869449541255</v>
       </c>
       <c r="CM51" s="1">
-        <f t="shared" si="212"/>
-        <v>6607.8898395787037</v>
+        <f t="shared" si="209"/>
+        <v>10576.040755045842</v>
       </c>
       <c r="CN51" s="1">
-        <f t="shared" si="212"/>
-        <v>6541.8109411829164</v>
+        <f t="shared" si="209"/>
+        <v>10470.280347495383</v>
       </c>
       <c r="CO51" s="1">
-        <f t="shared" si="212"/>
-        <v>6476.392831771087</v>
+        <f t="shared" si="209"/>
+        <v>10365.577544020429</v>
       </c>
       <c r="CP51" s="1">
-        <f t="shared" si="212"/>
-        <v>6411.6289034533756</v>
+        <f t="shared" si="209"/>
+        <v>10261.921768580225</v>
       </c>
       <c r="CQ51" s="1">
-        <f t="shared" si="212"/>
-        <v>6347.5126144188416</v>
+        <f t="shared" si="209"/>
+        <v>10159.302550894423</v>
       </c>
       <c r="CR51" s="1">
-        <f t="shared" si="212"/>
-        <v>6284.0374882746528</v>
+        <f t="shared" si="209"/>
+        <v>10057.709525385479</v>
       </c>
       <c r="CS51" s="1">
-        <f t="shared" si="212"/>
-        <v>6221.197113391906</v>
+        <f t="shared" si="209"/>
+        <v>9957.1324301316236</v>
       </c>
       <c r="CT51" s="1">
-        <f t="shared" si="212"/>
-        <v>6158.9851422579868</v>
+        <f t="shared" si="209"/>
+        <v>9857.5611058303075</v>
       </c>
       <c r="CU51" s="1">
-        <f t="shared" si="212"/>
-        <v>6097.3952908354067</v>
+        <f t="shared" si="209"/>
+        <v>9758.985494772005</v>
       </c>
       <c r="CV51" s="1">
-        <f t="shared" si="212"/>
-        <v>6036.4213379270523</v>
+        <f t="shared" si="209"/>
+        <v>9661.3956398242844</v>
       </c>
       <c r="CW51" s="1">
-        <f t="shared" si="212"/>
-        <v>5976.0571245477813</v>
+        <f t="shared" si="209"/>
+        <v>9564.7816834260411</v>
       </c>
       <c r="CX51" s="1">
-        <f t="shared" si="212"/>
-        <v>5916.2965533023034</v>
+        <f t="shared" si="209"/>
+        <v>9469.133866591781</v>
       </c>
       <c r="CY51" s="1">
-        <f t="shared" si="212"/>
-        <v>5857.13358776928</v>
+        <f t="shared" si="209"/>
+        <v>9374.442527925863</v>
       </c>
       <c r="CZ51" s="1">
-        <f t="shared" si="212"/>
-        <v>5798.562251891587</v>
+        <f t="shared" si="209"/>
+        <v>9280.6981026466037</v>
       </c>
       <c r="DA51" s="1">
-        <f t="shared" si="212"/>
-        <v>5740.5766293726711</v>
+        <f t="shared" si="209"/>
+        <v>9187.8911216201377</v>
       </c>
       <c r="DB51" s="1">
-        <f t="shared" si="212"/>
-        <v>5683.1708630789444</v>
+        <f t="shared" si="209"/>
+        <v>9096.0122104039365</v>
       </c>
       <c r="DC51" s="1">
-        <f t="shared" si="212"/>
-        <v>5626.3391544481547</v>
+        <f t="shared" si="209"/>
+        <v>9005.0520882998972</v>
       </c>
       <c r="DD51" s="1">
-        <f t="shared" si="212"/>
-        <v>5570.0757629036734</v>
+        <f t="shared" si="209"/>
+        <v>8915.001567416899</v>
       </c>
       <c r="DE51" s="1">
-        <f t="shared" si="212"/>
-        <v>5514.3750052746364</v>
+        <f t="shared" si="209"/>
+        <v>8825.8515517427295</v>
       </c>
       <c r="DF51" s="1">
-        <f t="shared" si="212"/>
-        <v>5459.23125522189</v>
+        <f t="shared" si="209"/>
+        <v>8737.5930362253021</v>
       </c>
       <c r="DG51" s="1">
-        <f t="shared" si="212"/>
-        <v>5404.6389426696715</v>
+        <f t="shared" si="209"/>
+        <v>8650.2171058630483</v>
       </c>
       <c r="DH51" s="1">
-        <f t="shared" si="212"/>
-        <v>5350.5925532429746</v>
+        <f t="shared" si="209"/>
+        <v>8563.7149348044186</v>
       </c>
       <c r="DI51" s="1">
-        <f t="shared" si="212"/>
-        <v>5297.0866277105451</v>
+        <f t="shared" si="209"/>
+        <v>8478.0777854563748</v>
       </c>
       <c r="DJ51" s="1">
-        <f t="shared" si="212"/>
-        <v>5244.1157614334397</v>
+        <f t="shared" si="209"/>
+        <v>8393.2970076018119</v>
       </c>
       <c r="DK51" s="1">
-        <f t="shared" ref="DK51:EK51" si="213">DJ51*(1+$AZ$25)</f>
-        <v>5191.674603819105</v>
+        <f t="shared" ref="DK51:EK51" si="210">DJ51*(1+$AZ$25)</f>
+        <v>8309.3640375257928</v>
       </c>
       <c r="DL51" s="1">
-        <f t="shared" si="213"/>
-        <v>5139.7578577809136</v>
+        <f t="shared" si="210"/>
+        <v>8226.2703971505343</v>
       </c>
       <c r="DM51" s="1">
-        <f t="shared" si="213"/>
-        <v>5088.3602792031043</v>
+        <f t="shared" si="210"/>
+        <v>8144.007693179029</v>
       </c>
       <c r="DN51" s="1">
-        <f t="shared" si="213"/>
-        <v>5037.4766764110727</v>
+        <f t="shared" si="210"/>
+        <v>8062.5676162472391</v>
       </c>
       <c r="DO51" s="1">
-        <f t="shared" si="213"/>
-        <v>4987.1019096469618</v>
+        <f t="shared" si="210"/>
+        <v>7981.9419400847664</v>
       </c>
       <c r="DP51" s="1">
-        <f t="shared" si="213"/>
-        <v>4937.2308905504924</v>
+        <f t="shared" si="210"/>
+        <v>7902.122520683919</v>
       </c>
       <c r="DQ51" s="1">
-        <f t="shared" si="213"/>
-        <v>4887.8585816449877</v>
+        <f t="shared" si="210"/>
+        <v>7823.1012954770795</v>
       </c>
       <c r="DR51" s="1">
-        <f t="shared" si="213"/>
-        <v>4838.9799958285375</v>
+        <f t="shared" si="210"/>
+        <v>7744.870282522309</v>
       </c>
       <c r="DS51" s="1">
-        <f t="shared" si="213"/>
-        <v>4790.5901958702525</v>
+        <f t="shared" si="210"/>
+        <v>7667.4215796970857</v>
       </c>
       <c r="DT51" s="1">
-        <f t="shared" si="213"/>
-        <v>4742.6842939115495</v>
+        <f t="shared" si="210"/>
+        <v>7590.7473639001146</v>
       </c>
       <c r="DU51" s="1">
-        <f t="shared" si="213"/>
-        <v>4695.2574509724336</v>
+        <f t="shared" si="210"/>
+        <v>7514.8398902611134</v>
       </c>
       <c r="DV51" s="1">
-        <f t="shared" si="213"/>
-        <v>4648.3048764627092</v>
+        <f t="shared" si="210"/>
+        <v>7439.6914913585024</v>
       </c>
       <c r="DW51" s="1">
-        <f t="shared" si="213"/>
-        <v>4601.8218276980824</v>
+        <f t="shared" si="210"/>
+        <v>7365.2945764449169</v>
       </c>
       <c r="DX51" s="1">
-        <f t="shared" si="213"/>
-        <v>4555.8036094211011</v>
+        <f t="shared" si="210"/>
+        <v>7291.6416306804676</v>
       </c>
       <c r="DY51" s="1">
-        <f t="shared" si="213"/>
-        <v>4510.2455733268898</v>
+        <f t="shared" si="210"/>
+        <v>7218.7252143736632</v>
       </c>
       <c r="DZ51" s="1">
-        <f t="shared" si="213"/>
-        <v>4465.1431175936204</v>
+        <f t="shared" si="210"/>
+        <v>7146.537962229927</v>
       </c>
       <c r="EA51" s="1">
-        <f t="shared" si="213"/>
-        <v>4420.4916864176839</v>
+        <f t="shared" si="210"/>
+        <v>7075.0725826076277</v>
       </c>
       <c r="EB51" s="1">
-        <f t="shared" si="213"/>
-        <v>4376.2867695535069</v>
+        <f t="shared" si="210"/>
+        <v>7004.3218567815511</v>
       </c>
       <c r="EC51" s="1">
-        <f t="shared" si="213"/>
-        <v>4332.5239018579714</v>
+        <f t="shared" si="210"/>
+        <v>6934.2786382137356</v>
       </c>
       <c r="ED51" s="1">
-        <f t="shared" si="213"/>
-        <v>4289.1986628393915</v>
+        <f t="shared" si="210"/>
+        <v>6864.9358518315985</v>
       </c>
       <c r="EE51" s="1">
-        <f t="shared" si="213"/>
-        <v>4246.3066762109975</v>
+        <f t="shared" si="210"/>
+        <v>6796.2864933132823</v>
       </c>
       <c r="EF51" s="1">
-        <f t="shared" si="213"/>
-        <v>4203.843609448887</v>
+        <f t="shared" si="210"/>
+        <v>6728.3236283801498</v>
       </c>
       <c r="EG51" s="1">
-        <f t="shared" si="213"/>
-        <v>4161.805173354398</v>
+        <f t="shared" si="210"/>
+        <v>6661.0403920963481</v>
       </c>
       <c r="EH51" s="1">
-        <f t="shared" si="213"/>
-        <v>4120.1871216208538</v>
+        <f t="shared" si="210"/>
+        <v>6594.429988175385</v>
       </c>
       <c r="EI51" s="1">
-        <f t="shared" si="213"/>
-        <v>4078.9852504046453</v>
+        <f t="shared" si="210"/>
+        <v>6528.485688293631</v>
       </c>
       <c r="EJ51" s="1">
-        <f t="shared" si="213"/>
-        <v>4038.1953979005989</v>
+        <f t="shared" si="210"/>
+        <v>6463.2008314106943</v>
       </c>
       <c r="EK51" s="1">
-        <f t="shared" si="213"/>
-        <v>3997.8134439215928</v>
+        <f t="shared" si="210"/>
+        <v>6398.568823096587</v>
       </c>
     </row>
     <row r="53" spans="2:141" x14ac:dyDescent="0.3">
@@ -7935,7 +7926,7 @@
     <row r="55" spans="2:141" x14ac:dyDescent="0.3">
       <c r="AZ55" s="5">
         <f>NPV(AZ26,AM51:EK51)</f>
-        <v>141857.03607088616</v>
+        <v>223134.46847264559</v>
       </c>
     </row>
     <row r="56" spans="2:141" x14ac:dyDescent="0.3">
@@ -7951,7 +7942,7 @@
       </c>
       <c r="AZ56" s="5">
         <f>Main!D8</f>
-        <v>5230</v>
+        <v>6437.9</v>
       </c>
     </row>
     <row r="57" spans="2:141" x14ac:dyDescent="0.3">
@@ -7967,7 +7958,7 @@
       </c>
       <c r="AZ57" s="5">
         <f>AZ55+AZ56</f>
-        <v>147087.03607088616</v>
+        <v>229572.36847264558</v>
       </c>
     </row>
     <row r="58" spans="2:141" x14ac:dyDescent="0.3">
@@ -7983,7 +7974,7 @@
       </c>
       <c r="AZ58" s="4">
         <f>AZ57/AW19</f>
-        <v>62.187990897550385</v>
+        <v>96.572593165339725</v>
       </c>
     </row>
     <row r="59" spans="2:141" x14ac:dyDescent="0.3">
@@ -7999,7 +7990,7 @@
       </c>
       <c r="AZ59" s="4">
         <f>Main!D3</f>
-        <v>182.39</v>
+        <v>192.48</v>
       </c>
     </row>
     <row r="60" spans="2:141" x14ac:dyDescent="0.3">
@@ -8015,7 +8006,7 @@
       </c>
       <c r="AZ60" s="10">
         <f>AZ58/AZ59-1</f>
-        <v>-0.65903837437606017</v>
+        <v>-0.49827206377109445</v>
       </c>
     </row>
     <row r="61" spans="2:141" x14ac:dyDescent="0.3">
